--- a/Dashboard/Jumia_Dashboard.xlsx
+++ b/Dashboard/Jumia_Dashboard.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuxDev\Jumia-Project\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4045AD82-E99D-48C7-B0D0-B4183C15027B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2065F2FF-0B6C-4EB0-AE2C-8F370B2DA003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="18960" windowHeight="10905" xr2:uid="{38F01665-FBFE-44BB-A07F-71C8247957D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6F17A25C-8142-493A-80DF-F27B81A0F9E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_Excel_jumia_datasetA1M1101" hidden="1">[2]Excel_jumia_dataset!$A$1:$N$110</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Excel_jumia_datasetA1M1101" hidden="1">[1]Excel_jumia_dataset!$A$1:$N$110</definedName>
     <definedName name="Slicer_Discount_Category">#N/A</definedName>
     <definedName name="Slicer_Product_Type">#N/A</definedName>
     <definedName name="Slicer_Rating">#N/A</definedName>
@@ -29,16 +28,16 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="125" r:id="rId4"/>
-        <pivotCache cacheId="126" r:id="rId5"/>
-        <pivotCache cacheId="127" r:id="rId6"/>
+        <pivotCache cacheId="4" r:id="rId3"/>
+        <pivotCache cacheId="3" r:id="rId4"/>
+        <pivotCache cacheId="0" r:id="rId5"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
+        <x14:slicerCache r:id="rId6"/>
         <x14:slicerCache r:id="rId7"/>
         <x14:slicerCache r:id="rId8"/>
-        <x14:slicerCache r:id="rId9"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -50,7 +49,7 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
       <x15:dataModel>
         <x15:modelTables>
-          <x15:modelTable id="Range-abc0bbba-e915-4d58-8685-f8d076d7229a" name="Range" connection="WorksheetConnection_Excel_jumia_dataset!$A$1:$M$110"/>
+          <x15:modelTable id="Range-aeb7d533-aafb-4579-9404-31f236ed0e9a" name="Range" connection="WorksheetConnection_Excel_jumia_dataset!$A$1:$M$110"/>
         </x15:modelTables>
       </x15:dataModel>
     </ext>
@@ -81,7 +80,7 @@
   <connection id="2" xr16:uid="{7E3001D3-86B0-493A-95E7-51BE1A00337D}" name="WorksheetConnection_Excel_jumia_dataset!$A$1:$M$110" type="102" refreshedVersion="8" minRefreshableVersion="5">
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="Range-abc0bbba-e915-4d58-8685-f8d076d7229a" autoDelete="1">
+        <x15:connection id="Range-aeb7d533-aafb-4579-9404-31f236ed0e9a" autoDelete="1">
           <x15:rangePr sourceName="_xlcn.WorksheetConnection_Excel_jumia_datasetA1M1101"/>
         </x15:connection>
       </ext>
@@ -110,7 +109,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,7 +485,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DFA3-4ACF-BB42-09320F8E17CC}"/>
+              <c16:uniqueId val="{00000000-79F5-4077-B2D7-81D75BA0F3BD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1002,7 +1001,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1103-4726-9C51-075E0AB17BEB}"/>
+              <c16:uniqueId val="{00000000-13DF-4CA3-95C1-68A2114F53F1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1303,7 +1302,7 @@
             <c:numRef>
               <c:f>[1]Excel_jumia_dataset!$H$2:$H$111</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0.38</c:v>
@@ -1980,7 +1979,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F89C-4409-A0F6-2562F806436E}"/>
+              <c16:uniqueId val="{00000000-81F7-488C-B092-48A56822E705}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2071,7 +2070,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2925,7 +2924,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-620B-461B-9BDB-7C85F03ED6C1}"/>
+              <c16:uniqueId val="{00000000-3A2B-4695-9D4B-E8A00B1B4CA0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3644,7 +3643,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-82F3-4345-B37B-822A09D116C1}"/>
+                <c16:uniqueId val="{00000001-1B0D-45A9-865C-6BDABD67614F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3666,7 +3665,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-82F3-4345-B37B-822A09D116C1}"/>
+                <c16:uniqueId val="{00000003-1B0D-45A9-865C-6BDABD67614F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3688,7 +3687,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-82F3-4345-B37B-822A09D116C1}"/>
+                <c16:uniqueId val="{00000005-1B0D-45A9-865C-6BDABD67614F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3710,7 +3709,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-82F3-4345-B37B-822A09D116C1}"/>
+                <c16:uniqueId val="{00000007-1B0D-45A9-865C-6BDABD67614F}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3748,7 +3747,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-82F3-4345-B37B-822A09D116C1}"/>
+              <c16:uniqueId val="{00000008-1B0D-45A9-865C-6BDABD67614F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3773,16 +3772,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.66666666666666663"/>
-          <c:y val="0.41629520268299797"/>
-          <c:w val="0.22321428571428575"/>
-          <c:h val="0.37976851851851851"/>
-        </c:manualLayout>
-      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3896,7 +3885,7 @@
                   <a:srgbClr val="FF0000"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Product Rating Category</a:t>
+              <a:t>Product Discount Category</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" b="1">
               <a:solidFill>
@@ -3906,14 +3895,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.34241797900262472"/>
-          <c:y val="7.3053368328958895E-2"/>
-        </c:manualLayout>
-      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4007,7 +3988,9 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent4"/>
+            <a:schemeClr val="accent4">
+              <a:shade val="76000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -4016,57 +3999,13 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent4">
-              <a:shade val="58000"/>
+              <a:tint val="77000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
@@ -4079,54 +4018,6 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent4">
-              <a:shade val="86000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent4">
-              <a:tint val="86000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent4">
-              <a:tint val="58000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent4"/>
@@ -4184,11 +4075,11 @@
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="7"/>
+        <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent4">
-              <a:shade val="58000"/>
+              <a:shade val="76000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
@@ -4200,11 +4091,101 @@
         </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:tint val="77000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:tint val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
         <c:idx val="8"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent4">
-              <a:shade val="86000"/>
+              <a:shade val="76000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
@@ -4220,7 +4201,7 @@
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent4">
-              <a:tint val="86000"/>
+              <a:tint val="77000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
@@ -4236,7 +4217,7 @@
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent4">
-              <a:tint val="58000"/>
+              <a:tint val="65000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:ln w="19050">
@@ -4264,7 +4245,7 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4">
-                  <a:shade val="58000"/>
+                  <a:shade val="76000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -4276,7 +4257,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-A4BF-46F5-B890-091CE9D3CD4A}"/>
+                <c16:uniqueId val="{00000001-7BC6-46A8-B242-ED1A089F9296}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4286,7 +4267,7 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4">
-                  <a:shade val="86000"/>
+                  <a:tint val="77000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -4298,7 +4279,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-A4BF-46F5-B890-091CE9D3CD4A}"/>
+                <c16:uniqueId val="{00000003-7BC6-46A8-B242-ED1A089F9296}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4308,7 +4289,7 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent4">
-                  <a:tint val="86000"/>
+                  <a:tint val="65000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -4320,67 +4301,42 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-A4BF-46F5-B890-091CE9D3CD4A}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:tint val="58000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-A4BF-46F5-B890-091CE9D3CD4A}"/>
+                <c16:uniqueId val="{00000005-7BC6-46A8-B242-ED1A089F9296}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="4"/>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>High</c:v>
+              </c:pt>
               <c:pt idx="1">
-                <c:v>Average</c:v>
+                <c:v>Low</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>Excellent</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>Poor</c:v>
+                <c:v>Medium</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
           <c:val>
             <c:numLit>
               <c:formatCode>General</c:formatCode>
-              <c:ptCount val="4"/>
+              <c:ptCount val="3"/>
               <c:pt idx="0">
-                <c:v>52</c:v>
+                <c:v>58</c:v>
               </c:pt>
               <c:pt idx="1">
-                <c:v>22</c:v>
+                <c:v>18</c:v>
               </c:pt>
               <c:pt idx="2">
-                <c:v>23</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>12</c:v>
+                <c:v>32</c:v>
               </c:pt>
             </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-A4BF-46F5-B890-091CE9D3CD4A}"/>
+              <c16:uniqueId val="{00000006-7BC6-46A8-B242-ED1A089F9296}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4409,10 +4365,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.66666666666666663"/>
-          <c:y val="0.41629520268299797"/>
-          <c:w val="0.22321428571428575"/>
-          <c:h val="0.37976851851851851"/>
+          <c:x val="0.6791666666666667"/>
+          <c:y val="0.44146908719743366"/>
+          <c:w val="0.23655913978494622"/>
+          <c:h val="0.30164297171186932"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -7606,13 +7562,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>584029</xdr:colOff>
+      <xdr:colOff>360349</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>162928</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>576514</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>64576</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>75002</xdr:rowOff>
     </xdr:to>
@@ -7621,7 +7577,7 @@
         <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EDBF375-3DE9-47D1-8BFD-8D4B3548EFC4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96B1F70B-D838-4607-AA6E-BF4B9A80D7D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7629,8 +7585,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3654588" y="162928"/>
-          <a:ext cx="4905380" cy="476054"/>
+          <a:off x="3408349" y="162928"/>
+          <a:ext cx="5800227" cy="483574"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7677,9 +7633,40 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="2000" b="1"/>
+            <a:rPr lang="en-US" sz="2400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>JUMIA PRODUCT PERFORMANCE EXPLORER</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="2400" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7703,7 +7690,7 @@
         <xdr:cNvPr id="3" name="Rectangle: Rounded Corners 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A84A9157-E3F1-467B-B71D-84F9BD22D1A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64036D69-F34D-4BA2-B402-C7A0301383DC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7761,20 +7748,20 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>98155</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>4113</xdr:rowOff>
+      <xdr:rowOff>16646</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>460104</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>115457</xdr:rowOff>
+      <xdr:rowOff>127990</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="Rectangle: Rounded Corners 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73776D31-449E-46F3-88EF-AC77B33D2D18}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7D8D434-BD83-419A-9848-42E93BC0D6B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7782,8 +7769,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5011050" y="756087"/>
-          <a:ext cx="1590172" cy="487331"/>
+          <a:off x="4974955" y="778646"/>
+          <a:ext cx="1581149" cy="492344"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7834,20 +7821,20 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>511238</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>170049</xdr:rowOff>
+      <xdr:rowOff>182582</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>263588</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>100262</xdr:rowOff>
+      <xdr:rowOff>112795</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="Rectangle: Rounded Corners 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EA9DF34-19E8-4885-A83C-1F3B64D0C265}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10945F70-79B4-4A7A-B5D9-525B2953D047}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7855,8 +7842,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6652356" y="734029"/>
-          <a:ext cx="1594686" cy="494194"/>
+          <a:off x="6607238" y="754082"/>
+          <a:ext cx="1581150" cy="501713"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7912,20 +7899,20 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>311214</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>173057</xdr:rowOff>
+      <xdr:rowOff>176668</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>63564</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>96407</xdr:rowOff>
+      <xdr:rowOff>100018</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="6" name="Rectangle: Rounded Corners 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159A25EE-A82B-414E-9A54-42F78277F3C9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7C56F05-6B2D-4641-8ABC-0095A1576914}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7933,8 +7920,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8294668" y="737037"/>
-          <a:ext cx="1594685" cy="487331"/>
+          <a:off x="8236014" y="748168"/>
+          <a:ext cx="1581150" cy="494850"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7987,15 +7974,15 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1842336" cy="1937084"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="1840424" cy="1994438"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Product Type 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3CA3234-6234-45B5-9C5B-D3CB86057F64}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA68A00C-ECE8-4454-AB42-EAB992D27D98}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8012,7 +7999,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8022,8 +8009,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="209550" y="1363580"/>
-              <a:ext cx="1842336" cy="1937084"/>
+              <a:off x="209550" y="1344084"/>
+              <a:ext cx="1840424" cy="1994438"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8060,15 +8047,15 @@
       <xdr:row>17</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1842336" cy="1156536"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="1840424" cy="1190948"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Discount Category 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CE397EC-7488-4470-817D-8B54F7A40EBB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4045BB-63FF-4FF3-BCE3-DA48B094C97A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8085,7 +8072,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8095,8 +8082,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="200025" y="3338763"/>
-              <a:ext cx="1842336" cy="1156536"/>
+              <a:off x="200025" y="3291417"/>
+              <a:ext cx="1840424" cy="1190948"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8133,15 +8120,15 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>38102</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1842336" cy="1343543"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="1840424" cy="1383690"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Rating 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F8B757B-9968-49E6-B9C6-2185AA1FF42D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE60699B-C9A1-4F55-B5BE-37FD36906261}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8158,7 +8145,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8168,8 +8155,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="190500" y="4549944"/>
-              <a:ext cx="1842336" cy="1343543"/>
+              <a:off x="190500" y="4483102"/>
+              <a:ext cx="1840424" cy="1383690"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8217,7 +8204,7 @@
         <xdr:cNvPr id="10" name="Chart 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBBD97DF-7438-4A42-B10A-66073D01826B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D6A86E6-0326-4E9E-9994-0FC38C4FDB6E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8255,7 +8242,7 @@
         <xdr:cNvPr id="11" name="Chart 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12C0D9D4-7715-4D23-91D8-EA9FD01CBBA4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6874E857-90A4-411A-BE9B-F9519C8E42CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8293,7 +8280,7 @@
         <xdr:cNvPr id="12" name="Chart 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3BCDF25-918A-435A-8A25-543EFEDB8E6C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA00C460-B2F4-4AB0-B54E-32B3B6E0DCFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8331,7 +8318,7 @@
         <xdr:cNvPr id="13" name="Chart 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{202F9121-F895-428E-91F4-80FCF16CA265}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848DC7A6-A222-44E1-8D73-DFE5DD716C31}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8354,22 +8341,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>258536</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>254925</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>136071</xdr:rowOff>
+      <xdr:colOff>91639</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="14" name="Chart 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{086ECA30-029B-4450-93EF-D12C96DBEC94}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B3D6D88-C34D-4706-9C00-E6B6ADEA71AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8392,22 +8379,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>258537</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>13607</xdr:rowOff>
+      <xdr:colOff>238126</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>37599</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>108857</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:colOff>75199</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>137862</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="15" name="Chart 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81CBB810-6DEA-42F3-87F0-3CE8387C3C95}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B23BF48E-0B7D-4191-B0A8-ED16F568AC9D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8452,1206 +8439,4527 @@
           <cell r="A1" t="str">
             <v>Product</v>
           </cell>
+          <cell r="B1" t="str">
+            <v>Product Type</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>Current price</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>Current price Num</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>old price</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>Old Price Num</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>Abs Discount</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>Discount</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>Discount Category</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>Review</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>Reviews</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>Rating</v>
+          </cell>
           <cell r="M1" t="str">
             <v>Rating Std</v>
           </cell>
+          <cell r="N1" t="str">
+            <v>Rating Category</v>
+          </cell>
         </row>
         <row r="2">
+          <cell r="A2" t="str">
+            <v>115  Piece Set Of Multifunctional Precision Screwdrivers</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>Tools &amp; Hardware</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>KSh 950</v>
+          </cell>
+          <cell r="D2">
+            <v>950</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>KSh 1,525</v>
+          </cell>
+          <cell r="F2">
+            <v>1525</v>
+          </cell>
+          <cell r="G2">
+            <v>575</v>
+          </cell>
           <cell r="H2">
             <v>0.38</v>
           </cell>
+          <cell r="I2" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J2">
+            <v>-2</v>
+          </cell>
           <cell r="K2">
             <v>2</v>
           </cell>
+          <cell r="L2" t="str">
+            <v>4.5 out of 5</v>
+          </cell>
           <cell r="M2">
             <v>4.5</v>
           </cell>
+          <cell r="N2" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="3">
+          <cell r="A3" t="str">
+            <v>Metal Decorative Hooks Key Hangers Entryway Wall Hooks Towel Hooks - Home</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>KSh 527</v>
+          </cell>
+          <cell r="D3">
+            <v>527</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>KSh 999</v>
+          </cell>
+          <cell r="F3">
+            <v>999</v>
+          </cell>
+          <cell r="G3">
+            <v>472</v>
+          </cell>
           <cell r="H3">
             <v>0.47</v>
           </cell>
+          <cell r="I3" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J3">
+            <v>-14</v>
+          </cell>
           <cell r="K3">
             <v>14</v>
           </cell>
+          <cell r="L3" t="str">
+            <v>4.1 out of 5</v>
+          </cell>
           <cell r="M3">
             <v>4.0999999999999996</v>
           </cell>
+          <cell r="N3" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="4">
+          <cell r="A4" t="str">
+            <v>Portable Mini Cordless Car Vacuum Cleaner - Blue</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>Cleaning &amp; Appliances</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>KSh 2,199</v>
+          </cell>
+          <cell r="D4">
+            <v>2199</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>KSh 2,923</v>
+          </cell>
+          <cell r="F4">
+            <v>2923</v>
+          </cell>
+          <cell r="G4">
+            <v>724</v>
+          </cell>
           <cell r="H4">
             <v>0.25</v>
           </cell>
+          <cell r="I4" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J4">
+            <v>-24</v>
+          </cell>
           <cell r="K4">
             <v>24</v>
           </cell>
+          <cell r="L4" t="str">
+            <v>4.6 out of 5</v>
+          </cell>
           <cell r="M4">
             <v>4.5999999999999996</v>
           </cell>
+          <cell r="N4" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="5">
+          <cell r="A5" t="str">
+            <v>Weighing Scale Digital Bathroom Body Fat Scale USB-Black</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>KSh 1,580</v>
+          </cell>
+          <cell r="D5">
+            <v>1580</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>KSh 2,499</v>
+          </cell>
+          <cell r="F5">
+            <v>2499</v>
+          </cell>
+          <cell r="G5">
+            <v>919</v>
+          </cell>
           <cell r="H5">
             <v>0.37</v>
           </cell>
+          <cell r="I5" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J5">
+            <v>-7</v>
+          </cell>
           <cell r="K5">
             <v>7</v>
           </cell>
+          <cell r="L5" t="str">
+            <v>4.7 out of 5</v>
+          </cell>
           <cell r="M5">
             <v>4.7</v>
           </cell>
+          <cell r="N5" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="6">
+          <cell r="A6" t="str">
+            <v>Portable Home Small Air Humidifier 3-Speed Fan - Green</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Cleaning &amp; Appliances</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>KSh 1,740</v>
+          </cell>
+          <cell r="D6">
+            <v>1740</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>KSh 2,356</v>
+          </cell>
+          <cell r="F6">
+            <v>2356</v>
+          </cell>
+          <cell r="G6">
+            <v>616</v>
+          </cell>
           <cell r="H6">
             <v>0.26</v>
           </cell>
+          <cell r="I6" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J6">
+            <v>-5</v>
+          </cell>
           <cell r="K6">
             <v>5</v>
           </cell>
+          <cell r="L6" t="str">
+            <v>4.8 out of 5</v>
+          </cell>
           <cell r="M6">
             <v>4.8</v>
           </cell>
+          <cell r="N6" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="7">
+          <cell r="A7" t="str">
+            <v>220V 60W Electric Soldering Iron Kits With Tools, Tips, And Multimeter</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>KSh 2,999</v>
+          </cell>
+          <cell r="D7">
+            <v>2999</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>KSh 3,290</v>
+          </cell>
+          <cell r="F7">
+            <v>3290</v>
+          </cell>
+          <cell r="G7">
+            <v>291</v>
+          </cell>
           <cell r="H7">
             <v>0.09</v>
           </cell>
+          <cell r="I7" t="str">
+            <v>Low</v>
+          </cell>
+          <cell r="J7">
+            <v>-15</v>
+          </cell>
           <cell r="K7">
             <v>15</v>
           </cell>
+          <cell r="L7" t="str">
+            <v>4 out of 5</v>
+          </cell>
           <cell r="M7">
             <v>4</v>
           </cell>
+          <cell r="N7" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="8">
+          <cell r="A8" t="str">
+            <v>137 Pieces Cake Decorating Tool Set Baking Supplies</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>KSh 2,319</v>
+          </cell>
+          <cell r="D8">
+            <v>2319</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>KSh 3,032</v>
+          </cell>
+          <cell r="F8">
+            <v>3032</v>
+          </cell>
+          <cell r="G8">
+            <v>713</v>
+          </cell>
           <cell r="H8">
             <v>0.24</v>
           </cell>
+          <cell r="I8" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J8">
+            <v>-55</v>
+          </cell>
           <cell r="K8">
             <v>55</v>
           </cell>
+          <cell r="L8" t="str">
+            <v>4.6 out of 5</v>
+          </cell>
           <cell r="M8">
             <v>4.5999999999999996</v>
           </cell>
+          <cell r="N8" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="9">
+          <cell r="A9" t="str">
+            <v>Desk Foldable Fan Adjustable Fan Strong Wind 3 Gear Usb</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Cleaning &amp; Appliances</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>KSh 988</v>
+          </cell>
+          <cell r="D9">
+            <v>988</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>KSh 1,580</v>
+          </cell>
+          <cell r="F9">
+            <v>1580</v>
+          </cell>
+          <cell r="G9">
+            <v>592</v>
+          </cell>
           <cell r="H9">
             <v>0.37</v>
           </cell>
+          <cell r="I9" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J9">
+            <v>-2</v>
+          </cell>
           <cell r="K9">
             <v>2</v>
           </cell>
+          <cell r="L9" t="str">
+            <v>4 out of 5</v>
+          </cell>
           <cell r="M9">
             <v>4</v>
           </cell>
+          <cell r="N9" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="10">
+          <cell r="A10" t="str">
+            <v>LASA FOLDING TABLE SERVING STAND</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>KSh 1,274</v>
+          </cell>
+          <cell r="D10">
+            <v>1274</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>KSh 2,800</v>
+          </cell>
+          <cell r="F10">
+            <v>2800</v>
+          </cell>
+          <cell r="G10">
+            <v>1526</v>
+          </cell>
           <cell r="H10">
             <v>0.55000000000000004</v>
           </cell>
+          <cell r="I10" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J10">
+            <v>-5</v>
+          </cell>
           <cell r="K10">
             <v>5</v>
           </cell>
+          <cell r="L10" t="str">
+            <v>4.8 out of 5</v>
+          </cell>
           <cell r="M10">
             <v>4.8</v>
           </cell>
+          <cell r="N10" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="11">
+          <cell r="A11" t="str">
+            <v>13 In 1 Home Repair Tools Box Kit Set</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>KSh 1,600</v>
+          </cell>
+          <cell r="D11">
+            <v>1600</v>
+          </cell>
+          <cell r="E11" t="str">
+            <v>KSh 2,929</v>
+          </cell>
+          <cell r="F11">
+            <v>2929</v>
+          </cell>
+          <cell r="G11">
+            <v>1329</v>
+          </cell>
           <cell r="H11">
             <v>0.45</v>
           </cell>
+          <cell r="I11" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J11">
+            <v>-5</v>
+          </cell>
           <cell r="K11">
             <v>5</v>
           </cell>
+          <cell r="L11" t="str">
+            <v>3.8 out of 5</v>
+          </cell>
           <cell r="M11">
             <v>3.8</v>
           </cell>
+          <cell r="N11" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="12">
+          <cell r="A12" t="str">
+            <v>Genebre 115 In 1 Screwdriver Repairing Tool Set For IPhone Cellphone Hand Tool</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>Tools &amp; Hardware</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>KSh 799</v>
+          </cell>
+          <cell r="D12">
+            <v>799</v>
+          </cell>
+          <cell r="E12" t="str">
+            <v>KSh 999</v>
+          </cell>
+          <cell r="F12">
+            <v>999</v>
+          </cell>
+          <cell r="G12">
+            <v>200</v>
+          </cell>
           <cell r="H12">
             <v>0.2</v>
           </cell>
+          <cell r="I12" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J12">
+            <v>-12</v>
+          </cell>
           <cell r="K12">
             <v>12</v>
           </cell>
+          <cell r="L12" t="str">
+            <v>4.1 out of 5</v>
+          </cell>
           <cell r="M12">
             <v>4.0999999999999996</v>
           </cell>
+          <cell r="N12" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="13">
+          <cell r="A13" t="str">
+            <v>100 Pcs Crochet Hook Tool Set Knitting Hook Set With Box</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>KSh 990</v>
+          </cell>
+          <cell r="D13">
+            <v>990</v>
+          </cell>
+          <cell r="E13" t="str">
+            <v>KSh 1,500</v>
+          </cell>
+          <cell r="F13">
+            <v>1500</v>
+          </cell>
+          <cell r="G13">
+            <v>510</v>
+          </cell>
           <cell r="H13">
             <v>0.34</v>
           </cell>
+          <cell r="I13" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J13">
+            <v>-39</v>
+          </cell>
           <cell r="K13">
             <v>39</v>
           </cell>
+          <cell r="L13" t="str">
+            <v>4.7 out of 5</v>
+          </cell>
           <cell r="M13">
             <v>4.7</v>
           </cell>
+          <cell r="N13" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="14">
+          <cell r="A14" t="str">
+            <v>40cm Gold DIY Acrylic Wall Sticker Clock</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>KSh 552</v>
+          </cell>
+          <cell r="D14">
+            <v>552</v>
+          </cell>
+          <cell r="E14" t="str">
+            <v>KSh 1,035</v>
+          </cell>
+          <cell r="F14">
+            <v>1035</v>
+          </cell>
+          <cell r="G14">
+            <v>483</v>
+          </cell>
           <cell r="H14">
             <v>0.47</v>
           </cell>
+          <cell r="I14" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J14">
+            <v>-12</v>
+          </cell>
           <cell r="K14">
             <v>12</v>
           </cell>
+          <cell r="L14" t="str">
+            <v>4.8 out of 5</v>
+          </cell>
           <cell r="M14">
             <v>4.8</v>
           </cell>
+          <cell r="N14" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="15">
+          <cell r="A15" t="str">
+            <v>LASA Digital Thermometer And Hydrometer</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>KSh 501</v>
+          </cell>
+          <cell r="D15">
+            <v>501</v>
+          </cell>
+          <cell r="E15" t="str">
+            <v>KSh 860</v>
+          </cell>
+          <cell r="F15">
+            <v>860</v>
+          </cell>
+          <cell r="G15">
+            <v>359</v>
+          </cell>
           <cell r="H15">
             <v>0.42</v>
           </cell>
+          <cell r="I15" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J15">
+            <v>-6</v>
+          </cell>
           <cell r="K15">
             <v>6</v>
           </cell>
+          <cell r="L15" t="str">
+            <v>4.5 out of 5</v>
+          </cell>
           <cell r="M15">
             <v>4.5</v>
           </cell>
+          <cell r="N15" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="16">
+          <cell r="A16" t="str">
+            <v>Multifunction Laser Level With Adjustment Tripod</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>KSh 1,680</v>
+          </cell>
+          <cell r="D16">
+            <v>1680</v>
+          </cell>
+          <cell r="E16" t="str">
+            <v>KSh 2,499</v>
+          </cell>
+          <cell r="F16">
+            <v>2499</v>
+          </cell>
+          <cell r="G16">
+            <v>819</v>
+          </cell>
           <cell r="H16">
             <v>0.33</v>
           </cell>
+          <cell r="I16" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J16">
+            <v>-9</v>
+          </cell>
           <cell r="K16">
             <v>9</v>
           </cell>
+          <cell r="L16" t="str">
+            <v>4.2 out of 5</v>
+          </cell>
           <cell r="M16">
             <v>4.2</v>
           </cell>
+          <cell r="N16" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="17">
+          <cell r="A17" t="str">
+            <v>Anti-Skid Absorbent Insulation Coaster  For Home Office</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>KSh 332</v>
+          </cell>
+          <cell r="D17">
+            <v>332</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>KSh 684</v>
+          </cell>
+          <cell r="F17">
+            <v>684</v>
+          </cell>
+          <cell r="G17">
+            <v>352</v>
+          </cell>
           <cell r="H17">
             <v>0.51</v>
           </cell>
+          <cell r="I17" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J17">
+            <v>-2</v>
+          </cell>
           <cell r="K17">
             <v>2</v>
           </cell>
+          <cell r="L17" t="str">
+            <v>5 out of 5</v>
+          </cell>
           <cell r="M17">
             <v>5</v>
           </cell>
+          <cell r="N17" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="18">
+          <cell r="A18" t="str">
+            <v>Peacock  Throw Pillow Cushion Case For Home Car</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>KSh 195</v>
+          </cell>
+          <cell r="D18">
+            <v>195</v>
+          </cell>
+          <cell r="E18" t="str">
+            <v>KSh 360</v>
+          </cell>
+          <cell r="F18">
+            <v>360</v>
+          </cell>
+          <cell r="G18">
+            <v>165</v>
+          </cell>
           <cell r="H18">
             <v>0.46</v>
           </cell>
+          <cell r="I18" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J18">
+            <v>-2</v>
+          </cell>
           <cell r="K18">
             <v>2</v>
           </cell>
+          <cell r="L18" t="str">
+            <v>5 out of 5</v>
+          </cell>
           <cell r="M18">
             <v>5</v>
           </cell>
+          <cell r="N18" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="19">
+          <cell r="A19" t="str">
+            <v>LASA Aluminum Folding Truck Hand Cart - 68kg Max</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>KSh 2,025</v>
+          </cell>
+          <cell r="D19">
+            <v>2025</v>
+          </cell>
+          <cell r="E19" t="str">
+            <v>KSh 3,971</v>
+          </cell>
+          <cell r="F19">
+            <v>3971</v>
+          </cell>
+          <cell r="G19">
+            <v>1946</v>
+          </cell>
           <cell r="H19">
             <v>0.49</v>
           </cell>
+          <cell r="I19" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J19">
+            <v>-3</v>
+          </cell>
           <cell r="K19">
             <v>3</v>
           </cell>
+          <cell r="L19" t="str">
+            <v>5 out of 5</v>
+          </cell>
           <cell r="M19">
             <v>5</v>
           </cell>
+          <cell r="N19" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="20">
+          <cell r="A20" t="str">
+            <v>LED Wall Digital Alarm Clock Study Home 12 / 24H Clock Calendar</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>KSh 2,999</v>
+          </cell>
+          <cell r="D20">
+            <v>2999</v>
+          </cell>
+          <cell r="E20" t="str">
+            <v>KSh 3,699</v>
+          </cell>
+          <cell r="F20">
+            <v>3699</v>
+          </cell>
+          <cell r="G20">
+            <v>700</v>
+          </cell>
           <cell r="H20">
             <v>0.19</v>
           </cell>
+          <cell r="I20" t="str">
+            <v>Low</v>
+          </cell>
+          <cell r="J20">
+            <v>-5</v>
+          </cell>
           <cell r="K20">
             <v>5</v>
           </cell>
+          <cell r="L20" t="str">
+            <v>4.6 out of 5</v>
+          </cell>
           <cell r="M20">
             <v>4.5999999999999996</v>
           </cell>
+          <cell r="N20" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="21">
+          <cell r="A21" t="str">
+            <v>3D Waterproof EVA Plastic Shower Curtain 1.8*2Mtrs</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>KSh 998</v>
+          </cell>
+          <cell r="D21">
+            <v>998</v>
+          </cell>
+          <cell r="E21" t="str">
+            <v>KSh 1,966</v>
+          </cell>
+          <cell r="F21">
+            <v>1966</v>
+          </cell>
+          <cell r="G21">
+            <v>968</v>
+          </cell>
           <cell r="H21">
             <v>0.49</v>
           </cell>
+          <cell r="I21" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J21">
+            <v>-44</v>
+          </cell>
           <cell r="K21">
             <v>44</v>
           </cell>
+          <cell r="L21" t="str">
+            <v>4.6 out of 5</v>
+          </cell>
           <cell r="M21">
             <v>4.5999999999999996</v>
           </cell>
+          <cell r="N21" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="22">
+          <cell r="A22" t="str">
+            <v>3PCS Single Head Knitting Crochet Sweater Needle Set</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>Craft &amp; DIY</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>KSh 38</v>
+          </cell>
+          <cell r="D22">
+            <v>38</v>
+          </cell>
+          <cell r="E22" t="str">
+            <v>KSh 80</v>
+          </cell>
+          <cell r="F22">
+            <v>80</v>
+          </cell>
+          <cell r="G22">
+            <v>42</v>
+          </cell>
           <cell r="H22">
             <v>0.53</v>
           </cell>
+          <cell r="I22" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J22">
+            <v>-13</v>
+          </cell>
           <cell r="K22">
             <v>13</v>
           </cell>
+          <cell r="L22" t="str">
+            <v>3.3 out of 5</v>
+          </cell>
           <cell r="M22">
             <v>3.3</v>
           </cell>
+          <cell r="N22" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="23">
+          <cell r="A23" t="str">
+            <v>4pcs Bathroom/Kitchen Towel Rack,Roll Paper Holder,Towel Bars,Hook</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>KSh 1,860</v>
+          </cell>
+          <cell r="D23">
+            <v>1860</v>
+          </cell>
+          <cell r="E23" t="str">
+            <v>KSh 3,220</v>
+          </cell>
+          <cell r="F23">
+            <v>3220</v>
+          </cell>
+          <cell r="G23">
+            <v>1360</v>
+          </cell>
           <cell r="H23">
             <v>0.42</v>
           </cell>
+          <cell r="I23" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K23" t="str">
             <v/>
           </cell>
           <cell r="M23" t="str">
+            <v/>
+          </cell>
+          <cell r="N23" t="str">
             <v/>
           </cell>
         </row>
         <row r="24">
+          <cell r="A24" t="str">
+            <v>LED Romantic Spaceship Starry Sky Projector,Children's Bedroom Night Light-Blue</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>KSh 880</v>
+          </cell>
+          <cell r="D24">
+            <v>880</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>KSh 1,350</v>
+          </cell>
+          <cell r="F24">
+            <v>1350</v>
+          </cell>
+          <cell r="G24">
+            <v>470</v>
+          </cell>
           <cell r="H24">
             <v>0.35</v>
           </cell>
+          <cell r="I24" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J24">
+            <v>-6</v>
+          </cell>
           <cell r="K24">
             <v>6</v>
           </cell>
+          <cell r="L24" t="str">
+            <v>4 out of 5</v>
+          </cell>
           <cell r="M24">
             <v>4</v>
           </cell>
+          <cell r="N24" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="25">
+          <cell r="A25" t="str">
+            <v>Foldable Overbed Table/Desk</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>KSh 1,650</v>
+          </cell>
+          <cell r="D25">
+            <v>1650</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>KSh 2,150</v>
+          </cell>
+          <cell r="F25">
+            <v>2150</v>
+          </cell>
+          <cell r="G25">
+            <v>500</v>
+          </cell>
           <cell r="H25">
             <v>0.23</v>
           </cell>
+          <cell r="I25" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J25">
+            <v>-14</v>
+          </cell>
           <cell r="K25">
             <v>14</v>
           </cell>
+          <cell r="L25" t="str">
+            <v>4.4 out of 5</v>
+          </cell>
           <cell r="M25">
             <v>4.4000000000000004</v>
           </cell>
+          <cell r="N25" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="26">
+          <cell r="A26" t="str">
+            <v>LASA 3 Tier Bamboo Shoe Bench Storage Shelf</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>KSh 2,048</v>
+          </cell>
+          <cell r="D26">
+            <v>2048</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>KSh 4,500</v>
+          </cell>
+          <cell r="F26">
+            <v>4500</v>
+          </cell>
+          <cell r="G26">
+            <v>2452</v>
+          </cell>
           <cell r="H26">
             <v>0.54</v>
           </cell>
+          <cell r="I26" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J26">
+            <v>-7</v>
+          </cell>
           <cell r="K26">
             <v>7</v>
           </cell>
+          <cell r="L26" t="str">
+            <v>4.3 out of 5</v>
+          </cell>
           <cell r="M26">
             <v>4.3</v>
           </cell>
+          <cell r="N26" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="27">
+          <cell r="A27" t="str">
+            <v>Electronic Digital Display Vernier Caliper</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>KSh 420</v>
+          </cell>
+          <cell r="D27">
+            <v>420</v>
+          </cell>
+          <cell r="E27" t="str">
+            <v>KSh 647</v>
+          </cell>
+          <cell r="F27">
+            <v>647</v>
+          </cell>
+          <cell r="G27">
+            <v>227</v>
+          </cell>
           <cell r="H27">
             <v>0.35</v>
           </cell>
+          <cell r="I27" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J27">
+            <v>-49</v>
+          </cell>
           <cell r="K27">
             <v>49</v>
           </cell>
+          <cell r="L27" t="str">
+            <v>4.6 out of 5</v>
+          </cell>
           <cell r="M27">
             <v>4.5999999999999996</v>
           </cell>
+          <cell r="N27" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="28">
+          <cell r="A28" t="str">
+            <v>Portable Wardrobe Nonwoven With 3 Hanging Rods And 6 Storage Shelves</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>KSh 2,880</v>
+          </cell>
+          <cell r="D28">
+            <v>2880</v>
+          </cell>
+          <cell r="E28" t="str">
+            <v>KSh 3,520</v>
+          </cell>
+          <cell r="F28">
+            <v>3520</v>
+          </cell>
+          <cell r="G28">
+            <v>640</v>
+          </cell>
           <cell r="H28">
             <v>0.18</v>
           </cell>
+          <cell r="I28" t="str">
+            <v>Low</v>
+          </cell>
+          <cell r="J28">
+            <v>-12</v>
+          </cell>
           <cell r="K28">
             <v>12</v>
           </cell>
+          <cell r="L28" t="str">
+            <v>3.8 out of 5</v>
+          </cell>
           <cell r="M28">
             <v>3.8</v>
           </cell>
+          <cell r="N28" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="29">
+          <cell r="A29" t="str">
+            <v>12 Litre Black Insulated Lunch Box</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>KSh 1,350</v>
+          </cell>
+          <cell r="D29">
+            <v>1350</v>
+          </cell>
+          <cell r="E29" t="str">
+            <v>KSh 1,990</v>
+          </cell>
+          <cell r="F29">
+            <v>1990</v>
+          </cell>
+          <cell r="G29">
+            <v>640</v>
+          </cell>
           <cell r="H29">
             <v>0.32</v>
           </cell>
+          <cell r="I29" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J29">
+            <v>-13</v>
+          </cell>
           <cell r="K29">
             <v>13</v>
           </cell>
+          <cell r="L29" t="str">
+            <v>3.8 out of 5</v>
+          </cell>
           <cell r="M29">
             <v>3.8</v>
           </cell>
+          <cell r="N29" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="30">
+          <cell r="A30" t="str">
+            <v>52 Pieces Cake Decorating Tool Set Gift Kit Baking Supplies</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>KSh 1,758</v>
+          </cell>
+          <cell r="D30">
+            <v>1758</v>
+          </cell>
+          <cell r="E30" t="str">
+            <v>KSh 2,499</v>
+          </cell>
+          <cell r="F30">
+            <v>2499</v>
+          </cell>
+          <cell r="G30">
+            <v>741</v>
+          </cell>
           <cell r="H30">
             <v>0.3</v>
           </cell>
+          <cell r="I30" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J30">
+            <v>-20</v>
+          </cell>
           <cell r="K30">
             <v>20</v>
           </cell>
+          <cell r="L30" t="str">
+            <v>4.1 out of 5</v>
+          </cell>
           <cell r="M30">
             <v>4.0999999999999996</v>
           </cell>
+          <cell r="N30" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="31">
+          <cell r="A31" t="str">
+            <v>MultiFunctional Storage Rack Multi-layer Bookshelf</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>KSh 2,200</v>
+          </cell>
+          <cell r="D31">
+            <v>2200</v>
+          </cell>
+          <cell r="E31" t="str">
+            <v>KSh 4,080</v>
+          </cell>
+          <cell r="F31">
+            <v>4080</v>
+          </cell>
+          <cell r="G31">
+            <v>1880</v>
+          </cell>
           <cell r="H31">
             <v>0.46</v>
           </cell>
+          <cell r="I31" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K31" t="str">
             <v/>
           </cell>
           <cell r="M31" t="str">
+            <v/>
+          </cell>
+          <cell r="N31" t="str">
             <v/>
           </cell>
         </row>
         <row r="32">
+          <cell r="A32" t="str">
+            <v>Exfoliate And Exfoliate Face Towel - Black</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>KSh 185</v>
+          </cell>
+          <cell r="D32">
+            <v>185</v>
+          </cell>
+          <cell r="E32" t="str">
+            <v>KSh 382</v>
+          </cell>
+          <cell r="F32">
+            <v>382</v>
+          </cell>
+          <cell r="G32">
+            <v>197</v>
+          </cell>
           <cell r="H32">
             <v>0.52</v>
           </cell>
+          <cell r="I32" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J32">
+            <v>-9</v>
+          </cell>
           <cell r="K32">
             <v>9</v>
           </cell>
+          <cell r="L32" t="str">
+            <v>4.3 out of 5</v>
+          </cell>
           <cell r="M32">
             <v>4.3</v>
           </cell>
+          <cell r="N32" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="33">
+          <cell r="A33" t="str">
+            <v>12 Litre Insulated Lunch Box Grey</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>KSh 980</v>
+          </cell>
+          <cell r="D33">
+            <v>980</v>
+          </cell>
+          <cell r="E33" t="str">
+            <v>KSh 1,490</v>
+          </cell>
+          <cell r="F33">
+            <v>1490</v>
+          </cell>
+          <cell r="G33">
+            <v>510</v>
+          </cell>
           <cell r="H33">
             <v>0.34</v>
           </cell>
+          <cell r="I33" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J33">
+            <v>-12</v>
+          </cell>
           <cell r="K33">
             <v>12</v>
           </cell>
+          <cell r="L33" t="str">
+            <v>4.7 out of 5</v>
+          </cell>
           <cell r="M33">
             <v>4.7</v>
           </cell>
+          <cell r="N33" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="34">
+          <cell r="A34" t="str">
+            <v>LED Eye Protection  Desk Lamp , Study, Reading, USB Fan - Double Pen Holder</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>Cleaning &amp; Appliances</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>KSh 1,820</v>
+          </cell>
+          <cell r="D34">
+            <v>1820</v>
+          </cell>
+          <cell r="E34" t="str">
+            <v>KSh 3,490</v>
+          </cell>
+          <cell r="F34">
+            <v>3490</v>
+          </cell>
+          <cell r="G34">
+            <v>1670</v>
+          </cell>
           <cell r="H34">
             <v>0.48</v>
           </cell>
+          <cell r="I34" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J34">
+            <v>-9</v>
+          </cell>
           <cell r="K34">
             <v>9</v>
           </cell>
+          <cell r="L34" t="str">
+            <v>4.3 out of 5</v>
+          </cell>
           <cell r="M34">
             <v>4.3</v>
           </cell>
+          <cell r="N34" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="35">
+          <cell r="A35" t="str">
+            <v>53Pcs/Set Yarn Knitting Crochet Hooks With Bag - Fortune Cat</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>KSh 1,940</v>
+          </cell>
+          <cell r="D35">
+            <v>1940</v>
+          </cell>
+          <cell r="E35" t="str">
+            <v>KSh 2,650</v>
+          </cell>
+          <cell r="F35">
+            <v>2650</v>
+          </cell>
+          <cell r="G35">
+            <v>710</v>
+          </cell>
           <cell r="H35">
             <v>0.27</v>
           </cell>
+          <cell r="I35" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J35">
+            <v>-20</v>
+          </cell>
           <cell r="K35">
             <v>20</v>
           </cell>
+          <cell r="L35" t="str">
+            <v>4.7 out of 5</v>
+          </cell>
           <cell r="M35">
             <v>4.7</v>
           </cell>
+          <cell r="N35" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="36">
+          <cell r="A36" t="str">
+            <v>53 Pieces/Set Yarn Knitting Crochet Hooks With Bag - Pansies</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>KSh 1,980</v>
+          </cell>
+          <cell r="D36">
+            <v>1980</v>
+          </cell>
+          <cell r="E36" t="str">
+            <v>KSh 2,699</v>
+          </cell>
+          <cell r="F36">
+            <v>2699</v>
+          </cell>
+          <cell r="G36">
+            <v>719</v>
+          </cell>
           <cell r="H36">
             <v>0.27</v>
           </cell>
+          <cell r="I36" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J36">
+            <v>-32</v>
+          </cell>
           <cell r="K36">
             <v>32</v>
           </cell>
+          <cell r="L36" t="str">
+            <v>4.5 out of 5</v>
+          </cell>
           <cell r="M36">
             <v>4.5</v>
           </cell>
+          <cell r="N36" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="37">
+          <cell r="A37" t="str">
+            <v>DIY File Folder, Office Drawer File Holder, Pen Holder, Desktop Storage Rack</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>KSh 1,620</v>
+          </cell>
+          <cell r="D37">
+            <v>1620</v>
+          </cell>
+          <cell r="E37" t="str">
+            <v>KSh 2,690</v>
+          </cell>
+          <cell r="F37">
+            <v>2690</v>
+          </cell>
+          <cell r="G37">
+            <v>1070</v>
+          </cell>
           <cell r="H37">
             <v>0.4</v>
           </cell>
+          <cell r="I37" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J37">
+            <v>-1</v>
+          </cell>
           <cell r="K37">
             <v>1</v>
           </cell>
+          <cell r="L37" t="str">
+            <v>5 out of 5</v>
+          </cell>
           <cell r="M37">
             <v>5</v>
           </cell>
+          <cell r="N37" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="38">
+          <cell r="A38" t="str">
+            <v>Classic Black Cat Cotton Hemp Pillow Case For Home Car</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>KSh 171</v>
+          </cell>
+          <cell r="D38">
+            <v>171</v>
+          </cell>
+          <cell r="E38" t="str">
+            <v>KSh 360</v>
+          </cell>
+          <cell r="F38">
+            <v>360</v>
+          </cell>
+          <cell r="G38">
+            <v>189</v>
+          </cell>
           <cell r="H38">
             <v>0.53</v>
           </cell>
+          <cell r="I38" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J38">
+            <v>-2</v>
+          </cell>
           <cell r="K38">
             <v>2</v>
           </cell>
+          <cell r="L38" t="str">
+            <v>5 out of 5</v>
+          </cell>
           <cell r="M38">
             <v>5</v>
           </cell>
+          <cell r="N38" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="39">
+          <cell r="A39" t="str">
+            <v>Punch-free Great Load Bearing Bathroom Storage Rack Wall Shelf-White</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>KSh 389</v>
+          </cell>
+          <cell r="D39">
+            <v>389</v>
+          </cell>
+          <cell r="E39" t="str">
+            <v>KSh 656</v>
+          </cell>
+          <cell r="F39">
+            <v>656</v>
+          </cell>
+          <cell r="G39">
+            <v>267</v>
+          </cell>
           <cell r="H39">
             <v>0.41</v>
           </cell>
+          <cell r="I39" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J39">
+            <v>-36</v>
+          </cell>
           <cell r="K39">
             <v>36</v>
           </cell>
+          <cell r="L39" t="str">
+            <v>4.3 out of 5</v>
+          </cell>
           <cell r="M39">
             <v>4.3</v>
           </cell>
+          <cell r="N39" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="40">
+          <cell r="A40" t="str">
+            <v>1/2/3 Seater Elastic Sofa Cover,Living Room/Home Decor Chair Cover-Grey</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>KSh 1,800</v>
+          </cell>
+          <cell r="D40">
+            <v>1800</v>
+          </cell>
+          <cell r="E40" t="str">
+            <v>KSh 2,700</v>
+          </cell>
+          <cell r="F40">
+            <v>2700</v>
+          </cell>
+          <cell r="G40">
+            <v>900</v>
+          </cell>
           <cell r="H40">
             <v>0.38</v>
           </cell>
+          <cell r="I40" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J40">
+            <v>-2</v>
+          </cell>
           <cell r="K40">
             <v>2</v>
           </cell>
+          <cell r="L40" t="str">
+            <v>4.5 out of 5</v>
+          </cell>
           <cell r="M40">
             <v>4.5</v>
           </cell>
+          <cell r="N40" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="41">
+          <cell r="A41" t="str">
+            <v>LASA Stainless Steel Double Wall Mount Soap Dispenser - 500ml</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C41" t="str">
+            <v>KSh 2,750</v>
+          </cell>
+          <cell r="D41">
+            <v>2750</v>
+          </cell>
+          <cell r="E41" t="str">
+            <v>KSh 4,471</v>
+          </cell>
+          <cell r="F41">
+            <v>4471</v>
+          </cell>
+          <cell r="G41">
+            <v>1721</v>
+          </cell>
           <cell r="H41">
             <v>0.38</v>
           </cell>
+          <cell r="I41" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K41" t="str">
             <v/>
           </cell>
           <cell r="M41" t="str">
+            <v/>
+          </cell>
+          <cell r="N41" t="str">
             <v/>
           </cell>
         </row>
         <row r="42">
+          <cell r="A42" t="str">
+            <v>4M Float Switch Water Level Controller -Water Tank</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>KSh 475</v>
+          </cell>
+          <cell r="D42">
+            <v>475</v>
+          </cell>
+          <cell r="E42" t="str">
+            <v>KSh 931</v>
+          </cell>
+          <cell r="F42">
+            <v>931</v>
+          </cell>
+          <cell r="G42">
+            <v>456</v>
+          </cell>
           <cell r="H42">
             <v>0.49</v>
           </cell>
+          <cell r="I42" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K42" t="str">
             <v/>
           </cell>
           <cell r="M42" t="str">
+            <v/>
+          </cell>
+          <cell r="N42" t="str">
             <v/>
           </cell>
         </row>
         <row r="43">
+          <cell r="A43" t="str">
+            <v>Modern Sofa Throw Pillow Cover-45x45cm-Blue&amp;Red</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>KSh 238</v>
+          </cell>
+          <cell r="D43">
+            <v>238</v>
+          </cell>
+          <cell r="E43" t="str">
+            <v>KSh 476</v>
+          </cell>
+          <cell r="F43">
+            <v>476</v>
+          </cell>
+          <cell r="G43">
+            <v>238</v>
+          </cell>
           <cell r="H43">
             <v>0.5</v>
           </cell>
+          <cell r="I43" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K43" t="str">
             <v/>
           </cell>
           <cell r="M43" t="str">
+            <v/>
+          </cell>
+          <cell r="N43" t="str">
             <v/>
           </cell>
         </row>
         <row r="44">
+          <cell r="A44" t="str">
+            <v>Balloon Insert, Birthday Party Balloon Set, PU Leather</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>KSh 610</v>
+          </cell>
+          <cell r="D44">
+            <v>610</v>
+          </cell>
+          <cell r="E44" t="str">
+            <v>KSh 1,060</v>
+          </cell>
+          <cell r="F44">
+            <v>1060</v>
+          </cell>
+          <cell r="G44">
+            <v>450</v>
+          </cell>
           <cell r="H44">
             <v>0.42</v>
           </cell>
+          <cell r="I44" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K44" t="str">
             <v/>
           </cell>
           <cell r="M44" t="str">
+            <v/>
+          </cell>
+          <cell r="N44" t="str">
             <v/>
           </cell>
         </row>
         <row r="45">
+          <cell r="A45" t="str">
+            <v>Shower Cap Wide Elastic Band Cover Reusable Bashroom Cap</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C45" t="str">
+            <v>KSh 2,132</v>
+          </cell>
+          <cell r="D45">
+            <v>2132</v>
+          </cell>
+          <cell r="E45" t="str">
+            <v>KSh 2,169</v>
+          </cell>
+          <cell r="F45">
+            <v>2169</v>
+          </cell>
+          <cell r="G45">
+            <v>37</v>
+          </cell>
           <cell r="H45">
             <v>0.02</v>
           </cell>
+          <cell r="I45" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K45" t="str">
             <v/>
           </cell>
           <cell r="M45" t="str">
+            <v/>
+          </cell>
+          <cell r="N45" t="str">
             <v/>
           </cell>
         </row>
         <row r="46">
+          <cell r="A46" t="str">
+            <v>Christmas Elk Fence Yard Lawn Decorations Cute For Holidays</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C46" t="str">
+            <v>KSh 999</v>
+          </cell>
+          <cell r="D46">
+            <v>999</v>
+          </cell>
+          <cell r="E46" t="str">
+            <v>KSh 2,000</v>
+          </cell>
+          <cell r="F46">
+            <v>2000</v>
+          </cell>
+          <cell r="G46">
+            <v>1001</v>
+          </cell>
           <cell r="H46">
             <v>0.5</v>
           </cell>
+          <cell r="I46" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K46" t="str">
             <v/>
           </cell>
           <cell r="M46" t="str">
+            <v/>
+          </cell>
+          <cell r="N46" t="str">
             <v/>
           </cell>
         </row>
         <row r="47">
+          <cell r="A47" t="str">
+            <v>60W Hot Melt Glue Sprayer - Efficient And Stable Glue Dispensing</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C47" t="str">
+            <v>KSh 1,190</v>
+          </cell>
+          <cell r="D47">
+            <v>1190</v>
+          </cell>
+          <cell r="E47" t="str">
+            <v>KSh 1,785</v>
+          </cell>
+          <cell r="F47">
+            <v>1785</v>
+          </cell>
+          <cell r="G47">
+            <v>595</v>
+          </cell>
           <cell r="H47">
             <v>0.33</v>
           </cell>
+          <cell r="I47" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K47" t="str">
             <v/>
           </cell>
           <cell r="M47" t="str">
+            <v/>
+          </cell>
+          <cell r="N47" t="str">
             <v/>
           </cell>
         </row>
         <row r="48">
+          <cell r="A48" t="str">
+            <v>Car Phone Charging Stand</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C48" t="str">
+            <v>KSh 671</v>
+          </cell>
+          <cell r="D48">
+            <v>671</v>
+          </cell>
+          <cell r="E48" t="str">
+            <v>KSh 1,316</v>
+          </cell>
+          <cell r="F48">
+            <v>1316</v>
+          </cell>
+          <cell r="G48">
+            <v>645</v>
+          </cell>
           <cell r="H48">
             <v>0.49</v>
           </cell>
+          <cell r="I48" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K48" t="str">
             <v/>
           </cell>
           <cell r="M48" t="str">
+            <v/>
+          </cell>
+          <cell r="N48" t="str">
             <v/>
           </cell>
         </row>
         <row r="49">
+          <cell r="A49" t="str">
+            <v>2pcs Solar Street Light Flood Light Outdoor</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C49" t="str">
+            <v>KSh 1,200</v>
+          </cell>
+          <cell r="D49">
+            <v>1200</v>
+          </cell>
+          <cell r="E49" t="str">
+            <v>KSh 1,950</v>
+          </cell>
+          <cell r="F49">
+            <v>1950</v>
+          </cell>
+          <cell r="G49">
+            <v>750</v>
+          </cell>
           <cell r="H49">
             <v>0.38</v>
           </cell>
+          <cell r="I49" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K49" t="str">
             <v/>
           </cell>
           <cell r="M49" t="str">
+            <v/>
+          </cell>
+          <cell r="N49" t="str">
             <v/>
           </cell>
         </row>
         <row r="50">
+          <cell r="A50" t="str">
+            <v>Creative Owl Shape Keychain Black</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C50" t="str">
+            <v>KSh 199</v>
+          </cell>
+          <cell r="D50">
+            <v>199</v>
+          </cell>
+          <cell r="E50" t="str">
+            <v>KSh 504</v>
+          </cell>
+          <cell r="F50">
+            <v>504</v>
+          </cell>
+          <cell r="G50">
+            <v>305</v>
+          </cell>
           <cell r="H50">
             <v>0.61</v>
           </cell>
+          <cell r="I50" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K50" t="str">
             <v/>
           </cell>
           <cell r="M50" t="str">
+            <v/>
+          </cell>
+          <cell r="N50" t="str">
             <v/>
           </cell>
         </row>
         <row r="51">
+          <cell r="A51" t="str">
+            <v>Brush &amp; Paintbrush Cleaning Tool Pink</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C51" t="str">
+            <v>KSh 299</v>
+          </cell>
+          <cell r="D51">
+            <v>299</v>
+          </cell>
+          <cell r="E51" t="str">
+            <v>KSh 600</v>
+          </cell>
+          <cell r="F51">
+            <v>600</v>
+          </cell>
+          <cell r="G51">
+            <v>301</v>
+          </cell>
           <cell r="H51">
             <v>0.5</v>
           </cell>
+          <cell r="I51" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K51" t="str">
             <v/>
           </cell>
           <cell r="M51" t="str">
+            <v/>
+          </cell>
+          <cell r="N51" t="str">
             <v/>
           </cell>
         </row>
         <row r="52">
+          <cell r="A52" t="str">
+            <v>Pen Grips For Kids Pen Grip Posture Correction Tool For Kids</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C52" t="str">
+            <v>KSh 1,660</v>
+          </cell>
+          <cell r="D52">
+            <v>1660</v>
+          </cell>
+          <cell r="E52" t="str">
+            <v>KSh 1,699</v>
+          </cell>
+          <cell r="F52">
+            <v>1699</v>
+          </cell>
+          <cell r="G52">
+            <v>39</v>
+          </cell>
           <cell r="H52">
             <v>0.02</v>
           </cell>
+          <cell r="I52" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K52" t="str">
             <v/>
           </cell>
           <cell r="M52" t="str">
+            <v/>
+          </cell>
+          <cell r="N52" t="str">
             <v/>
           </cell>
         </row>
         <row r="53">
+          <cell r="A53" t="str">
+            <v>Pilates Cloth Bag Waterproof Durable High Capacity Purple</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C53" t="str">
+            <v>KSh 299</v>
+          </cell>
+          <cell r="D53">
+            <v>299</v>
+          </cell>
+          <cell r="E53" t="str">
+            <v>KSh 384</v>
+          </cell>
+          <cell r="F53">
+            <v>384</v>
+          </cell>
+          <cell r="G53">
+            <v>85</v>
+          </cell>
           <cell r="H53">
             <v>0.22</v>
           </cell>
+          <cell r="I53" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K53" t="str">
             <v/>
           </cell>
           <cell r="M53" t="str">
+            <v/>
+          </cell>
+          <cell r="N53" t="str">
             <v/>
           </cell>
         </row>
         <row r="54">
+          <cell r="A54" t="str">
+            <v>Multi-purpose Rice Drainage Basket And Fruit And Vegetable Drainage Sieve</v>
+          </cell>
+          <cell r="B54" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C54" t="str">
+            <v>KSh 1,459</v>
+          </cell>
+          <cell r="D54">
+            <v>1459</v>
+          </cell>
+          <cell r="E54" t="str">
+            <v>KSh 1,499</v>
+          </cell>
+          <cell r="F54">
+            <v>1499</v>
+          </cell>
+          <cell r="G54">
+            <v>40</v>
+          </cell>
           <cell r="H54">
             <v>0.03</v>
           </cell>
+          <cell r="I54" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K54" t="str">
             <v/>
           </cell>
           <cell r="M54" t="str">
+            <v/>
+          </cell>
+          <cell r="N54" t="str">
             <v/>
           </cell>
         </row>
         <row r="55">
+          <cell r="A55" t="str">
+            <v>Cute Christmas Fence Garden Decorations For Holiday Home</v>
+          </cell>
+          <cell r="B55" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C55" t="str">
+            <v>KSh 799</v>
+          </cell>
+          <cell r="D55">
+            <v>799</v>
+          </cell>
+          <cell r="E55" t="str">
+            <v>KSh 1,343</v>
+          </cell>
+          <cell r="F55">
+            <v>1343</v>
+          </cell>
+          <cell r="G55">
+            <v>544</v>
+          </cell>
           <cell r="H55">
             <v>0.41</v>
           </cell>
+          <cell r="I55" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K55" t="str">
             <v/>
           </cell>
           <cell r="M55" t="str">
+            <v/>
+          </cell>
+          <cell r="N55" t="str">
             <v/>
           </cell>
         </row>
         <row r="56">
+          <cell r="A56" t="str">
+            <v>Simple Metal Dog Art Sculpture Decoration For Home Office</v>
+          </cell>
+          <cell r="B56" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C56" t="str">
+            <v>KSh 499</v>
+          </cell>
+          <cell r="D56">
+            <v>499</v>
+          </cell>
+          <cell r="E56" t="str">
+            <v>KSh 900</v>
+          </cell>
+          <cell r="F56">
+            <v>900</v>
+          </cell>
+          <cell r="G56">
+            <v>401</v>
+          </cell>
           <cell r="H56">
             <v>0.45</v>
           </cell>
+          <cell r="I56" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K56" t="str">
             <v/>
           </cell>
           <cell r="M56" t="str">
+            <v/>
+          </cell>
+          <cell r="N56" t="str">
             <v/>
           </cell>
         </row>
         <row r="57">
+          <cell r="A57" t="str">
+            <v>Christmas Fence Garden Decorations Outdoor For Holiday Home</v>
+          </cell>
+          <cell r="B57" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C57" t="str">
+            <v>KSh 699</v>
+          </cell>
+          <cell r="D57">
+            <v>699</v>
+          </cell>
+          <cell r="E57" t="str">
+            <v>KSh 1,343</v>
+          </cell>
+          <cell r="F57">
+            <v>1343</v>
+          </cell>
+          <cell r="G57">
+            <v>644</v>
+          </cell>
           <cell r="H57">
             <v>0.48</v>
           </cell>
+          <cell r="I57" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K57" t="str">
             <v/>
           </cell>
           <cell r="M57" t="str">
+            <v/>
+          </cell>
+          <cell r="N57" t="str">
             <v/>
           </cell>
         </row>
         <row r="58">
+          <cell r="A58" t="str">
+            <v>Angle Measuring Tool Full Metal Multi Angle Measuring Tool</v>
+          </cell>
+          <cell r="B58" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>KSh 799</v>
+          </cell>
+          <cell r="D58">
+            <v>799</v>
+          </cell>
+          <cell r="E58" t="str">
+            <v>KSh 1,567</v>
+          </cell>
+          <cell r="F58">
+            <v>1567</v>
+          </cell>
+          <cell r="G58">
+            <v>768</v>
+          </cell>
           <cell r="H58">
             <v>0.49</v>
           </cell>
+          <cell r="I58" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K58" t="str">
             <v/>
           </cell>
           <cell r="M58" t="str">
+            <v/>
+          </cell>
+          <cell r="N58" t="str">
             <v/>
           </cell>
         </row>
         <row r="59">
+          <cell r="A59" t="str">
+            <v>12V 19500rpm Handheld Electric Angle Grinder Tool - UK - Yellow/Black</v>
+          </cell>
+          <cell r="B59" t="str">
+            <v>Tools &amp; Hardware</v>
+          </cell>
+          <cell r="C59" t="str">
+            <v>KSh 2,799</v>
+          </cell>
+          <cell r="D59">
+            <v>2799</v>
+          </cell>
+          <cell r="E59" t="str">
+            <v>KSh 3,810</v>
+          </cell>
+          <cell r="F59">
+            <v>3810</v>
+          </cell>
+          <cell r="G59">
+            <v>1011</v>
+          </cell>
           <cell r="H59">
             <v>0.27</v>
           </cell>
+          <cell r="I59" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K59" t="str">
             <v/>
           </cell>
           <cell r="M59" t="str">
+            <v/>
+          </cell>
+          <cell r="N59" t="str">
             <v/>
           </cell>
         </row>
         <row r="60">
+          <cell r="A60" t="str">
+            <v>5 Pieces/set Of Stainless Steel Induction Cooker Pots</v>
+          </cell>
+          <cell r="B60" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C60" t="str">
+            <v>KSh 2,170</v>
+          </cell>
+          <cell r="D60">
+            <v>2170</v>
+          </cell>
+          <cell r="E60" t="str">
+            <v>KSh 2,500</v>
+          </cell>
+          <cell r="F60">
+            <v>2500</v>
+          </cell>
+          <cell r="G60">
+            <v>330</v>
+          </cell>
           <cell r="H60">
             <v>0.13</v>
           </cell>
+          <cell r="I60" t="str">
+            <v>Low</v>
+          </cell>
+          <cell r="J60">
+            <v>-6</v>
+          </cell>
           <cell r="K60">
             <v>6</v>
           </cell>
+          <cell r="L60" t="str">
+            <v>2.5 out of 5</v>
+          </cell>
           <cell r="M60">
             <v>2.5</v>
           </cell>
+          <cell r="N60" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="61">
+          <cell r="A61" t="str">
+            <v>Mythco 120COB Solar Wall Ligt With Motion Sensor And Remote Control 3 Modes</v>
+          </cell>
+          <cell r="B61" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C61" t="str">
+            <v>KSh 458</v>
+          </cell>
+          <cell r="D61">
+            <v>458</v>
+          </cell>
+          <cell r="E61" t="str">
+            <v>KSh 986</v>
+          </cell>
+          <cell r="F61">
+            <v>986</v>
+          </cell>
+          <cell r="G61">
+            <v>528</v>
+          </cell>
           <cell r="H61">
             <v>0.54</v>
           </cell>
+          <cell r="I61" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J61">
+            <v>-10</v>
+          </cell>
           <cell r="K61">
             <v>10</v>
           </cell>
+          <cell r="L61" t="str">
+            <v>3 out of 5</v>
+          </cell>
           <cell r="M61">
             <v>3</v>
           </cell>
+          <cell r="N61" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="62">
+          <cell r="A62" t="str">
+            <v>5-PCS Stainless Steel Cooking Pot Set With Steamed Slices</v>
+          </cell>
+          <cell r="B62" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C62" t="str">
+            <v>KSh 2,115</v>
+          </cell>
+          <cell r="D62">
+            <v>2115</v>
+          </cell>
+          <cell r="E62" t="str">
+            <v>KSh 4,700</v>
+          </cell>
+          <cell r="F62">
+            <v>4700</v>
+          </cell>
+          <cell r="G62">
+            <v>2585</v>
+          </cell>
           <cell r="H62">
             <v>0.55000000000000004</v>
           </cell>
+          <cell r="I62" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J62">
+            <v>-13</v>
+          </cell>
           <cell r="K62">
             <v>13</v>
           </cell>
+          <cell r="L62" t="str">
+            <v>2.1 out of 5</v>
+          </cell>
           <cell r="M62">
             <v>2.1</v>
           </cell>
+          <cell r="N62" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="63">
+          <cell r="A63" t="str">
+            <v>120W Cordless Vacuum Cleaners Handheld Electric Vacuum Cleaner</v>
+          </cell>
+          <cell r="B63" t="str">
+            <v>Cleaning &amp; Appliances</v>
+          </cell>
+          <cell r="C63" t="str">
+            <v>KSh 445</v>
+          </cell>
+          <cell r="D63">
+            <v>445</v>
+          </cell>
+          <cell r="E63" t="str">
+            <v>KSh 873</v>
+          </cell>
+          <cell r="F63">
+            <v>873</v>
+          </cell>
+          <cell r="G63">
+            <v>428</v>
+          </cell>
           <cell r="H63">
             <v>0.49</v>
           </cell>
+          <cell r="I63" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J63">
+            <v>-69</v>
+          </cell>
           <cell r="K63">
             <v>69</v>
           </cell>
+          <cell r="L63" t="str">
+            <v>2.8 out of 5</v>
+          </cell>
           <cell r="M63">
             <v>2.8</v>
           </cell>
+          <cell r="N63" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="64">
+          <cell r="A64" t="str">
+            <v>Intelligent  LED Body Sensor Wireless Lighting Night Light USB</v>
+          </cell>
+          <cell r="B64" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C64" t="str">
+            <v>KSh 325</v>
+          </cell>
+          <cell r="D64">
+            <v>325</v>
+          </cell>
+          <cell r="E64" t="str">
+            <v>KSh 680</v>
+          </cell>
+          <cell r="F64">
+            <v>680</v>
+          </cell>
+          <cell r="G64">
+            <v>355</v>
+          </cell>
           <cell r="H64">
             <v>0.52</v>
           </cell>
+          <cell r="I64" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J64">
+            <v>-15</v>
+          </cell>
           <cell r="K64">
             <v>15</v>
           </cell>
+          <cell r="L64" t="str">
+            <v>2.7 out of 5</v>
+          </cell>
           <cell r="M64">
             <v>2.7</v>
           </cell>
+          <cell r="N64" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="65">
+          <cell r="A65" t="str">
+            <v>VIC Wireless Vacuum Cleaner Dual Use For Home And Car 120W High Power Powerful</v>
+          </cell>
+          <cell r="B65" t="str">
+            <v>Cleaning &amp; Appliances</v>
+          </cell>
+          <cell r="C65" t="str">
+            <v>KSh 1,220</v>
+          </cell>
+          <cell r="D65">
+            <v>1220</v>
+          </cell>
+          <cell r="E65" t="str">
+            <v>KSh 1,555</v>
+          </cell>
+          <cell r="F65">
+            <v>1555</v>
+          </cell>
+          <cell r="G65">
+            <v>335</v>
+          </cell>
           <cell r="H65">
             <v>0.22</v>
           </cell>
+          <cell r="I65" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J65">
+            <v>-16</v>
+          </cell>
           <cell r="K65">
             <v>16</v>
           </cell>
+          <cell r="L65" t="str">
+            <v>2.9 out of 5</v>
+          </cell>
           <cell r="M65">
             <v>2.9</v>
           </cell>
+          <cell r="N65" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="66">
+          <cell r="A66" t="str">
+            <v>Artificial Potted Flowers Room Decorative Flowers (2 Pieces)</v>
+          </cell>
+          <cell r="B66" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C66" t="str">
+            <v>KSh 990</v>
+          </cell>
+          <cell r="D66">
+            <v>990</v>
+          </cell>
+          <cell r="E66" t="str">
+            <v>KSh 1,814</v>
+          </cell>
+          <cell r="F66">
+            <v>1814</v>
+          </cell>
+          <cell r="G66">
+            <v>824</v>
+          </cell>
           <cell r="H66">
             <v>0.45</v>
           </cell>
+          <cell r="I66" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J66">
+            <v>-6</v>
+          </cell>
           <cell r="K66">
             <v>6</v>
           </cell>
+          <cell r="L66" t="str">
+            <v>2.2 out of 5</v>
+          </cell>
           <cell r="M66">
             <v>2.2000000000000002</v>
           </cell>
+          <cell r="N66" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="67">
+          <cell r="A67" t="str">
+            <v>380ML USB Rechargeable Portable Small Blenders And Juicers</v>
+          </cell>
+          <cell r="B67" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>KSh 1,000</v>
+          </cell>
+          <cell r="D67">
+            <v>1000</v>
+          </cell>
+          <cell r="E67" t="str">
+            <v>KSh 2,000</v>
+          </cell>
+          <cell r="F67">
+            <v>2000</v>
+          </cell>
+          <cell r="G67">
+            <v>1000</v>
+          </cell>
           <cell r="H67">
             <v>0.5</v>
           </cell>
+          <cell r="I67" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J67">
+            <v>-7</v>
+          </cell>
           <cell r="K67">
             <v>7</v>
           </cell>
+          <cell r="L67" t="str">
+            <v>2.3 out of 5</v>
+          </cell>
           <cell r="M67">
             <v>2.2999999999999998</v>
           </cell>
+          <cell r="N67" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="68">
+          <cell r="A68" t="str">
+            <v>32PCS Portable Cordless Drill Set With Cyclic Battery Drive -26 Variable Speed</v>
+          </cell>
+          <cell r="B68" t="str">
+            <v>Tools &amp; Hardware</v>
+          </cell>
+          <cell r="C68" t="str">
+            <v>KSh 3,750</v>
+          </cell>
+          <cell r="D68">
+            <v>3750</v>
+          </cell>
+          <cell r="E68" t="str">
+            <v>KSh 6,143</v>
+          </cell>
+          <cell r="F68">
+            <v>6143</v>
+          </cell>
+          <cell r="G68">
+            <v>2393</v>
+          </cell>
           <cell r="H68">
             <v>0.39</v>
           </cell>
+          <cell r="I68" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J68">
+            <v>-5</v>
+          </cell>
           <cell r="K68">
             <v>5</v>
           </cell>
+          <cell r="L68" t="str">
+            <v>3 out of 5</v>
+          </cell>
           <cell r="M68">
             <v>3</v>
           </cell>
+          <cell r="N68" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="69">
+          <cell r="A69" t="str">
+            <v>Agapeon Toothbrush Holder And Toothpaste Dispenser</v>
+          </cell>
+          <cell r="B69" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C69" t="str">
+            <v>KSh 382</v>
+          </cell>
+          <cell r="D69">
+            <v>382</v>
+          </cell>
+          <cell r="E69" t="str">
+            <v>KSh 700</v>
+          </cell>
+          <cell r="F69">
+            <v>700</v>
+          </cell>
+          <cell r="G69">
+            <v>318</v>
+          </cell>
           <cell r="H69">
             <v>0.45</v>
           </cell>
+          <cell r="I69" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J69">
+            <v>-17</v>
+          </cell>
           <cell r="K69">
             <v>17</v>
           </cell>
+          <cell r="L69" t="str">
+            <v>2.6 out of 5</v>
+          </cell>
           <cell r="M69">
             <v>2.6</v>
           </cell>
+          <cell r="N69" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="70">
+          <cell r="A70" t="str">
+            <v>Large Lazy Inflatable Sofa Chairs PVC Lounger Seat Bag</v>
+          </cell>
+          <cell r="B70" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C70" t="str">
+            <v>KSh 2,300</v>
+          </cell>
+          <cell r="D70">
+            <v>2300</v>
+          </cell>
+          <cell r="E70" t="str">
+            <v>KSh 3,240</v>
+          </cell>
+          <cell r="F70">
+            <v>3240</v>
+          </cell>
+          <cell r="G70">
+            <v>940</v>
+          </cell>
           <cell r="H70">
             <v>0.28999999999999998</v>
           </cell>
+          <cell r="I70" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J70">
+            <v>-5</v>
+          </cell>
           <cell r="K70">
             <v>5</v>
           </cell>
+          <cell r="L70" t="str">
+            <v>3 out of 5</v>
+          </cell>
           <cell r="M70">
             <v>3</v>
           </cell>
+          <cell r="N70" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="71">
+          <cell r="A71" t="str">
+            <v>Watercolour Gold Foil Textured Print Pillow Cover</v>
+          </cell>
+          <cell r="B71" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C71" t="str">
+            <v>KSh 345</v>
+          </cell>
+          <cell r="D71">
+            <v>345</v>
+          </cell>
+          <cell r="E71" t="str">
+            <v>KSh 602</v>
+          </cell>
+          <cell r="F71">
+            <v>602</v>
+          </cell>
+          <cell r="G71">
+            <v>257</v>
+          </cell>
           <cell r="H71">
             <v>0.43</v>
           </cell>
+          <cell r="I71" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J71">
+            <v>-6</v>
+          </cell>
           <cell r="K71">
             <v>6</v>
           </cell>
+          <cell r="L71" t="str">
+            <v>2.3 out of 5</v>
+          </cell>
           <cell r="M71">
             <v>2.2999999999999998</v>
           </cell>
+          <cell r="N71" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="72">
+          <cell r="A72" t="str">
+            <v>Wrought Iron Bathroom Shelf Wall Mounted Free Punch Toilet Rack</v>
+          </cell>
+          <cell r="B72" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>KSh 509</v>
+          </cell>
+          <cell r="D72">
+            <v>509</v>
+          </cell>
+          <cell r="E72" t="str">
+            <v>KSh 899</v>
+          </cell>
+          <cell r="F72">
+            <v>899</v>
+          </cell>
+          <cell r="G72">
+            <v>390</v>
+          </cell>
           <cell r="H72">
             <v>0.43</v>
           </cell>
+          <cell r="I72" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J72">
+            <v>-5</v>
+          </cell>
           <cell r="K72">
             <v>5</v>
           </cell>
+          <cell r="L72" t="str">
+            <v>3 out of 5</v>
+          </cell>
           <cell r="M72">
             <v>3</v>
           </cell>
+          <cell r="N72" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="73">
+          <cell r="A73" t="str">
+            <v>7-piece Set Of Storage Bags, Travel Storage Bags, Shoe Bags</v>
+          </cell>
+          <cell r="B73" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C73" t="str">
+            <v>KSh 968</v>
+          </cell>
+          <cell r="D73">
+            <v>968</v>
+          </cell>
+          <cell r="E73" t="str">
+            <v>KSh 1,814</v>
+          </cell>
+          <cell r="F73">
+            <v>1814</v>
+          </cell>
+          <cell r="G73">
+            <v>846</v>
+          </cell>
           <cell r="H73">
             <v>0.47</v>
           </cell>
+          <cell r="I73" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J73">
+            <v>-6</v>
+          </cell>
           <cell r="K73">
             <v>6</v>
           </cell>
+          <cell r="L73" t="str">
+            <v>2.2 out of 5</v>
+          </cell>
           <cell r="M73">
             <v>2.2000000000000002</v>
           </cell>
+          <cell r="N73" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="74">
+          <cell r="A74" t="str">
+            <v>Electric LED UV Mosquito Killer Lamp, Outdoor/Indoor Fly Killer Trap Light -USB</v>
+          </cell>
+          <cell r="B74" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C74" t="str">
+            <v>KSh 1,570</v>
+          </cell>
+          <cell r="D74">
+            <v>1570</v>
+          </cell>
+          <cell r="E74" t="str">
+            <v>KSh 2,988</v>
+          </cell>
+          <cell r="F74">
+            <v>2988</v>
+          </cell>
+          <cell r="G74">
+            <v>1418</v>
+          </cell>
           <cell r="H74">
             <v>0.47</v>
           </cell>
+          <cell r="I74" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J74">
+            <v>-7</v>
+          </cell>
           <cell r="K74">
             <v>7</v>
           </cell>
+          <cell r="L74" t="str">
+            <v>2.1 out of 5</v>
+          </cell>
           <cell r="M74">
             <v>2.1</v>
           </cell>
+          <cell r="N74" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="75">
+          <cell r="A75" t="str">
+            <v>2PCS/LOT Solar LED Outdoor Intelligent Light Controlled Wall Lamp</v>
+          </cell>
+          <cell r="B75" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C75" t="str">
+            <v>KSh 790</v>
+          </cell>
+          <cell r="D75">
+            <v>790</v>
+          </cell>
+          <cell r="E75" t="str">
+            <v>KSh 1,485</v>
+          </cell>
+          <cell r="F75">
+            <v>1485</v>
+          </cell>
+          <cell r="G75">
+            <v>695</v>
+          </cell>
           <cell r="H75">
             <v>0.47</v>
           </cell>
+          <cell r="I75" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K75" t="str">
             <v/>
           </cell>
           <cell r="M75" t="str">
+            <v/>
+          </cell>
+          <cell r="N75" t="str">
             <v/>
           </cell>
         </row>
         <row r="76">
+          <cell r="A76" t="str">
+            <v>3PCS Rotary Scraper Thermomix For Kitchen</v>
+          </cell>
+          <cell r="B76" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C76" t="str">
+            <v>KSh 690</v>
+          </cell>
+          <cell r="D76">
+            <v>690</v>
+          </cell>
+          <cell r="E76" t="str">
+            <v>KSh 1,200</v>
+          </cell>
+          <cell r="F76">
+            <v>1200</v>
+          </cell>
+          <cell r="G76">
+            <v>510</v>
+          </cell>
           <cell r="H76">
             <v>0.43</v>
           </cell>
+          <cell r="I76" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K76" t="str">
             <v/>
           </cell>
           <cell r="M76" t="str">
+            <v/>
+          </cell>
+          <cell r="N76" t="str">
             <v/>
           </cell>
         </row>
         <row r="77">
+          <cell r="A77" t="str">
+            <v>Cushion Silicone Butt Cushion Summer Ice Cushion Honeycomb Gel Cushion</v>
+          </cell>
+          <cell r="B77" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C77" t="str">
+            <v>KSh 1,732</v>
+          </cell>
+          <cell r="D77">
+            <v>1732</v>
+          </cell>
+          <cell r="E77" t="str">
+            <v>KSh 1,799</v>
+          </cell>
+          <cell r="F77">
+            <v>1799</v>
+          </cell>
+          <cell r="G77">
+            <v>67</v>
+          </cell>
           <cell r="H77">
             <v>0.04</v>
           </cell>
+          <cell r="I77" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K77" t="str">
             <v/>
           </cell>
           <cell r="M77" t="str">
+            <v/>
+          </cell>
+          <cell r="N77" t="str">
             <v/>
           </cell>
         </row>
         <row r="78">
+          <cell r="A78" t="str">
+            <v>7PCS Silicone Thumb Knife Finger Protector Vegetable Harvesting Knife</v>
+          </cell>
+          <cell r="B78" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C78" t="str">
+            <v>KSh 230</v>
+          </cell>
+          <cell r="D78">
+            <v>230</v>
+          </cell>
+          <cell r="E78" t="str">
+            <v>KSh 450</v>
+          </cell>
+          <cell r="F78">
+            <v>450</v>
+          </cell>
+          <cell r="G78">
+            <v>220</v>
+          </cell>
           <cell r="H78">
             <v>0.49</v>
           </cell>
+          <cell r="I78" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K78" t="str">
             <v/>
           </cell>
           <cell r="M78" t="str">
+            <v/>
+          </cell>
+          <cell r="N78" t="str">
             <v/>
           </cell>
         </row>
         <row r="79">
+          <cell r="A79" t="str">
+            <v>Memory Foam Neck Pillow Cover, With Pillow Core - 50*30cm</v>
+          </cell>
+          <cell r="B79" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C79" t="str">
+            <v>KSh 1,189</v>
+          </cell>
+          <cell r="D79">
+            <v>1189</v>
+          </cell>
+          <cell r="E79" t="str">
+            <v>KSh 2,199</v>
+          </cell>
+          <cell r="F79">
+            <v>2199</v>
+          </cell>
+          <cell r="G79">
+            <v>1010</v>
+          </cell>
           <cell r="H79">
             <v>0.46</v>
           </cell>
+          <cell r="I79" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J79">
+            <v>-1</v>
+          </cell>
           <cell r="K79">
             <v>1</v>
           </cell>
+          <cell r="L79" t="str">
+            <v>3 out of 5</v>
+          </cell>
           <cell r="M79">
             <v>3</v>
           </cell>
+          <cell r="N79" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="80">
+          <cell r="A80" t="str">
+            <v>Bedroom Simple Floor Hanging Clothes Rack Single Pole Hat Rack - White</v>
+          </cell>
+          <cell r="B80" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C80" t="str">
+            <v>KSh 979</v>
+          </cell>
+          <cell r="D80">
+            <v>979</v>
+          </cell>
+          <cell r="E80" t="str">
+            <v>KSh 1,920</v>
+          </cell>
+          <cell r="F80">
+            <v>1920</v>
+          </cell>
+          <cell r="G80">
+            <v>941</v>
+          </cell>
           <cell r="H80">
             <v>0.49</v>
           </cell>
+          <cell r="I80" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J80">
+            <v>-1</v>
+          </cell>
           <cell r="K80">
             <v>1</v>
           </cell>
+          <cell r="L80" t="str">
+            <v>5 out of 5</v>
+          </cell>
           <cell r="M80">
             <v>5</v>
           </cell>
+          <cell r="N80" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="81">
+          <cell r="A81" t="str">
+            <v>5m Waterproof Spherical LED String Lights Outdoor Ball Chain Lights Party Lighting Decoration Adjustable</v>
+          </cell>
+          <cell r="B81" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C81" t="str">
+            <v>KSh 1,460</v>
+          </cell>
+          <cell r="D81">
+            <v>1460</v>
+          </cell>
+          <cell r="E81" t="str">
+            <v>KSh 2,290</v>
+          </cell>
+          <cell r="F81">
+            <v>2290</v>
+          </cell>
+          <cell r="G81">
+            <v>830</v>
+          </cell>
           <cell r="H81">
             <v>0.36</v>
           </cell>
+          <cell r="I81" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K81" t="str">
             <v/>
           </cell>
           <cell r="M81" t="str">
+            <v/>
+          </cell>
+          <cell r="N81" t="str">
             <v/>
           </cell>
         </row>
         <row r="82">
+          <cell r="A82" t="str">
+            <v>2 Pairs Cowhide Split Leather Work Gloves.32â„‰ Or Above Welding Gloves</v>
+          </cell>
+          <cell r="B82" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C82" t="str">
+            <v>KSh 1,666</v>
+          </cell>
+          <cell r="D82">
+            <v>1666</v>
+          </cell>
+          <cell r="E82" t="str">
+            <v>KSh 1,699</v>
+          </cell>
+          <cell r="F82">
+            <v>1699</v>
+          </cell>
+          <cell r="G82">
+            <v>33</v>
+          </cell>
           <cell r="H82">
             <v>0.02</v>
           </cell>
+          <cell r="I82" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K82" t="str">
             <v/>
           </cell>
           <cell r="M82" t="str">
+            <v/>
+          </cell>
+          <cell r="N82" t="str">
             <v/>
           </cell>
         </row>
         <row r="83">
+          <cell r="A83" t="str">
+            <v>Household Pineapple Peeler Peeler</v>
+          </cell>
+          <cell r="B83" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C83" t="str">
+            <v>KSh 330</v>
+          </cell>
+          <cell r="D83">
+            <v>330</v>
+          </cell>
+          <cell r="E83" t="str">
+            <v>KSh 647</v>
+          </cell>
+          <cell r="F83">
+            <v>647</v>
+          </cell>
+          <cell r="G83">
+            <v>317</v>
+          </cell>
           <cell r="H83">
             <v>0.49</v>
           </cell>
+          <cell r="I83" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J83">
+            <v>-1</v>
+          </cell>
           <cell r="K83">
             <v>1</v>
           </cell>
+          <cell r="L83" t="str">
+            <v>4 out of 5</v>
+          </cell>
           <cell r="M83">
             <v>4</v>
           </cell>
+          <cell r="N83" t="str">
+            <v>Average</v>
+          </cell>
         </row>
         <row r="84">
+          <cell r="A84" t="str">
+            <v>Office Chair Lumbar Back Support Spine Posture Correction Pillow Car Cushion</v>
+          </cell>
+          <cell r="B84" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C84" t="str">
+            <v>KSh 1,466</v>
+          </cell>
+          <cell r="D84">
+            <v>1466</v>
+          </cell>
+          <cell r="E84" t="str">
+            <v>KSh 1,699</v>
+          </cell>
+          <cell r="F84">
+            <v>1699</v>
+          </cell>
+          <cell r="G84">
+            <v>233</v>
+          </cell>
           <cell r="H84">
             <v>0.14000000000000001</v>
           </cell>
+          <cell r="I84" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K84" t="str">
             <v/>
           </cell>
           <cell r="M84" t="str">
+            <v/>
+          </cell>
+          <cell r="N84" t="str">
             <v/>
           </cell>
         </row>
         <row r="85">
+          <cell r="A85" t="str">
+            <v>Cartoon Car Decoration Cute Individuality For Car Home Desk</v>
+          </cell>
+          <cell r="B85" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C85" t="str">
+            <v>KSh 274</v>
+          </cell>
+          <cell r="D85">
+            <v>274</v>
+          </cell>
+          <cell r="E85" t="str">
+            <v>KSh 537</v>
+          </cell>
+          <cell r="F85">
+            <v>537</v>
+          </cell>
+          <cell r="G85">
+            <v>263</v>
+          </cell>
           <cell r="H85">
             <v>0.49</v>
           </cell>
+          <cell r="I85" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K85" t="str">
             <v/>
           </cell>
           <cell r="M85" t="str">
+            <v/>
+          </cell>
+          <cell r="N85" t="str">
             <v/>
           </cell>
         </row>
         <row r="86">
+          <cell r="A86" t="str">
+            <v>Outdoor Portable Water Bottle With Medicine Box - 600ML - Black</v>
+          </cell>
+          <cell r="B86" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C86" t="str">
+            <v>KSh 799</v>
+          </cell>
+          <cell r="D86">
+            <v>799</v>
+          </cell>
+          <cell r="E86" t="str">
+            <v>KSh 900</v>
+          </cell>
+          <cell r="F86">
+            <v>900</v>
+          </cell>
+          <cell r="G86">
+            <v>101</v>
+          </cell>
           <cell r="H86">
             <v>0.11</v>
           </cell>
+          <cell r="I86" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K86" t="str">
             <v/>
           </cell>
           <cell r="M86" t="str">
+            <v/>
+          </cell>
+          <cell r="N86" t="str">
             <v/>
           </cell>
         </row>
         <row r="87">
+          <cell r="A87" t="str">
+            <v>Wall-Mounted Toothbrush Toothpaste Holder With Multiple Slots</v>
+          </cell>
+          <cell r="B87" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C87" t="str">
+            <v>KSh 1,468</v>
+          </cell>
+          <cell r="D87">
+            <v>1468</v>
+          </cell>
+          <cell r="E87" t="str">
+            <v>KSh 1,699</v>
+          </cell>
+          <cell r="F87">
+            <v>1699</v>
+          </cell>
+          <cell r="G87">
+            <v>231</v>
+          </cell>
           <cell r="H87">
             <v>0.14000000000000001</v>
           </cell>
+          <cell r="I87" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K87" t="str">
             <v/>
           </cell>
           <cell r="M87" t="str">
+            <v/>
+          </cell>
+          <cell r="N87" t="str">
             <v/>
           </cell>
         </row>
         <row r="88">
+          <cell r="A88" t="str">
+            <v>Multifunctional Hanging Storage Box Storage Bag (4 Layers)</v>
+          </cell>
+          <cell r="B88" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C88" t="str">
+            <v>KSh 630</v>
+          </cell>
+          <cell r="D88">
+            <v>630</v>
+          </cell>
+          <cell r="E88" t="str">
+            <v>KSh 1,100</v>
+          </cell>
+          <cell r="F88">
+            <v>1100</v>
+          </cell>
+          <cell r="G88">
+            <v>470</v>
+          </cell>
           <cell r="H88">
             <v>0.43</v>
           </cell>
+          <cell r="I88" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K88" t="str">
             <v/>
           </cell>
           <cell r="M88" t="str">
+            <v/>
+          </cell>
+          <cell r="N88" t="str">
             <v/>
           </cell>
         </row>
         <row r="89">
+          <cell r="A89" t="str">
+            <v>Wall Clock With Hidden Safe Box</v>
+          </cell>
+          <cell r="B89" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C89" t="str">
+            <v>KSh 850</v>
+          </cell>
+          <cell r="D89">
+            <v>850</v>
+          </cell>
+          <cell r="E89" t="str">
+            <v>KSh 1,700</v>
+          </cell>
+          <cell r="F89">
+            <v>1700</v>
+          </cell>
+          <cell r="G89">
+            <v>850</v>
+          </cell>
           <cell r="H89">
             <v>0.5</v>
           </cell>
+          <cell r="I89" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K89" t="str">
             <v/>
           </cell>
           <cell r="M89" t="str">
+            <v/>
+          </cell>
+          <cell r="N89" t="str">
             <v/>
           </cell>
         </row>
         <row r="90">
+          <cell r="A90" t="str">
+            <v>Portable Wine Table With Folding Round Table</v>
+          </cell>
+          <cell r="B90" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C90" t="str">
+            <v>KSh 1,300</v>
+          </cell>
+          <cell r="D90">
+            <v>1300</v>
+          </cell>
+          <cell r="E90" t="str">
+            <v>KSh 2,500</v>
+          </cell>
+          <cell r="F90">
+            <v>2500</v>
+          </cell>
+          <cell r="G90">
+            <v>1200</v>
+          </cell>
           <cell r="H90">
             <v>0.48</v>
           </cell>
+          <cell r="I90" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K90" t="str">
             <v/>
           </cell>
           <cell r="M90" t="str">
+            <v/>
+          </cell>
+          <cell r="N90" t="str">
             <v/>
           </cell>
         </row>
         <row r="91">
+          <cell r="A91" t="str">
+            <v>Sewing Machine Needle Threader Stitch Insertion Tool Automatic Quick Sewing</v>
+          </cell>
+          <cell r="B91" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C91" t="str">
+            <v>KSh 105</v>
+          </cell>
+          <cell r="D91">
+            <v>105</v>
+          </cell>
+          <cell r="E91" t="str">
+            <v>KSh 200</v>
+          </cell>
+          <cell r="F91">
+            <v>200</v>
+          </cell>
+          <cell r="G91">
+            <v>95</v>
+          </cell>
           <cell r="H91">
             <v>0.48</v>
           </cell>
+          <cell r="I91" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K91" t="str">
             <v/>
           </cell>
           <cell r="M91" t="str">
+            <v/>
+          </cell>
+          <cell r="N91" t="str">
             <v/>
           </cell>
         </row>
         <row r="92">
+          <cell r="A92" t="str">
+            <v>6 Layers Steel Pipe Assembling Dustproof Storage Shoe Cabinet</v>
+          </cell>
+          <cell r="B92" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C92" t="str">
+            <v>KSh 899</v>
+          </cell>
+          <cell r="D92">
+            <v>899</v>
+          </cell>
+          <cell r="E92" t="str">
+            <v>KSh 1,699</v>
+          </cell>
+          <cell r="F92">
+            <v>1699</v>
+          </cell>
+          <cell r="G92">
+            <v>800</v>
+          </cell>
           <cell r="H92">
             <v>0.47</v>
           </cell>
+          <cell r="I92" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K92" t="str">
             <v/>
           </cell>
           <cell r="M92" t="str">
+            <v/>
+          </cell>
+          <cell r="N92" t="str">
             <v/>
           </cell>
         </row>
         <row r="93">
+          <cell r="A93" t="str">
+            <v>2PCS Ice Silk Square Cushion Cover Pillowcases - 65x65cm</v>
+          </cell>
+          <cell r="B93" t="str">
+            <v>Home Decor</v>
+          </cell>
+          <cell r="C93" t="str">
+            <v>KSh 1,200</v>
+          </cell>
+          <cell r="D93">
+            <v>1200</v>
+          </cell>
+          <cell r="E93" t="str">
+            <v>KSh 2,400</v>
+          </cell>
+          <cell r="F93">
+            <v>2400</v>
+          </cell>
+          <cell r="G93">
+            <v>1200</v>
+          </cell>
           <cell r="H93">
             <v>0.5</v>
           </cell>
+          <cell r="I93" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K93" t="str">
             <v/>
           </cell>
           <cell r="M93" t="str">
+            <v/>
+          </cell>
+          <cell r="N93" t="str">
             <v/>
           </cell>
         </row>
         <row r="94">
+          <cell r="A94" t="str">
+            <v>Wall Mount Automatic Toothpaste Dispenser Toothbrush Holder Toothpaste Squeezer</v>
+          </cell>
+          <cell r="B94" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C94" t="str">
+            <v>KSh 1,526</v>
+          </cell>
+          <cell r="D94">
+            <v>1526</v>
+          </cell>
+          <cell r="E94" t="str">
+            <v>KSh 1,660</v>
+          </cell>
+          <cell r="F94">
+            <v>1660</v>
+          </cell>
+          <cell r="G94">
+            <v>134</v>
+          </cell>
           <cell r="H94">
             <v>0.08</v>
           </cell>
+          <cell r="I94" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K94" t="str">
             <v/>
           </cell>
           <cell r="M94" t="str">
+            <v/>
+          </cell>
+          <cell r="N94" t="str">
             <v/>
           </cell>
         </row>
         <row r="95">
+          <cell r="A95" t="str">
+            <v>Portable Soap Dispenser Kitchen Detergent Press Box Kitchen Tools</v>
+          </cell>
+          <cell r="B95" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C95" t="str">
+            <v>KSh 1,462</v>
+          </cell>
+          <cell r="D95">
+            <v>1462</v>
+          </cell>
+          <cell r="E95" t="str">
+            <v>KSh 1,499</v>
+          </cell>
+          <cell r="F95">
+            <v>1499</v>
+          </cell>
+          <cell r="G95">
+            <v>37</v>
+          </cell>
           <cell r="H95">
             <v>0.02</v>
           </cell>
+          <cell r="I95" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K95" t="str">
             <v/>
           </cell>
           <cell r="M95" t="str">
+            <v/>
+          </cell>
+          <cell r="N95" t="str">
             <v/>
           </cell>
         </row>
         <row r="96">
+          <cell r="A96" t="str">
+            <v>4 Piece Coloured Stainless Steel Kitchenware Set</v>
+          </cell>
+          <cell r="B96" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C96" t="str">
+            <v>KSh 248</v>
+          </cell>
+          <cell r="D96">
+            <v>248</v>
+          </cell>
+          <cell r="E96" t="str">
+            <v>KSh 486</v>
+          </cell>
+          <cell r="F96">
+            <v>486</v>
+          </cell>
+          <cell r="G96">
+            <v>238</v>
+          </cell>
           <cell r="H96">
             <v>0.49</v>
           </cell>
+          <cell r="I96" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K96" t="str">
             <v/>
           </cell>
           <cell r="M96" t="str">
+            <v/>
+          </cell>
+          <cell r="N96" t="str">
             <v/>
           </cell>
         </row>
         <row r="97">
+          <cell r="A97" t="str">
+            <v>Metal Wall Clock Silver Dial Crystal Jewelry Round Home Decoration Wall Clock</v>
+          </cell>
+          <cell r="B97" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C97" t="str">
+            <v>KSh 3,546</v>
+          </cell>
+          <cell r="D97">
+            <v>3546</v>
+          </cell>
+          <cell r="E97" t="str">
+            <v>KSh 3,699</v>
+          </cell>
+          <cell r="F97">
+            <v>3699</v>
+          </cell>
+          <cell r="G97">
+            <v>153</v>
+          </cell>
           <cell r="H97">
             <v>0.04</v>
           </cell>
+          <cell r="I97" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K97" t="str">
             <v/>
           </cell>
           <cell r="M97" t="str">
+            <v/>
+          </cell>
+          <cell r="N97" t="str">
             <v/>
           </cell>
         </row>
         <row r="98">
+          <cell r="A98" t="str">
+            <v>Baby Early Education Shape And Color Cognitive Training Toys</v>
+          </cell>
+          <cell r="B98" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C98" t="str">
+            <v>KSh 525</v>
+          </cell>
+          <cell r="D98">
+            <v>525</v>
+          </cell>
+          <cell r="E98" t="str">
+            <v>KSh 1,029</v>
+          </cell>
+          <cell r="F98">
+            <v>1029</v>
+          </cell>
+          <cell r="G98">
+            <v>504</v>
+          </cell>
           <cell r="H98">
             <v>0.49</v>
           </cell>
+          <cell r="I98" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K98" t="str">
             <v/>
           </cell>
           <cell r="M98" t="str">
+            <v/>
+          </cell>
+          <cell r="N98" t="str">
             <v/>
           </cell>
         </row>
         <row r="99">
+          <cell r="A99" t="str">
+            <v>8in1 Screwdriver With LED Light</v>
+          </cell>
+          <cell r="B99" t="str">
+            <v>Tools &amp; Hardware</v>
+          </cell>
+          <cell r="C99" t="str">
+            <v>KSh 1,080</v>
+          </cell>
+          <cell r="D99">
+            <v>1080</v>
+          </cell>
+          <cell r="E99" t="str">
+            <v>KSh 1,874</v>
+          </cell>
+          <cell r="F99">
+            <v>1874</v>
+          </cell>
+          <cell r="G99">
+            <v>794</v>
+          </cell>
           <cell r="H99">
             <v>0.42</v>
           </cell>
+          <cell r="I99" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K99" t="str">
             <v/>
           </cell>
           <cell r="M99" t="str">
+            <v/>
+          </cell>
+          <cell r="N99" t="str">
             <v/>
           </cell>
         </row>
         <row r="100">
+          <cell r="A100" t="str">
+            <v>Konka Healty Electric Kettle, 24-hour Heat Preservation,1.5L,800W, White</v>
+          </cell>
+          <cell r="B100" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C100" t="str">
+            <v>KSh 3,640</v>
+          </cell>
+          <cell r="D100">
+            <v>3640</v>
+          </cell>
+          <cell r="E100" t="str">
+            <v>KSh 4,588</v>
+          </cell>
+          <cell r="F100">
+            <v>4588</v>
+          </cell>
+          <cell r="G100">
+            <v>948</v>
+          </cell>
           <cell r="H100">
             <v>0.21</v>
           </cell>
+          <cell r="I100" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
+          <cell r="J100">
+            <v>-1</v>
+          </cell>
           <cell r="K100">
             <v>1</v>
           </cell>
+          <cell r="L100" t="str">
+            <v>5 out of 5</v>
+          </cell>
           <cell r="M100">
             <v>5</v>
           </cell>
+          <cell r="N100" t="str">
+            <v>Excellent</v>
+          </cell>
         </row>
         <row r="101">
+          <cell r="A101" t="str">
+            <v>9pcs Gas Mask, For Painting, Dust, Formaldehyde Grinding, Polishing</v>
+          </cell>
+          <cell r="B101" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C101" t="str">
+            <v>KSh 1,420</v>
+          </cell>
+          <cell r="D101">
+            <v>1420</v>
+          </cell>
+          <cell r="E101" t="str">
+            <v>KSh 2,420</v>
+          </cell>
+          <cell r="F101">
+            <v>2420</v>
+          </cell>
+          <cell r="G101">
+            <v>1000</v>
+          </cell>
           <cell r="H101">
             <v>0.41</v>
           </cell>
+          <cell r="I101" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K101" t="str">
             <v/>
           </cell>
           <cell r="M101" t="str">
+            <v/>
+          </cell>
+          <cell r="N101" t="str">
             <v/>
           </cell>
         </row>
         <row r="102">
+          <cell r="A102" t="str">
+            <v>24 Grid Wall-mounted Sundries Organiser Fabric Closet Bag Storage Rack</v>
+          </cell>
+          <cell r="B102" t="str">
+            <v>Home &amp; Kitchen</v>
+          </cell>
+          <cell r="C102" t="str">
+            <v>KSh 1,875</v>
+          </cell>
+          <cell r="D102">
+            <v>1875</v>
+          </cell>
+          <cell r="E102" t="str">
+            <v>KSh 1,899</v>
+          </cell>
+          <cell r="F102">
+            <v>1899</v>
+          </cell>
+          <cell r="G102">
+            <v>24</v>
+          </cell>
           <cell r="H102">
             <v>0.01</v>
           </cell>
+          <cell r="I102" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K102" t="str">
             <v/>
           </cell>
           <cell r="M102" t="str">
+            <v/>
+          </cell>
+          <cell r="N102" t="str">
             <v/>
           </cell>
         </row>
         <row r="103">
+          <cell r="A103" t="str">
+            <v>1PC Refrigerator Food Seal Pocket Fridge Bags</v>
+          </cell>
+          <cell r="B103" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C103" t="str">
+            <v>KSh 198</v>
+          </cell>
+          <cell r="D103">
+            <v>198</v>
+          </cell>
+          <cell r="E103" t="str">
+            <v>KSh 260</v>
+          </cell>
+          <cell r="F103">
+            <v>260</v>
+          </cell>
+          <cell r="G103">
+            <v>62</v>
+          </cell>
           <cell r="H103">
             <v>0.24</v>
           </cell>
+          <cell r="I103" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K103" t="str">
             <v/>
           </cell>
           <cell r="M103" t="str">
+            <v/>
+          </cell>
+          <cell r="N103" t="str">
             <v/>
           </cell>
         </row>
         <row r="104">
+          <cell r="A104" t="str">
+            <v>LED Solar Street Light-fake Camera</v>
+          </cell>
+          <cell r="B104" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C104" t="str">
+            <v>KSh 1,150</v>
+          </cell>
+          <cell r="D104">
+            <v>1150</v>
+          </cell>
+          <cell r="E104" t="str">
+            <v>KSh 1,737</v>
+          </cell>
+          <cell r="F104">
+            <v>1737</v>
+          </cell>
+          <cell r="G104">
+            <v>587</v>
+          </cell>
           <cell r="H104">
             <v>0.34</v>
           </cell>
+          <cell r="I104" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K104" t="str">
             <v/>
           </cell>
           <cell r="M104" t="str">
+            <v/>
+          </cell>
+          <cell r="N104" t="str">
             <v/>
           </cell>
         </row>
         <row r="105">
+          <cell r="A105" t="str">
+            <v>Cartoon Embroidered Mini Towel Bear Cotton Wash Cloth Hand 4pcs</v>
+          </cell>
+          <cell r="B105" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C105" t="str">
+            <v>KSh 1,190</v>
+          </cell>
+          <cell r="D105">
+            <v>1190</v>
+          </cell>
+          <cell r="E105" t="str">
+            <v>KSh 1,810</v>
+          </cell>
+          <cell r="F105">
+            <v>1810</v>
+          </cell>
+          <cell r="G105">
+            <v>620</v>
+          </cell>
           <cell r="H105">
             <v>0.34</v>
           </cell>
+          <cell r="I105" t="str">
+            <v xml:space="preserve">Medium </v>
+          </cell>
           <cell r="K105" t="str">
             <v/>
           </cell>
           <cell r="M105" t="str">
+            <v/>
+          </cell>
+          <cell r="N105" t="str">
             <v/>
           </cell>
         </row>
         <row r="106">
+          <cell r="A106" t="str">
+            <v>Shower Nozzle Cleaning Unclogging Needle Mini Crevice Small Hole Cleaning Brush</v>
+          </cell>
+          <cell r="B106" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C106" t="str">
+            <v>KSh 1,658</v>
+          </cell>
+          <cell r="D106">
+            <v>1658</v>
+          </cell>
+          <cell r="E106" t="str">
+            <v>KSh 1,699</v>
+          </cell>
+          <cell r="F106">
+            <v>1699</v>
+          </cell>
+          <cell r="G106">
+            <v>41</v>
+          </cell>
           <cell r="H106">
             <v>0.02</v>
           </cell>
+          <cell r="I106" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K106" t="str">
             <v/>
           </cell>
           <cell r="M106" t="str">
+            <v/>
+          </cell>
+          <cell r="N106" t="str">
             <v/>
           </cell>
         </row>
         <row r="107">
+          <cell r="A107" t="str">
+            <v>Thickening Multipurpose Non Stick Easy To Clean Heat Resistant Spoon Pad</v>
+          </cell>
+          <cell r="B107" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C107" t="str">
+            <v>KSh 1,768</v>
+          </cell>
+          <cell r="D107">
+            <v>1768</v>
+          </cell>
+          <cell r="E107" t="str">
+            <v>KSh 1,799</v>
+          </cell>
+          <cell r="F107">
+            <v>1799</v>
+          </cell>
+          <cell r="G107">
+            <v>31</v>
+          </cell>
           <cell r="H107">
             <v>0.02</v>
           </cell>
+          <cell r="I107" t="str">
+            <v>Low</v>
+          </cell>
           <cell r="K107" t="str">
             <v/>
           </cell>
           <cell r="M107" t="str">
+            <v/>
+          </cell>
+          <cell r="N107" t="str">
             <v/>
           </cell>
         </row>
         <row r="108">
+          <cell r="A108" t="str">
+            <v>6 In 1 Bottle Can Opener Multifunctional Easy Opener</v>
+          </cell>
+          <cell r="B108" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C108" t="str">
+            <v>KSh 199</v>
+          </cell>
+          <cell r="D108">
+            <v>199</v>
+          </cell>
+          <cell r="E108" t="str">
+            <v>KSh 553</v>
+          </cell>
+          <cell r="F108">
+            <v>553</v>
+          </cell>
+          <cell r="G108">
+            <v>354</v>
+          </cell>
           <cell r="H108">
             <v>0.64</v>
           </cell>
+          <cell r="I108" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K108" t="str">
             <v/>
           </cell>
           <cell r="M108" t="str">
+            <v/>
+          </cell>
+          <cell r="N108" t="str">
             <v/>
           </cell>
         </row>
         <row r="109">
+          <cell r="A109" t="str">
+            <v>Wall-mounted Sticker Punch-free Plug Fixer</v>
+          </cell>
+          <cell r="B109" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C109" t="str">
+            <v>KSh 450</v>
+          </cell>
+          <cell r="D109">
+            <v>450</v>
+          </cell>
+          <cell r="E109" t="str">
+            <v>KSh 900</v>
+          </cell>
+          <cell r="F109">
+            <v>900</v>
+          </cell>
+          <cell r="G109">
+            <v>450</v>
+          </cell>
           <cell r="H109">
             <v>0.5</v>
           </cell>
+          <cell r="I109" t="str">
+            <v>High</v>
+          </cell>
+          <cell r="J109">
+            <v>-1</v>
+          </cell>
           <cell r="K109">
             <v>1</v>
           </cell>
+          <cell r="L109" t="str">
+            <v>2 out of 5</v>
+          </cell>
           <cell r="M109">
             <v>2</v>
           </cell>
+          <cell r="N109" t="str">
+            <v>Poor</v>
+          </cell>
         </row>
         <row r="110">
+          <cell r="A110" t="str">
+            <v>Black Simple Water Cup Wine Coaster Anti Slip Absorbent</v>
+          </cell>
+          <cell r="B110" t="str">
+            <v>Other</v>
+          </cell>
+          <cell r="C110" t="str">
+            <v>KSh 169</v>
+          </cell>
+          <cell r="D110">
+            <v>169</v>
+          </cell>
+          <cell r="E110" t="str">
+            <v>KSh 320</v>
+          </cell>
+          <cell r="F110">
+            <v>320</v>
+          </cell>
+          <cell r="G110">
+            <v>151</v>
+          </cell>
           <cell r="H110">
             <v>0.47</v>
           </cell>
+          <cell r="I110" t="str">
+            <v>High</v>
+          </cell>
           <cell r="K110" t="str">
             <v/>
           </cell>
           <cell r="M110" t="str">
+            <v/>
+          </cell>
+          <cell r="N110" t="str">
             <v/>
           </cell>
         </row>
@@ -9678,21 +12986,8 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Excel_jumia_dataset"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Admin" refreshedDate="46187.592307870371" backgroundQuery="1" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9EFA05AB-CDCE-4682-991D-B4AB6DD54C6E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Admin" refreshedDate="46187.592307870371" backgroundQuery="1" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{97D48C0C-E4A1-43CD-8416-31554B7670FB}">
   <cacheSource type="external" connectionId="1">
     <extLst>
       <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
@@ -9739,14 +13034,14 @@
   </maps>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="1716339441" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="461475748" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Admin" refreshedDate="46187.591822453702" backgroundQuery="1" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{CC7633C8-8C27-4552-BF11-5D3B5A3DE3FF}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Admin" refreshedDate="46187.591822453702" backgroundQuery="1" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{4C6E6C32-48AF-4E7A-8391-25CA6A870118}">
   <cacheSource type="external" connectionId="1">
     <extLst>
       <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
@@ -9793,14 +13088,14 @@
   </maps>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="984701355" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="247560598" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Admin" refreshedDate="46187.558900231481" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="109" xr:uid="{4BAF839F-12DF-4E90-A5B3-A80423004D33}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Admin" refreshedDate="46187.558900231481" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="109" xr:uid="{A8FB2BCD-382E-489F-84C6-4CBEDB62F885}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:N110" sheet="Excel_jumia_dataset" r:id="rId2"/>
   </cacheSource>
@@ -10131,7 +13426,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="846873961"/>
+      <x14:pivotCacheDefinition pivotCacheId="174457134"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -11669,9 +14964,9 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Product_Type" xr10:uid="{03779E8C-6DAC-4BC1-8497-7D9E15C6B3C1}" sourceName="[Range].[Product Type]">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Product_Type" xr10:uid="{84E41534-912A-4F45-BBEC-AC18206FC402}" sourceName="[Range].[Product Type]">
   <data>
-    <olap pivotCacheId="1716339441">
+    <olap pivotCacheId="461475748">
       <levels count="2">
         <level uniqueName="[Range].[Product Type].[(All)]" sourceCaption="(All)" count="0"/>
         <level uniqueName="[Range].[Product Type].[Product Type]" sourceCaption="Product Type" count="6">
@@ -11700,9 +14995,9 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Discount_Category" xr10:uid="{7A0554FB-3033-471D-8FC2-49071FADDBEE}" sourceName="[Range].[Discount Category]">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Discount_Category" xr10:uid="{DB17B446-57C8-41E8-A530-E7350E60A25D}" sourceName="[Range].[Discount Category]">
   <data>
-    <olap pivotCacheId="984701355">
+    <olap pivotCacheId="247560598">
       <levels count="2">
         <level uniqueName="[Range].[Discount Category].[(All)]" sourceCaption="(All)" count="0"/>
         <level uniqueName="[Range].[Discount Category].[Discount Category]" sourceCaption="Discount Category" count="3">
@@ -11715,9 +15010,8 @@
           </ranges>
         </level>
       </levels>
-      <selections count="2">
-        <selection n="[Range].[Discount Category].&amp;[High]"/>
-        <selection n="[Range].[Discount Category].&amp;[Low]"/>
+      <selections count="1">
+        <selection n="[Range].[Discount Category].[All]"/>
       </selections>
     </olap>
   </data>
@@ -11725,9 +15019,9 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Rating" xr10:uid="{E04A7A19-2FD6-42B3-A007-25E47BCC762A}" sourceName="Rating">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Rating" xr10:uid="{6E66D705-21B8-4578-A2A8-FBF57FE5CBAF}" sourceName="Rating">
   <data>
-    <tabular pivotCacheId="846873961">
+    <tabular pivotCacheId="174457134">
       <items count="23">
         <i x="22" s="1"/>
         <i x="15" s="1"/>
@@ -11760,9 +15054,9 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Product Type 1" xr10:uid="{03758F35-E806-4799-9DA6-A477078DD7A9}" cache="Slicer_Product_Type" caption="Product Type" level="1" rowHeight="241300"/>
-  <slicer name="Discount Category 1" xr10:uid="{EBF3F0EF-6452-407B-A1E6-FBBAE666A4E3}" cache="Slicer_Discount_Category" caption="Discount Category" level="1" rowHeight="241300"/>
-  <slicer name="Rating 1" xr10:uid="{F65F2E63-78CE-44CF-B3BC-BAC7BAB34526}" cache="Slicer_Rating" caption="Rating" rowHeight="241300"/>
+  <slicer name="Product Type 1" xr10:uid="{BBB223DA-C6C2-4BCB-855D-967A01DB0FFA}" cache="Slicer_Product_Type" caption="Product Type" level="1" rowHeight="241300"/>
+  <slicer name="Discount Category 1" xr10:uid="{C6D454A1-3431-406C-B37B-61D8C503609A}" cache="Slicer_Discount_Category" caption="Discount Category" level="1" rowHeight="241300"/>
+  <slicer name="Rating 1" xr10:uid="{BD07FDD5-58FF-4A31-A1BB-FCC3216B1ACE}" cache="Slicer_Rating" caption="Rating" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -12062,7 +15356,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424B4061-6432-4192-B52C-CB22197A5927}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7979A96D-B9C6-47E6-A887-434C78F194B4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Dashboard/Jumia_Dashboard.xlsx
+++ b/Dashboard/Jumia_Dashboard.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuxDev\Jumia-Project\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2065F2FF-0B6C-4EB0-AE2C-8F370B2DA003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0D7053-509B-4645-9A3E-C8482C565ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6F17A25C-8142-493A-80DF-F27B81A0F9E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{6F17A25C-8142-493A-80DF-F27B81A0F9E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_Excel_jumia_datasetA1M1101" hidden="1">[1]Excel_jumia_dataset!$A$1:$N$110</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Excel_jumia_datasetA1M110" hidden="1">[2]Excel_jumia_dataset!$A$1:$N$110</definedName>
     <definedName name="Slicer_Discount_Category">#N/A</definedName>
     <definedName name="Slicer_Product_Type">#N/A</definedName>
     <definedName name="Slicer_Rating">#N/A</definedName>
@@ -28,16 +29,16 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="4" r:id="rId3"/>
-        <pivotCache cacheId="3" r:id="rId4"/>
-        <pivotCache cacheId="0" r:id="rId5"/>
+        <pivotCache cacheId="0" r:id="rId4"/>
+        <pivotCache cacheId="1" r:id="rId5"/>
+        <pivotCache cacheId="2" r:id="rId6"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId6"/>
         <x14:slicerCache r:id="rId7"/>
         <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -81,7 +82,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range-aeb7d533-aafb-4579-9404-31f236ed0e9a" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Excel_jumia_datasetA1M1101"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Excel_jumia_datasetA1M110"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -1302,7 +1303,7 @@
             <c:numRef>
               <c:f>[1]Excel_jumia_dataset!$H$2:$H$111</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0.38</c:v>
@@ -2070,7 +2071,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -7975,8 +7976,8 @@
       <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1840424" cy="1994438"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Product Type 1">
@@ -7999,7 +8000,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8048,8 +8049,8 @@
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1840424" cy="1190948"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Discount Category 1">
@@ -8072,7 +8073,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8121,8 +8122,8 @@
       <xdr:rowOff>38102</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1840424" cy="1383690"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Rating 1">
@@ -8145,7 +8146,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8341,13 +8342,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>254925</xdr:colOff>
+      <xdr:colOff>240918</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>91639</xdr:colOff>
+      <xdr:colOff>77632</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
@@ -8439,4527 +8440,1206 @@
           <cell r="A1" t="str">
             <v>Product</v>
           </cell>
-          <cell r="B1" t="str">
-            <v>Product Type</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Current price</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>Current price Num</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>old price</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>Old Price Num</v>
-          </cell>
-          <cell r="G1" t="str">
-            <v>Abs Discount</v>
-          </cell>
-          <cell r="H1" t="str">
-            <v>Discount</v>
-          </cell>
-          <cell r="I1" t="str">
-            <v>Discount Category</v>
-          </cell>
-          <cell r="J1" t="str">
-            <v>Review</v>
-          </cell>
-          <cell r="K1" t="str">
-            <v>Reviews</v>
-          </cell>
-          <cell r="L1" t="str">
-            <v>Rating</v>
-          </cell>
           <cell r="M1" t="str">
             <v>Rating Std</v>
           </cell>
-          <cell r="N1" t="str">
-            <v>Rating Category</v>
-          </cell>
         </row>
         <row r="2">
-          <cell r="A2" t="str">
-            <v>115  Piece Set Of Multifunctional Precision Screwdrivers</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>Tools &amp; Hardware</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>KSh 950</v>
-          </cell>
-          <cell r="D2">
-            <v>950</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>KSh 1,525</v>
-          </cell>
-          <cell r="F2">
-            <v>1525</v>
-          </cell>
-          <cell r="G2">
-            <v>575</v>
-          </cell>
           <cell r="H2">
             <v>0.38</v>
           </cell>
-          <cell r="I2" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J2">
-            <v>-2</v>
-          </cell>
           <cell r="K2">
             <v>2</v>
           </cell>
-          <cell r="L2" t="str">
-            <v>4.5 out of 5</v>
-          </cell>
           <cell r="M2">
             <v>4.5</v>
           </cell>
-          <cell r="N2" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="3">
-          <cell r="A3" t="str">
-            <v>Metal Decorative Hooks Key Hangers Entryway Wall Hooks Towel Hooks - Home</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>KSh 527</v>
-          </cell>
-          <cell r="D3">
-            <v>527</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>KSh 999</v>
-          </cell>
-          <cell r="F3">
-            <v>999</v>
-          </cell>
-          <cell r="G3">
-            <v>472</v>
-          </cell>
           <cell r="H3">
             <v>0.47</v>
           </cell>
-          <cell r="I3" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J3">
-            <v>-14</v>
-          </cell>
           <cell r="K3">
             <v>14</v>
           </cell>
-          <cell r="L3" t="str">
-            <v>4.1 out of 5</v>
-          </cell>
           <cell r="M3">
             <v>4.0999999999999996</v>
           </cell>
-          <cell r="N3" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="4">
-          <cell r="A4" t="str">
-            <v>Portable Mini Cordless Car Vacuum Cleaner - Blue</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>Cleaning &amp; Appliances</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>KSh 2,199</v>
-          </cell>
-          <cell r="D4">
-            <v>2199</v>
-          </cell>
-          <cell r="E4" t="str">
-            <v>KSh 2,923</v>
-          </cell>
-          <cell r="F4">
-            <v>2923</v>
-          </cell>
-          <cell r="G4">
-            <v>724</v>
-          </cell>
           <cell r="H4">
             <v>0.25</v>
           </cell>
-          <cell r="I4" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J4">
-            <v>-24</v>
-          </cell>
           <cell r="K4">
             <v>24</v>
           </cell>
-          <cell r="L4" t="str">
-            <v>4.6 out of 5</v>
-          </cell>
           <cell r="M4">
             <v>4.5999999999999996</v>
           </cell>
-          <cell r="N4" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="5">
-          <cell r="A5" t="str">
-            <v>Weighing Scale Digital Bathroom Body Fat Scale USB-Black</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>KSh 1,580</v>
-          </cell>
-          <cell r="D5">
-            <v>1580</v>
-          </cell>
-          <cell r="E5" t="str">
-            <v>KSh 2,499</v>
-          </cell>
-          <cell r="F5">
-            <v>2499</v>
-          </cell>
-          <cell r="G5">
-            <v>919</v>
-          </cell>
           <cell r="H5">
             <v>0.37</v>
           </cell>
-          <cell r="I5" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J5">
-            <v>-7</v>
-          </cell>
           <cell r="K5">
             <v>7</v>
           </cell>
-          <cell r="L5" t="str">
-            <v>4.7 out of 5</v>
-          </cell>
           <cell r="M5">
             <v>4.7</v>
           </cell>
-          <cell r="N5" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="6">
-          <cell r="A6" t="str">
-            <v>Portable Home Small Air Humidifier 3-Speed Fan - Green</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>Cleaning &amp; Appliances</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>KSh 1,740</v>
-          </cell>
-          <cell r="D6">
-            <v>1740</v>
-          </cell>
-          <cell r="E6" t="str">
-            <v>KSh 2,356</v>
-          </cell>
-          <cell r="F6">
-            <v>2356</v>
-          </cell>
-          <cell r="G6">
-            <v>616</v>
-          </cell>
           <cell r="H6">
             <v>0.26</v>
           </cell>
-          <cell r="I6" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J6">
-            <v>-5</v>
-          </cell>
           <cell r="K6">
             <v>5</v>
           </cell>
-          <cell r="L6" t="str">
-            <v>4.8 out of 5</v>
-          </cell>
           <cell r="M6">
             <v>4.8</v>
           </cell>
-          <cell r="N6" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="7">
-          <cell r="A7" t="str">
-            <v>220V 60W Electric Soldering Iron Kits With Tools, Tips, And Multimeter</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>KSh 2,999</v>
-          </cell>
-          <cell r="D7">
-            <v>2999</v>
-          </cell>
-          <cell r="E7" t="str">
-            <v>KSh 3,290</v>
-          </cell>
-          <cell r="F7">
-            <v>3290</v>
-          </cell>
-          <cell r="G7">
-            <v>291</v>
-          </cell>
           <cell r="H7">
             <v>0.09</v>
           </cell>
-          <cell r="I7" t="str">
-            <v>Low</v>
-          </cell>
-          <cell r="J7">
-            <v>-15</v>
-          </cell>
           <cell r="K7">
             <v>15</v>
           </cell>
-          <cell r="L7" t="str">
-            <v>4 out of 5</v>
-          </cell>
           <cell r="M7">
             <v>4</v>
           </cell>
-          <cell r="N7" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="8">
-          <cell r="A8" t="str">
-            <v>137 Pieces Cake Decorating Tool Set Baking Supplies</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>KSh 2,319</v>
-          </cell>
-          <cell r="D8">
-            <v>2319</v>
-          </cell>
-          <cell r="E8" t="str">
-            <v>KSh 3,032</v>
-          </cell>
-          <cell r="F8">
-            <v>3032</v>
-          </cell>
-          <cell r="G8">
-            <v>713</v>
-          </cell>
           <cell r="H8">
             <v>0.24</v>
           </cell>
-          <cell r="I8" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J8">
-            <v>-55</v>
-          </cell>
           <cell r="K8">
             <v>55</v>
           </cell>
-          <cell r="L8" t="str">
-            <v>4.6 out of 5</v>
-          </cell>
           <cell r="M8">
             <v>4.5999999999999996</v>
           </cell>
-          <cell r="N8" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="9">
-          <cell r="A9" t="str">
-            <v>Desk Foldable Fan Adjustable Fan Strong Wind 3 Gear Usb</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Cleaning &amp; Appliances</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>KSh 988</v>
-          </cell>
-          <cell r="D9">
-            <v>988</v>
-          </cell>
-          <cell r="E9" t="str">
-            <v>KSh 1,580</v>
-          </cell>
-          <cell r="F9">
-            <v>1580</v>
-          </cell>
-          <cell r="G9">
-            <v>592</v>
-          </cell>
           <cell r="H9">
             <v>0.37</v>
           </cell>
-          <cell r="I9" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J9">
-            <v>-2</v>
-          </cell>
           <cell r="K9">
             <v>2</v>
           </cell>
-          <cell r="L9" t="str">
-            <v>4 out of 5</v>
-          </cell>
           <cell r="M9">
             <v>4</v>
           </cell>
-          <cell r="N9" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="10">
-          <cell r="A10" t="str">
-            <v>LASA FOLDING TABLE SERVING STAND</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>KSh 1,274</v>
-          </cell>
-          <cell r="D10">
-            <v>1274</v>
-          </cell>
-          <cell r="E10" t="str">
-            <v>KSh 2,800</v>
-          </cell>
-          <cell r="F10">
-            <v>2800</v>
-          </cell>
-          <cell r="G10">
-            <v>1526</v>
-          </cell>
           <cell r="H10">
             <v>0.55000000000000004</v>
           </cell>
-          <cell r="I10" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J10">
-            <v>-5</v>
-          </cell>
           <cell r="K10">
             <v>5</v>
           </cell>
-          <cell r="L10" t="str">
-            <v>4.8 out of 5</v>
-          </cell>
           <cell r="M10">
             <v>4.8</v>
           </cell>
-          <cell r="N10" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="11">
-          <cell r="A11" t="str">
-            <v>13 In 1 Home Repair Tools Box Kit Set</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>KSh 1,600</v>
-          </cell>
-          <cell r="D11">
-            <v>1600</v>
-          </cell>
-          <cell r="E11" t="str">
-            <v>KSh 2,929</v>
-          </cell>
-          <cell r="F11">
-            <v>2929</v>
-          </cell>
-          <cell r="G11">
-            <v>1329</v>
-          </cell>
           <cell r="H11">
             <v>0.45</v>
           </cell>
-          <cell r="I11" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J11">
-            <v>-5</v>
-          </cell>
           <cell r="K11">
             <v>5</v>
           </cell>
-          <cell r="L11" t="str">
-            <v>3.8 out of 5</v>
-          </cell>
           <cell r="M11">
             <v>3.8</v>
           </cell>
-          <cell r="N11" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="12">
-          <cell r="A12" t="str">
-            <v>Genebre 115 In 1 Screwdriver Repairing Tool Set For IPhone Cellphone Hand Tool</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>Tools &amp; Hardware</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>KSh 799</v>
-          </cell>
-          <cell r="D12">
-            <v>799</v>
-          </cell>
-          <cell r="E12" t="str">
-            <v>KSh 999</v>
-          </cell>
-          <cell r="F12">
-            <v>999</v>
-          </cell>
-          <cell r="G12">
-            <v>200</v>
-          </cell>
           <cell r="H12">
             <v>0.2</v>
           </cell>
-          <cell r="I12" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J12">
-            <v>-12</v>
-          </cell>
           <cell r="K12">
             <v>12</v>
           </cell>
-          <cell r="L12" t="str">
-            <v>4.1 out of 5</v>
-          </cell>
           <cell r="M12">
             <v>4.0999999999999996</v>
           </cell>
-          <cell r="N12" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="13">
-          <cell r="A13" t="str">
-            <v>100 Pcs Crochet Hook Tool Set Knitting Hook Set With Box</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>KSh 990</v>
-          </cell>
-          <cell r="D13">
-            <v>990</v>
-          </cell>
-          <cell r="E13" t="str">
-            <v>KSh 1,500</v>
-          </cell>
-          <cell r="F13">
-            <v>1500</v>
-          </cell>
-          <cell r="G13">
-            <v>510</v>
-          </cell>
           <cell r="H13">
             <v>0.34</v>
           </cell>
-          <cell r="I13" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J13">
-            <v>-39</v>
-          </cell>
           <cell r="K13">
             <v>39</v>
           </cell>
-          <cell r="L13" t="str">
-            <v>4.7 out of 5</v>
-          </cell>
           <cell r="M13">
             <v>4.7</v>
           </cell>
-          <cell r="N13" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="14">
-          <cell r="A14" t="str">
-            <v>40cm Gold DIY Acrylic Wall Sticker Clock</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>KSh 552</v>
-          </cell>
-          <cell r="D14">
-            <v>552</v>
-          </cell>
-          <cell r="E14" t="str">
-            <v>KSh 1,035</v>
-          </cell>
-          <cell r="F14">
-            <v>1035</v>
-          </cell>
-          <cell r="G14">
-            <v>483</v>
-          </cell>
           <cell r="H14">
             <v>0.47</v>
           </cell>
-          <cell r="I14" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J14">
-            <v>-12</v>
-          </cell>
           <cell r="K14">
             <v>12</v>
           </cell>
-          <cell r="L14" t="str">
-            <v>4.8 out of 5</v>
-          </cell>
           <cell r="M14">
             <v>4.8</v>
           </cell>
-          <cell r="N14" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="15">
-          <cell r="A15" t="str">
-            <v>LASA Digital Thermometer And Hydrometer</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>KSh 501</v>
-          </cell>
-          <cell r="D15">
-            <v>501</v>
-          </cell>
-          <cell r="E15" t="str">
-            <v>KSh 860</v>
-          </cell>
-          <cell r="F15">
-            <v>860</v>
-          </cell>
-          <cell r="G15">
-            <v>359</v>
-          </cell>
           <cell r="H15">
             <v>0.42</v>
           </cell>
-          <cell r="I15" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J15">
-            <v>-6</v>
-          </cell>
           <cell r="K15">
             <v>6</v>
           </cell>
-          <cell r="L15" t="str">
-            <v>4.5 out of 5</v>
-          </cell>
           <cell r="M15">
             <v>4.5</v>
           </cell>
-          <cell r="N15" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="16">
-          <cell r="A16" t="str">
-            <v>Multifunction Laser Level With Adjustment Tripod</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>KSh 1,680</v>
-          </cell>
-          <cell r="D16">
-            <v>1680</v>
-          </cell>
-          <cell r="E16" t="str">
-            <v>KSh 2,499</v>
-          </cell>
-          <cell r="F16">
-            <v>2499</v>
-          </cell>
-          <cell r="G16">
-            <v>819</v>
-          </cell>
           <cell r="H16">
             <v>0.33</v>
           </cell>
-          <cell r="I16" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J16">
-            <v>-9</v>
-          </cell>
           <cell r="K16">
             <v>9</v>
           </cell>
-          <cell r="L16" t="str">
-            <v>4.2 out of 5</v>
-          </cell>
           <cell r="M16">
             <v>4.2</v>
           </cell>
-          <cell r="N16" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="17">
-          <cell r="A17" t="str">
-            <v>Anti-Skid Absorbent Insulation Coaster  For Home Office</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>KSh 332</v>
-          </cell>
-          <cell r="D17">
-            <v>332</v>
-          </cell>
-          <cell r="E17" t="str">
-            <v>KSh 684</v>
-          </cell>
-          <cell r="F17">
-            <v>684</v>
-          </cell>
-          <cell r="G17">
-            <v>352</v>
-          </cell>
           <cell r="H17">
             <v>0.51</v>
           </cell>
-          <cell r="I17" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J17">
-            <v>-2</v>
-          </cell>
           <cell r="K17">
             <v>2</v>
           </cell>
-          <cell r="L17" t="str">
-            <v>5 out of 5</v>
-          </cell>
           <cell r="M17">
             <v>5</v>
           </cell>
-          <cell r="N17" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="18">
-          <cell r="A18" t="str">
-            <v>Peacock  Throw Pillow Cushion Case For Home Car</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>KSh 195</v>
-          </cell>
-          <cell r="D18">
-            <v>195</v>
-          </cell>
-          <cell r="E18" t="str">
-            <v>KSh 360</v>
-          </cell>
-          <cell r="F18">
-            <v>360</v>
-          </cell>
-          <cell r="G18">
-            <v>165</v>
-          </cell>
           <cell r="H18">
             <v>0.46</v>
           </cell>
-          <cell r="I18" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J18">
-            <v>-2</v>
-          </cell>
           <cell r="K18">
             <v>2</v>
           </cell>
-          <cell r="L18" t="str">
-            <v>5 out of 5</v>
-          </cell>
           <cell r="M18">
             <v>5</v>
           </cell>
-          <cell r="N18" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="19">
-          <cell r="A19" t="str">
-            <v>LASA Aluminum Folding Truck Hand Cart - 68kg Max</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>KSh 2,025</v>
-          </cell>
-          <cell r="D19">
-            <v>2025</v>
-          </cell>
-          <cell r="E19" t="str">
-            <v>KSh 3,971</v>
-          </cell>
-          <cell r="F19">
-            <v>3971</v>
-          </cell>
-          <cell r="G19">
-            <v>1946</v>
-          </cell>
           <cell r="H19">
             <v>0.49</v>
           </cell>
-          <cell r="I19" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J19">
-            <v>-3</v>
-          </cell>
           <cell r="K19">
             <v>3</v>
           </cell>
-          <cell r="L19" t="str">
-            <v>5 out of 5</v>
-          </cell>
           <cell r="M19">
             <v>5</v>
           </cell>
-          <cell r="N19" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="20">
-          <cell r="A20" t="str">
-            <v>LED Wall Digital Alarm Clock Study Home 12 / 24H Clock Calendar</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>KSh 2,999</v>
-          </cell>
-          <cell r="D20">
-            <v>2999</v>
-          </cell>
-          <cell r="E20" t="str">
-            <v>KSh 3,699</v>
-          </cell>
-          <cell r="F20">
-            <v>3699</v>
-          </cell>
-          <cell r="G20">
-            <v>700</v>
-          </cell>
           <cell r="H20">
             <v>0.19</v>
           </cell>
-          <cell r="I20" t="str">
-            <v>Low</v>
-          </cell>
-          <cell r="J20">
-            <v>-5</v>
-          </cell>
           <cell r="K20">
             <v>5</v>
           </cell>
-          <cell r="L20" t="str">
-            <v>4.6 out of 5</v>
-          </cell>
           <cell r="M20">
             <v>4.5999999999999996</v>
           </cell>
-          <cell r="N20" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="21">
-          <cell r="A21" t="str">
-            <v>3D Waterproof EVA Plastic Shower Curtain 1.8*2Mtrs</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>KSh 998</v>
-          </cell>
-          <cell r="D21">
-            <v>998</v>
-          </cell>
-          <cell r="E21" t="str">
-            <v>KSh 1,966</v>
-          </cell>
-          <cell r="F21">
-            <v>1966</v>
-          </cell>
-          <cell r="G21">
-            <v>968</v>
-          </cell>
           <cell r="H21">
             <v>0.49</v>
           </cell>
-          <cell r="I21" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J21">
-            <v>-44</v>
-          </cell>
           <cell r="K21">
             <v>44</v>
           </cell>
-          <cell r="L21" t="str">
-            <v>4.6 out of 5</v>
-          </cell>
           <cell r="M21">
             <v>4.5999999999999996</v>
           </cell>
-          <cell r="N21" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="22">
-          <cell r="A22" t="str">
-            <v>3PCS Single Head Knitting Crochet Sweater Needle Set</v>
-          </cell>
-          <cell r="B22" t="str">
-            <v>Craft &amp; DIY</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>KSh 38</v>
-          </cell>
-          <cell r="D22">
-            <v>38</v>
-          </cell>
-          <cell r="E22" t="str">
-            <v>KSh 80</v>
-          </cell>
-          <cell r="F22">
-            <v>80</v>
-          </cell>
-          <cell r="G22">
-            <v>42</v>
-          </cell>
           <cell r="H22">
             <v>0.53</v>
           </cell>
-          <cell r="I22" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J22">
-            <v>-13</v>
-          </cell>
           <cell r="K22">
             <v>13</v>
           </cell>
-          <cell r="L22" t="str">
-            <v>3.3 out of 5</v>
-          </cell>
           <cell r="M22">
             <v>3.3</v>
           </cell>
-          <cell r="N22" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="23">
-          <cell r="A23" t="str">
-            <v>4pcs Bathroom/Kitchen Towel Rack,Roll Paper Holder,Towel Bars,Hook</v>
-          </cell>
-          <cell r="B23" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>KSh 1,860</v>
-          </cell>
-          <cell r="D23">
-            <v>1860</v>
-          </cell>
-          <cell r="E23" t="str">
-            <v>KSh 3,220</v>
-          </cell>
-          <cell r="F23">
-            <v>3220</v>
-          </cell>
-          <cell r="G23">
-            <v>1360</v>
-          </cell>
           <cell r="H23">
             <v>0.42</v>
           </cell>
-          <cell r="I23" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K23" t="str">
             <v/>
           </cell>
           <cell r="M23" t="str">
             <v/>
           </cell>
-          <cell r="N23" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="24">
-          <cell r="A24" t="str">
-            <v>LED Romantic Spaceship Starry Sky Projector,Children's Bedroom Night Light-Blue</v>
-          </cell>
-          <cell r="B24" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>KSh 880</v>
-          </cell>
-          <cell r="D24">
-            <v>880</v>
-          </cell>
-          <cell r="E24" t="str">
-            <v>KSh 1,350</v>
-          </cell>
-          <cell r="F24">
-            <v>1350</v>
-          </cell>
-          <cell r="G24">
-            <v>470</v>
-          </cell>
           <cell r="H24">
             <v>0.35</v>
           </cell>
-          <cell r="I24" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J24">
-            <v>-6</v>
-          </cell>
           <cell r="K24">
             <v>6</v>
           </cell>
-          <cell r="L24" t="str">
-            <v>4 out of 5</v>
-          </cell>
           <cell r="M24">
             <v>4</v>
           </cell>
-          <cell r="N24" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="25">
-          <cell r="A25" t="str">
-            <v>Foldable Overbed Table/Desk</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>KSh 1,650</v>
-          </cell>
-          <cell r="D25">
-            <v>1650</v>
-          </cell>
-          <cell r="E25" t="str">
-            <v>KSh 2,150</v>
-          </cell>
-          <cell r="F25">
-            <v>2150</v>
-          </cell>
-          <cell r="G25">
-            <v>500</v>
-          </cell>
           <cell r="H25">
             <v>0.23</v>
           </cell>
-          <cell r="I25" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J25">
-            <v>-14</v>
-          </cell>
           <cell r="K25">
             <v>14</v>
           </cell>
-          <cell r="L25" t="str">
-            <v>4.4 out of 5</v>
-          </cell>
           <cell r="M25">
             <v>4.4000000000000004</v>
           </cell>
-          <cell r="N25" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="26">
-          <cell r="A26" t="str">
-            <v>LASA 3 Tier Bamboo Shoe Bench Storage Shelf</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>KSh 2,048</v>
-          </cell>
-          <cell r="D26">
-            <v>2048</v>
-          </cell>
-          <cell r="E26" t="str">
-            <v>KSh 4,500</v>
-          </cell>
-          <cell r="F26">
-            <v>4500</v>
-          </cell>
-          <cell r="G26">
-            <v>2452</v>
-          </cell>
           <cell r="H26">
             <v>0.54</v>
           </cell>
-          <cell r="I26" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J26">
-            <v>-7</v>
-          </cell>
           <cell r="K26">
             <v>7</v>
           </cell>
-          <cell r="L26" t="str">
-            <v>4.3 out of 5</v>
-          </cell>
           <cell r="M26">
             <v>4.3</v>
           </cell>
-          <cell r="N26" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="27">
-          <cell r="A27" t="str">
-            <v>Electronic Digital Display Vernier Caliper</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>KSh 420</v>
-          </cell>
-          <cell r="D27">
-            <v>420</v>
-          </cell>
-          <cell r="E27" t="str">
-            <v>KSh 647</v>
-          </cell>
-          <cell r="F27">
-            <v>647</v>
-          </cell>
-          <cell r="G27">
-            <v>227</v>
-          </cell>
           <cell r="H27">
             <v>0.35</v>
           </cell>
-          <cell r="I27" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J27">
-            <v>-49</v>
-          </cell>
           <cell r="K27">
             <v>49</v>
           </cell>
-          <cell r="L27" t="str">
-            <v>4.6 out of 5</v>
-          </cell>
           <cell r="M27">
             <v>4.5999999999999996</v>
           </cell>
-          <cell r="N27" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="28">
-          <cell r="A28" t="str">
-            <v>Portable Wardrobe Nonwoven With 3 Hanging Rods And 6 Storage Shelves</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>KSh 2,880</v>
-          </cell>
-          <cell r="D28">
-            <v>2880</v>
-          </cell>
-          <cell r="E28" t="str">
-            <v>KSh 3,520</v>
-          </cell>
-          <cell r="F28">
-            <v>3520</v>
-          </cell>
-          <cell r="G28">
-            <v>640</v>
-          </cell>
           <cell r="H28">
             <v>0.18</v>
           </cell>
-          <cell r="I28" t="str">
-            <v>Low</v>
-          </cell>
-          <cell r="J28">
-            <v>-12</v>
-          </cell>
           <cell r="K28">
             <v>12</v>
           </cell>
-          <cell r="L28" t="str">
-            <v>3.8 out of 5</v>
-          </cell>
           <cell r="M28">
             <v>3.8</v>
           </cell>
-          <cell r="N28" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="29">
-          <cell r="A29" t="str">
-            <v>12 Litre Black Insulated Lunch Box</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>KSh 1,350</v>
-          </cell>
-          <cell r="D29">
-            <v>1350</v>
-          </cell>
-          <cell r="E29" t="str">
-            <v>KSh 1,990</v>
-          </cell>
-          <cell r="F29">
-            <v>1990</v>
-          </cell>
-          <cell r="G29">
-            <v>640</v>
-          </cell>
           <cell r="H29">
             <v>0.32</v>
           </cell>
-          <cell r="I29" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J29">
-            <v>-13</v>
-          </cell>
           <cell r="K29">
             <v>13</v>
           </cell>
-          <cell r="L29" t="str">
-            <v>3.8 out of 5</v>
-          </cell>
           <cell r="M29">
             <v>3.8</v>
           </cell>
-          <cell r="N29" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="30">
-          <cell r="A30" t="str">
-            <v>52 Pieces Cake Decorating Tool Set Gift Kit Baking Supplies</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>KSh 1,758</v>
-          </cell>
-          <cell r="D30">
-            <v>1758</v>
-          </cell>
-          <cell r="E30" t="str">
-            <v>KSh 2,499</v>
-          </cell>
-          <cell r="F30">
-            <v>2499</v>
-          </cell>
-          <cell r="G30">
-            <v>741</v>
-          </cell>
           <cell r="H30">
             <v>0.3</v>
           </cell>
-          <cell r="I30" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J30">
-            <v>-20</v>
-          </cell>
           <cell r="K30">
             <v>20</v>
           </cell>
-          <cell r="L30" t="str">
-            <v>4.1 out of 5</v>
-          </cell>
           <cell r="M30">
             <v>4.0999999999999996</v>
           </cell>
-          <cell r="N30" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="31">
-          <cell r="A31" t="str">
-            <v>MultiFunctional Storage Rack Multi-layer Bookshelf</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>KSh 2,200</v>
-          </cell>
-          <cell r="D31">
-            <v>2200</v>
-          </cell>
-          <cell r="E31" t="str">
-            <v>KSh 4,080</v>
-          </cell>
-          <cell r="F31">
-            <v>4080</v>
-          </cell>
-          <cell r="G31">
-            <v>1880</v>
-          </cell>
           <cell r="H31">
             <v>0.46</v>
           </cell>
-          <cell r="I31" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K31" t="str">
             <v/>
           </cell>
           <cell r="M31" t="str">
             <v/>
           </cell>
-          <cell r="N31" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="32">
-          <cell r="A32" t="str">
-            <v>Exfoliate And Exfoliate Face Towel - Black</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>KSh 185</v>
-          </cell>
-          <cell r="D32">
-            <v>185</v>
-          </cell>
-          <cell r="E32" t="str">
-            <v>KSh 382</v>
-          </cell>
-          <cell r="F32">
-            <v>382</v>
-          </cell>
-          <cell r="G32">
-            <v>197</v>
-          </cell>
           <cell r="H32">
             <v>0.52</v>
           </cell>
-          <cell r="I32" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J32">
-            <v>-9</v>
-          </cell>
           <cell r="K32">
             <v>9</v>
           </cell>
-          <cell r="L32" t="str">
-            <v>4.3 out of 5</v>
-          </cell>
           <cell r="M32">
             <v>4.3</v>
           </cell>
-          <cell r="N32" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="33">
-          <cell r="A33" t="str">
-            <v>12 Litre Insulated Lunch Box Grey</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>KSh 980</v>
-          </cell>
-          <cell r="D33">
-            <v>980</v>
-          </cell>
-          <cell r="E33" t="str">
-            <v>KSh 1,490</v>
-          </cell>
-          <cell r="F33">
-            <v>1490</v>
-          </cell>
-          <cell r="G33">
-            <v>510</v>
-          </cell>
           <cell r="H33">
             <v>0.34</v>
           </cell>
-          <cell r="I33" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J33">
-            <v>-12</v>
-          </cell>
           <cell r="K33">
             <v>12</v>
           </cell>
-          <cell r="L33" t="str">
-            <v>4.7 out of 5</v>
-          </cell>
           <cell r="M33">
             <v>4.7</v>
           </cell>
-          <cell r="N33" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="34">
-          <cell r="A34" t="str">
-            <v>LED Eye Protection  Desk Lamp , Study, Reading, USB Fan - Double Pen Holder</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>Cleaning &amp; Appliances</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>KSh 1,820</v>
-          </cell>
-          <cell r="D34">
-            <v>1820</v>
-          </cell>
-          <cell r="E34" t="str">
-            <v>KSh 3,490</v>
-          </cell>
-          <cell r="F34">
-            <v>3490</v>
-          </cell>
-          <cell r="G34">
-            <v>1670</v>
-          </cell>
           <cell r="H34">
             <v>0.48</v>
           </cell>
-          <cell r="I34" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J34">
-            <v>-9</v>
-          </cell>
           <cell r="K34">
             <v>9</v>
           </cell>
-          <cell r="L34" t="str">
-            <v>4.3 out of 5</v>
-          </cell>
           <cell r="M34">
             <v>4.3</v>
           </cell>
-          <cell r="N34" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="35">
-          <cell r="A35" t="str">
-            <v>53Pcs/Set Yarn Knitting Crochet Hooks With Bag - Fortune Cat</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>KSh 1,940</v>
-          </cell>
-          <cell r="D35">
-            <v>1940</v>
-          </cell>
-          <cell r="E35" t="str">
-            <v>KSh 2,650</v>
-          </cell>
-          <cell r="F35">
-            <v>2650</v>
-          </cell>
-          <cell r="G35">
-            <v>710</v>
-          </cell>
           <cell r="H35">
             <v>0.27</v>
           </cell>
-          <cell r="I35" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J35">
-            <v>-20</v>
-          </cell>
           <cell r="K35">
             <v>20</v>
           </cell>
-          <cell r="L35" t="str">
-            <v>4.7 out of 5</v>
-          </cell>
           <cell r="M35">
             <v>4.7</v>
           </cell>
-          <cell r="N35" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="36">
-          <cell r="A36" t="str">
-            <v>53 Pieces/Set Yarn Knitting Crochet Hooks With Bag - Pansies</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>KSh 1,980</v>
-          </cell>
-          <cell r="D36">
-            <v>1980</v>
-          </cell>
-          <cell r="E36" t="str">
-            <v>KSh 2,699</v>
-          </cell>
-          <cell r="F36">
-            <v>2699</v>
-          </cell>
-          <cell r="G36">
-            <v>719</v>
-          </cell>
           <cell r="H36">
             <v>0.27</v>
           </cell>
-          <cell r="I36" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J36">
-            <v>-32</v>
-          </cell>
           <cell r="K36">
             <v>32</v>
           </cell>
-          <cell r="L36" t="str">
-            <v>4.5 out of 5</v>
-          </cell>
           <cell r="M36">
             <v>4.5</v>
           </cell>
-          <cell r="N36" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="37">
-          <cell r="A37" t="str">
-            <v>DIY File Folder, Office Drawer File Holder, Pen Holder, Desktop Storage Rack</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>KSh 1,620</v>
-          </cell>
-          <cell r="D37">
-            <v>1620</v>
-          </cell>
-          <cell r="E37" t="str">
-            <v>KSh 2,690</v>
-          </cell>
-          <cell r="F37">
-            <v>2690</v>
-          </cell>
-          <cell r="G37">
-            <v>1070</v>
-          </cell>
           <cell r="H37">
             <v>0.4</v>
           </cell>
-          <cell r="I37" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J37">
-            <v>-1</v>
-          </cell>
           <cell r="K37">
             <v>1</v>
           </cell>
-          <cell r="L37" t="str">
-            <v>5 out of 5</v>
-          </cell>
           <cell r="M37">
             <v>5</v>
           </cell>
-          <cell r="N37" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="38">
-          <cell r="A38" t="str">
-            <v>Classic Black Cat Cotton Hemp Pillow Case For Home Car</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>KSh 171</v>
-          </cell>
-          <cell r="D38">
-            <v>171</v>
-          </cell>
-          <cell r="E38" t="str">
-            <v>KSh 360</v>
-          </cell>
-          <cell r="F38">
-            <v>360</v>
-          </cell>
-          <cell r="G38">
-            <v>189</v>
-          </cell>
           <cell r="H38">
             <v>0.53</v>
           </cell>
-          <cell r="I38" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J38">
-            <v>-2</v>
-          </cell>
           <cell r="K38">
             <v>2</v>
           </cell>
-          <cell r="L38" t="str">
-            <v>5 out of 5</v>
-          </cell>
           <cell r="M38">
             <v>5</v>
           </cell>
-          <cell r="N38" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="39">
-          <cell r="A39" t="str">
-            <v>Punch-free Great Load Bearing Bathroom Storage Rack Wall Shelf-White</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>KSh 389</v>
-          </cell>
-          <cell r="D39">
-            <v>389</v>
-          </cell>
-          <cell r="E39" t="str">
-            <v>KSh 656</v>
-          </cell>
-          <cell r="F39">
-            <v>656</v>
-          </cell>
-          <cell r="G39">
-            <v>267</v>
-          </cell>
           <cell r="H39">
             <v>0.41</v>
           </cell>
-          <cell r="I39" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J39">
-            <v>-36</v>
-          </cell>
           <cell r="K39">
             <v>36</v>
           </cell>
-          <cell r="L39" t="str">
-            <v>4.3 out of 5</v>
-          </cell>
           <cell r="M39">
             <v>4.3</v>
           </cell>
-          <cell r="N39" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="40">
-          <cell r="A40" t="str">
-            <v>1/2/3 Seater Elastic Sofa Cover,Living Room/Home Decor Chair Cover-Grey</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>KSh 1,800</v>
-          </cell>
-          <cell r="D40">
-            <v>1800</v>
-          </cell>
-          <cell r="E40" t="str">
-            <v>KSh 2,700</v>
-          </cell>
-          <cell r="F40">
-            <v>2700</v>
-          </cell>
-          <cell r="G40">
-            <v>900</v>
-          </cell>
           <cell r="H40">
             <v>0.38</v>
           </cell>
-          <cell r="I40" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J40">
-            <v>-2</v>
-          </cell>
           <cell r="K40">
             <v>2</v>
           </cell>
-          <cell r="L40" t="str">
-            <v>4.5 out of 5</v>
-          </cell>
           <cell r="M40">
             <v>4.5</v>
           </cell>
-          <cell r="N40" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="41">
-          <cell r="A41" t="str">
-            <v>LASA Stainless Steel Double Wall Mount Soap Dispenser - 500ml</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>KSh 2,750</v>
-          </cell>
-          <cell r="D41">
-            <v>2750</v>
-          </cell>
-          <cell r="E41" t="str">
-            <v>KSh 4,471</v>
-          </cell>
-          <cell r="F41">
-            <v>4471</v>
-          </cell>
-          <cell r="G41">
-            <v>1721</v>
-          </cell>
           <cell r="H41">
             <v>0.38</v>
           </cell>
-          <cell r="I41" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K41" t="str">
             <v/>
           </cell>
           <cell r="M41" t="str">
             <v/>
           </cell>
-          <cell r="N41" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="42">
-          <cell r="A42" t="str">
-            <v>4M Float Switch Water Level Controller -Water Tank</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>KSh 475</v>
-          </cell>
-          <cell r="D42">
-            <v>475</v>
-          </cell>
-          <cell r="E42" t="str">
-            <v>KSh 931</v>
-          </cell>
-          <cell r="F42">
-            <v>931</v>
-          </cell>
-          <cell r="G42">
-            <v>456</v>
-          </cell>
           <cell r="H42">
             <v>0.49</v>
           </cell>
-          <cell r="I42" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K42" t="str">
             <v/>
           </cell>
           <cell r="M42" t="str">
             <v/>
           </cell>
-          <cell r="N42" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="43">
-          <cell r="A43" t="str">
-            <v>Modern Sofa Throw Pillow Cover-45x45cm-Blue&amp;Red</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>KSh 238</v>
-          </cell>
-          <cell r="D43">
-            <v>238</v>
-          </cell>
-          <cell r="E43" t="str">
-            <v>KSh 476</v>
-          </cell>
-          <cell r="F43">
-            <v>476</v>
-          </cell>
-          <cell r="G43">
-            <v>238</v>
-          </cell>
           <cell r="H43">
             <v>0.5</v>
           </cell>
-          <cell r="I43" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K43" t="str">
             <v/>
           </cell>
           <cell r="M43" t="str">
             <v/>
           </cell>
-          <cell r="N43" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="44">
-          <cell r="A44" t="str">
-            <v>Balloon Insert, Birthday Party Balloon Set, PU Leather</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>KSh 610</v>
-          </cell>
-          <cell r="D44">
-            <v>610</v>
-          </cell>
-          <cell r="E44" t="str">
-            <v>KSh 1,060</v>
-          </cell>
-          <cell r="F44">
-            <v>1060</v>
-          </cell>
-          <cell r="G44">
-            <v>450</v>
-          </cell>
           <cell r="H44">
             <v>0.42</v>
           </cell>
-          <cell r="I44" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K44" t="str">
             <v/>
           </cell>
           <cell r="M44" t="str">
             <v/>
           </cell>
-          <cell r="N44" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="45">
-          <cell r="A45" t="str">
-            <v>Shower Cap Wide Elastic Band Cover Reusable Bashroom Cap</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>KSh 2,132</v>
-          </cell>
-          <cell r="D45">
-            <v>2132</v>
-          </cell>
-          <cell r="E45" t="str">
-            <v>KSh 2,169</v>
-          </cell>
-          <cell r="F45">
-            <v>2169</v>
-          </cell>
-          <cell r="G45">
-            <v>37</v>
-          </cell>
           <cell r="H45">
             <v>0.02</v>
           </cell>
-          <cell r="I45" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K45" t="str">
             <v/>
           </cell>
           <cell r="M45" t="str">
             <v/>
           </cell>
-          <cell r="N45" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="46">
-          <cell r="A46" t="str">
-            <v>Christmas Elk Fence Yard Lawn Decorations Cute For Holidays</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>KSh 999</v>
-          </cell>
-          <cell r="D46">
-            <v>999</v>
-          </cell>
-          <cell r="E46" t="str">
-            <v>KSh 2,000</v>
-          </cell>
-          <cell r="F46">
-            <v>2000</v>
-          </cell>
-          <cell r="G46">
-            <v>1001</v>
-          </cell>
           <cell r="H46">
             <v>0.5</v>
           </cell>
-          <cell r="I46" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K46" t="str">
             <v/>
           </cell>
           <cell r="M46" t="str">
             <v/>
           </cell>
-          <cell r="N46" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="47">
-          <cell r="A47" t="str">
-            <v>60W Hot Melt Glue Sprayer - Efficient And Stable Glue Dispensing</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C47" t="str">
-            <v>KSh 1,190</v>
-          </cell>
-          <cell r="D47">
-            <v>1190</v>
-          </cell>
-          <cell r="E47" t="str">
-            <v>KSh 1,785</v>
-          </cell>
-          <cell r="F47">
-            <v>1785</v>
-          </cell>
-          <cell r="G47">
-            <v>595</v>
-          </cell>
           <cell r="H47">
             <v>0.33</v>
           </cell>
-          <cell r="I47" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K47" t="str">
             <v/>
           </cell>
           <cell r="M47" t="str">
             <v/>
           </cell>
-          <cell r="N47" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="48">
-          <cell r="A48" t="str">
-            <v>Car Phone Charging Stand</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C48" t="str">
-            <v>KSh 671</v>
-          </cell>
-          <cell r="D48">
-            <v>671</v>
-          </cell>
-          <cell r="E48" t="str">
-            <v>KSh 1,316</v>
-          </cell>
-          <cell r="F48">
-            <v>1316</v>
-          </cell>
-          <cell r="G48">
-            <v>645</v>
-          </cell>
           <cell r="H48">
             <v>0.49</v>
           </cell>
-          <cell r="I48" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K48" t="str">
             <v/>
           </cell>
           <cell r="M48" t="str">
             <v/>
           </cell>
-          <cell r="N48" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="49">
-          <cell r="A49" t="str">
-            <v>2pcs Solar Street Light Flood Light Outdoor</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C49" t="str">
-            <v>KSh 1,200</v>
-          </cell>
-          <cell r="D49">
-            <v>1200</v>
-          </cell>
-          <cell r="E49" t="str">
-            <v>KSh 1,950</v>
-          </cell>
-          <cell r="F49">
-            <v>1950</v>
-          </cell>
-          <cell r="G49">
-            <v>750</v>
-          </cell>
           <cell r="H49">
             <v>0.38</v>
           </cell>
-          <cell r="I49" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K49" t="str">
             <v/>
           </cell>
           <cell r="M49" t="str">
             <v/>
           </cell>
-          <cell r="N49" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="50">
-          <cell r="A50" t="str">
-            <v>Creative Owl Shape Keychain Black</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C50" t="str">
-            <v>KSh 199</v>
-          </cell>
-          <cell r="D50">
-            <v>199</v>
-          </cell>
-          <cell r="E50" t="str">
-            <v>KSh 504</v>
-          </cell>
-          <cell r="F50">
-            <v>504</v>
-          </cell>
-          <cell r="G50">
-            <v>305</v>
-          </cell>
           <cell r="H50">
             <v>0.61</v>
           </cell>
-          <cell r="I50" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K50" t="str">
             <v/>
           </cell>
           <cell r="M50" t="str">
             <v/>
           </cell>
-          <cell r="N50" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="51">
-          <cell r="A51" t="str">
-            <v>Brush &amp; Paintbrush Cleaning Tool Pink</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C51" t="str">
-            <v>KSh 299</v>
-          </cell>
-          <cell r="D51">
-            <v>299</v>
-          </cell>
-          <cell r="E51" t="str">
-            <v>KSh 600</v>
-          </cell>
-          <cell r="F51">
-            <v>600</v>
-          </cell>
-          <cell r="G51">
-            <v>301</v>
-          </cell>
           <cell r="H51">
             <v>0.5</v>
           </cell>
-          <cell r="I51" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K51" t="str">
             <v/>
           </cell>
           <cell r="M51" t="str">
             <v/>
           </cell>
-          <cell r="N51" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="52">
-          <cell r="A52" t="str">
-            <v>Pen Grips For Kids Pen Grip Posture Correction Tool For Kids</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C52" t="str">
-            <v>KSh 1,660</v>
-          </cell>
-          <cell r="D52">
-            <v>1660</v>
-          </cell>
-          <cell r="E52" t="str">
-            <v>KSh 1,699</v>
-          </cell>
-          <cell r="F52">
-            <v>1699</v>
-          </cell>
-          <cell r="G52">
-            <v>39</v>
-          </cell>
           <cell r="H52">
             <v>0.02</v>
           </cell>
-          <cell r="I52" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K52" t="str">
             <v/>
           </cell>
           <cell r="M52" t="str">
             <v/>
           </cell>
-          <cell r="N52" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="53">
-          <cell r="A53" t="str">
-            <v>Pilates Cloth Bag Waterproof Durable High Capacity Purple</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C53" t="str">
-            <v>KSh 299</v>
-          </cell>
-          <cell r="D53">
-            <v>299</v>
-          </cell>
-          <cell r="E53" t="str">
-            <v>KSh 384</v>
-          </cell>
-          <cell r="F53">
-            <v>384</v>
-          </cell>
-          <cell r="G53">
-            <v>85</v>
-          </cell>
           <cell r="H53">
             <v>0.22</v>
           </cell>
-          <cell r="I53" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K53" t="str">
             <v/>
           </cell>
           <cell r="M53" t="str">
             <v/>
           </cell>
-          <cell r="N53" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="54">
-          <cell r="A54" t="str">
-            <v>Multi-purpose Rice Drainage Basket And Fruit And Vegetable Drainage Sieve</v>
-          </cell>
-          <cell r="B54" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C54" t="str">
-            <v>KSh 1,459</v>
-          </cell>
-          <cell r="D54">
-            <v>1459</v>
-          </cell>
-          <cell r="E54" t="str">
-            <v>KSh 1,499</v>
-          </cell>
-          <cell r="F54">
-            <v>1499</v>
-          </cell>
-          <cell r="G54">
-            <v>40</v>
-          </cell>
           <cell r="H54">
             <v>0.03</v>
           </cell>
-          <cell r="I54" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K54" t="str">
             <v/>
           </cell>
           <cell r="M54" t="str">
             <v/>
           </cell>
-          <cell r="N54" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="55">
-          <cell r="A55" t="str">
-            <v>Cute Christmas Fence Garden Decorations For Holiday Home</v>
-          </cell>
-          <cell r="B55" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C55" t="str">
-            <v>KSh 799</v>
-          </cell>
-          <cell r="D55">
-            <v>799</v>
-          </cell>
-          <cell r="E55" t="str">
-            <v>KSh 1,343</v>
-          </cell>
-          <cell r="F55">
-            <v>1343</v>
-          </cell>
-          <cell r="G55">
-            <v>544</v>
-          </cell>
           <cell r="H55">
             <v>0.41</v>
           </cell>
-          <cell r="I55" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K55" t="str">
             <v/>
           </cell>
           <cell r="M55" t="str">
             <v/>
           </cell>
-          <cell r="N55" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="56">
-          <cell r="A56" t="str">
-            <v>Simple Metal Dog Art Sculpture Decoration For Home Office</v>
-          </cell>
-          <cell r="B56" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C56" t="str">
-            <v>KSh 499</v>
-          </cell>
-          <cell r="D56">
-            <v>499</v>
-          </cell>
-          <cell r="E56" t="str">
-            <v>KSh 900</v>
-          </cell>
-          <cell r="F56">
-            <v>900</v>
-          </cell>
-          <cell r="G56">
-            <v>401</v>
-          </cell>
           <cell r="H56">
             <v>0.45</v>
           </cell>
-          <cell r="I56" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K56" t="str">
             <v/>
           </cell>
           <cell r="M56" t="str">
             <v/>
           </cell>
-          <cell r="N56" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="57">
-          <cell r="A57" t="str">
-            <v>Christmas Fence Garden Decorations Outdoor For Holiday Home</v>
-          </cell>
-          <cell r="B57" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C57" t="str">
-            <v>KSh 699</v>
-          </cell>
-          <cell r="D57">
-            <v>699</v>
-          </cell>
-          <cell r="E57" t="str">
-            <v>KSh 1,343</v>
-          </cell>
-          <cell r="F57">
-            <v>1343</v>
-          </cell>
-          <cell r="G57">
-            <v>644</v>
-          </cell>
           <cell r="H57">
             <v>0.48</v>
           </cell>
-          <cell r="I57" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K57" t="str">
             <v/>
           </cell>
           <cell r="M57" t="str">
             <v/>
           </cell>
-          <cell r="N57" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="58">
-          <cell r="A58" t="str">
-            <v>Angle Measuring Tool Full Metal Multi Angle Measuring Tool</v>
-          </cell>
-          <cell r="B58" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C58" t="str">
-            <v>KSh 799</v>
-          </cell>
-          <cell r="D58">
-            <v>799</v>
-          </cell>
-          <cell r="E58" t="str">
-            <v>KSh 1,567</v>
-          </cell>
-          <cell r="F58">
-            <v>1567</v>
-          </cell>
-          <cell r="G58">
-            <v>768</v>
-          </cell>
           <cell r="H58">
             <v>0.49</v>
           </cell>
-          <cell r="I58" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K58" t="str">
             <v/>
           </cell>
           <cell r="M58" t="str">
             <v/>
           </cell>
-          <cell r="N58" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="59">
-          <cell r="A59" t="str">
-            <v>12V 19500rpm Handheld Electric Angle Grinder Tool - UK - Yellow/Black</v>
-          </cell>
-          <cell r="B59" t="str">
-            <v>Tools &amp; Hardware</v>
-          </cell>
-          <cell r="C59" t="str">
-            <v>KSh 2,799</v>
-          </cell>
-          <cell r="D59">
-            <v>2799</v>
-          </cell>
-          <cell r="E59" t="str">
-            <v>KSh 3,810</v>
-          </cell>
-          <cell r="F59">
-            <v>3810</v>
-          </cell>
-          <cell r="G59">
-            <v>1011</v>
-          </cell>
           <cell r="H59">
             <v>0.27</v>
           </cell>
-          <cell r="I59" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K59" t="str">
             <v/>
           </cell>
           <cell r="M59" t="str">
             <v/>
           </cell>
-          <cell r="N59" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="60">
-          <cell r="A60" t="str">
-            <v>5 Pieces/set Of Stainless Steel Induction Cooker Pots</v>
-          </cell>
-          <cell r="B60" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C60" t="str">
-            <v>KSh 2,170</v>
-          </cell>
-          <cell r="D60">
-            <v>2170</v>
-          </cell>
-          <cell r="E60" t="str">
-            <v>KSh 2,500</v>
-          </cell>
-          <cell r="F60">
-            <v>2500</v>
-          </cell>
-          <cell r="G60">
-            <v>330</v>
-          </cell>
           <cell r="H60">
             <v>0.13</v>
           </cell>
-          <cell r="I60" t="str">
-            <v>Low</v>
-          </cell>
-          <cell r="J60">
-            <v>-6</v>
-          </cell>
           <cell r="K60">
             <v>6</v>
           </cell>
-          <cell r="L60" t="str">
-            <v>2.5 out of 5</v>
-          </cell>
           <cell r="M60">
             <v>2.5</v>
           </cell>
-          <cell r="N60" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="61">
-          <cell r="A61" t="str">
-            <v>Mythco 120COB Solar Wall Ligt With Motion Sensor And Remote Control 3 Modes</v>
-          </cell>
-          <cell r="B61" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C61" t="str">
-            <v>KSh 458</v>
-          </cell>
-          <cell r="D61">
-            <v>458</v>
-          </cell>
-          <cell r="E61" t="str">
-            <v>KSh 986</v>
-          </cell>
-          <cell r="F61">
-            <v>986</v>
-          </cell>
-          <cell r="G61">
-            <v>528</v>
-          </cell>
           <cell r="H61">
             <v>0.54</v>
           </cell>
-          <cell r="I61" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J61">
-            <v>-10</v>
-          </cell>
           <cell r="K61">
             <v>10</v>
           </cell>
-          <cell r="L61" t="str">
-            <v>3 out of 5</v>
-          </cell>
           <cell r="M61">
             <v>3</v>
           </cell>
-          <cell r="N61" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="62">
-          <cell r="A62" t="str">
-            <v>5-PCS Stainless Steel Cooking Pot Set With Steamed Slices</v>
-          </cell>
-          <cell r="B62" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C62" t="str">
-            <v>KSh 2,115</v>
-          </cell>
-          <cell r="D62">
-            <v>2115</v>
-          </cell>
-          <cell r="E62" t="str">
-            <v>KSh 4,700</v>
-          </cell>
-          <cell r="F62">
-            <v>4700</v>
-          </cell>
-          <cell r="G62">
-            <v>2585</v>
-          </cell>
           <cell r="H62">
             <v>0.55000000000000004</v>
           </cell>
-          <cell r="I62" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J62">
-            <v>-13</v>
-          </cell>
           <cell r="K62">
             <v>13</v>
           </cell>
-          <cell r="L62" t="str">
-            <v>2.1 out of 5</v>
-          </cell>
           <cell r="M62">
             <v>2.1</v>
           </cell>
-          <cell r="N62" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="63">
-          <cell r="A63" t="str">
-            <v>120W Cordless Vacuum Cleaners Handheld Electric Vacuum Cleaner</v>
-          </cell>
-          <cell r="B63" t="str">
-            <v>Cleaning &amp; Appliances</v>
-          </cell>
-          <cell r="C63" t="str">
-            <v>KSh 445</v>
-          </cell>
-          <cell r="D63">
-            <v>445</v>
-          </cell>
-          <cell r="E63" t="str">
-            <v>KSh 873</v>
-          </cell>
-          <cell r="F63">
-            <v>873</v>
-          </cell>
-          <cell r="G63">
-            <v>428</v>
-          </cell>
           <cell r="H63">
             <v>0.49</v>
           </cell>
-          <cell r="I63" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J63">
-            <v>-69</v>
-          </cell>
           <cell r="K63">
             <v>69</v>
           </cell>
-          <cell r="L63" t="str">
-            <v>2.8 out of 5</v>
-          </cell>
           <cell r="M63">
             <v>2.8</v>
           </cell>
-          <cell r="N63" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="64">
-          <cell r="A64" t="str">
-            <v>Intelligent  LED Body Sensor Wireless Lighting Night Light USB</v>
-          </cell>
-          <cell r="B64" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C64" t="str">
-            <v>KSh 325</v>
-          </cell>
-          <cell r="D64">
-            <v>325</v>
-          </cell>
-          <cell r="E64" t="str">
-            <v>KSh 680</v>
-          </cell>
-          <cell r="F64">
-            <v>680</v>
-          </cell>
-          <cell r="G64">
-            <v>355</v>
-          </cell>
           <cell r="H64">
             <v>0.52</v>
           </cell>
-          <cell r="I64" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J64">
-            <v>-15</v>
-          </cell>
           <cell r="K64">
             <v>15</v>
           </cell>
-          <cell r="L64" t="str">
-            <v>2.7 out of 5</v>
-          </cell>
           <cell r="M64">
             <v>2.7</v>
           </cell>
-          <cell r="N64" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="65">
-          <cell r="A65" t="str">
-            <v>VIC Wireless Vacuum Cleaner Dual Use For Home And Car 120W High Power Powerful</v>
-          </cell>
-          <cell r="B65" t="str">
-            <v>Cleaning &amp; Appliances</v>
-          </cell>
-          <cell r="C65" t="str">
-            <v>KSh 1,220</v>
-          </cell>
-          <cell r="D65">
-            <v>1220</v>
-          </cell>
-          <cell r="E65" t="str">
-            <v>KSh 1,555</v>
-          </cell>
-          <cell r="F65">
-            <v>1555</v>
-          </cell>
-          <cell r="G65">
-            <v>335</v>
-          </cell>
           <cell r="H65">
             <v>0.22</v>
           </cell>
-          <cell r="I65" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J65">
-            <v>-16</v>
-          </cell>
           <cell r="K65">
             <v>16</v>
           </cell>
-          <cell r="L65" t="str">
-            <v>2.9 out of 5</v>
-          </cell>
           <cell r="M65">
             <v>2.9</v>
           </cell>
-          <cell r="N65" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="66">
-          <cell r="A66" t="str">
-            <v>Artificial Potted Flowers Room Decorative Flowers (2 Pieces)</v>
-          </cell>
-          <cell r="B66" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C66" t="str">
-            <v>KSh 990</v>
-          </cell>
-          <cell r="D66">
-            <v>990</v>
-          </cell>
-          <cell r="E66" t="str">
-            <v>KSh 1,814</v>
-          </cell>
-          <cell r="F66">
-            <v>1814</v>
-          </cell>
-          <cell r="G66">
-            <v>824</v>
-          </cell>
           <cell r="H66">
             <v>0.45</v>
           </cell>
-          <cell r="I66" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J66">
-            <v>-6</v>
-          </cell>
           <cell r="K66">
             <v>6</v>
           </cell>
-          <cell r="L66" t="str">
-            <v>2.2 out of 5</v>
-          </cell>
           <cell r="M66">
             <v>2.2000000000000002</v>
           </cell>
-          <cell r="N66" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="67">
-          <cell r="A67" t="str">
-            <v>380ML USB Rechargeable Portable Small Blenders And Juicers</v>
-          </cell>
-          <cell r="B67" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C67" t="str">
-            <v>KSh 1,000</v>
-          </cell>
-          <cell r="D67">
-            <v>1000</v>
-          </cell>
-          <cell r="E67" t="str">
-            <v>KSh 2,000</v>
-          </cell>
-          <cell r="F67">
-            <v>2000</v>
-          </cell>
-          <cell r="G67">
-            <v>1000</v>
-          </cell>
           <cell r="H67">
             <v>0.5</v>
           </cell>
-          <cell r="I67" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J67">
-            <v>-7</v>
-          </cell>
           <cell r="K67">
             <v>7</v>
           </cell>
-          <cell r="L67" t="str">
-            <v>2.3 out of 5</v>
-          </cell>
           <cell r="M67">
             <v>2.2999999999999998</v>
           </cell>
-          <cell r="N67" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="68">
-          <cell r="A68" t="str">
-            <v>32PCS Portable Cordless Drill Set With Cyclic Battery Drive -26 Variable Speed</v>
-          </cell>
-          <cell r="B68" t="str">
-            <v>Tools &amp; Hardware</v>
-          </cell>
-          <cell r="C68" t="str">
-            <v>KSh 3,750</v>
-          </cell>
-          <cell r="D68">
-            <v>3750</v>
-          </cell>
-          <cell r="E68" t="str">
-            <v>KSh 6,143</v>
-          </cell>
-          <cell r="F68">
-            <v>6143</v>
-          </cell>
-          <cell r="G68">
-            <v>2393</v>
-          </cell>
           <cell r="H68">
             <v>0.39</v>
           </cell>
-          <cell r="I68" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J68">
-            <v>-5</v>
-          </cell>
           <cell r="K68">
             <v>5</v>
           </cell>
-          <cell r="L68" t="str">
-            <v>3 out of 5</v>
-          </cell>
           <cell r="M68">
             <v>3</v>
           </cell>
-          <cell r="N68" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="69">
-          <cell r="A69" t="str">
-            <v>Agapeon Toothbrush Holder And Toothpaste Dispenser</v>
-          </cell>
-          <cell r="B69" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C69" t="str">
-            <v>KSh 382</v>
-          </cell>
-          <cell r="D69">
-            <v>382</v>
-          </cell>
-          <cell r="E69" t="str">
-            <v>KSh 700</v>
-          </cell>
-          <cell r="F69">
-            <v>700</v>
-          </cell>
-          <cell r="G69">
-            <v>318</v>
-          </cell>
           <cell r="H69">
             <v>0.45</v>
           </cell>
-          <cell r="I69" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J69">
-            <v>-17</v>
-          </cell>
           <cell r="K69">
             <v>17</v>
           </cell>
-          <cell r="L69" t="str">
-            <v>2.6 out of 5</v>
-          </cell>
           <cell r="M69">
             <v>2.6</v>
           </cell>
-          <cell r="N69" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="70">
-          <cell r="A70" t="str">
-            <v>Large Lazy Inflatable Sofa Chairs PVC Lounger Seat Bag</v>
-          </cell>
-          <cell r="B70" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C70" t="str">
-            <v>KSh 2,300</v>
-          </cell>
-          <cell r="D70">
-            <v>2300</v>
-          </cell>
-          <cell r="E70" t="str">
-            <v>KSh 3,240</v>
-          </cell>
-          <cell r="F70">
-            <v>3240</v>
-          </cell>
-          <cell r="G70">
-            <v>940</v>
-          </cell>
           <cell r="H70">
             <v>0.28999999999999998</v>
           </cell>
-          <cell r="I70" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J70">
-            <v>-5</v>
-          </cell>
           <cell r="K70">
             <v>5</v>
           </cell>
-          <cell r="L70" t="str">
-            <v>3 out of 5</v>
-          </cell>
           <cell r="M70">
             <v>3</v>
           </cell>
-          <cell r="N70" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="71">
-          <cell r="A71" t="str">
-            <v>Watercolour Gold Foil Textured Print Pillow Cover</v>
-          </cell>
-          <cell r="B71" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C71" t="str">
-            <v>KSh 345</v>
-          </cell>
-          <cell r="D71">
-            <v>345</v>
-          </cell>
-          <cell r="E71" t="str">
-            <v>KSh 602</v>
-          </cell>
-          <cell r="F71">
-            <v>602</v>
-          </cell>
-          <cell r="G71">
-            <v>257</v>
-          </cell>
           <cell r="H71">
             <v>0.43</v>
           </cell>
-          <cell r="I71" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J71">
-            <v>-6</v>
-          </cell>
           <cell r="K71">
             <v>6</v>
           </cell>
-          <cell r="L71" t="str">
-            <v>2.3 out of 5</v>
-          </cell>
           <cell r="M71">
             <v>2.2999999999999998</v>
           </cell>
-          <cell r="N71" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="72">
-          <cell r="A72" t="str">
-            <v>Wrought Iron Bathroom Shelf Wall Mounted Free Punch Toilet Rack</v>
-          </cell>
-          <cell r="B72" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C72" t="str">
-            <v>KSh 509</v>
-          </cell>
-          <cell r="D72">
-            <v>509</v>
-          </cell>
-          <cell r="E72" t="str">
-            <v>KSh 899</v>
-          </cell>
-          <cell r="F72">
-            <v>899</v>
-          </cell>
-          <cell r="G72">
-            <v>390</v>
-          </cell>
           <cell r="H72">
             <v>0.43</v>
           </cell>
-          <cell r="I72" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J72">
-            <v>-5</v>
-          </cell>
           <cell r="K72">
             <v>5</v>
           </cell>
-          <cell r="L72" t="str">
-            <v>3 out of 5</v>
-          </cell>
           <cell r="M72">
             <v>3</v>
           </cell>
-          <cell r="N72" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="73">
-          <cell r="A73" t="str">
-            <v>7-piece Set Of Storage Bags, Travel Storage Bags, Shoe Bags</v>
-          </cell>
-          <cell r="B73" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C73" t="str">
-            <v>KSh 968</v>
-          </cell>
-          <cell r="D73">
-            <v>968</v>
-          </cell>
-          <cell r="E73" t="str">
-            <v>KSh 1,814</v>
-          </cell>
-          <cell r="F73">
-            <v>1814</v>
-          </cell>
-          <cell r="G73">
-            <v>846</v>
-          </cell>
           <cell r="H73">
             <v>0.47</v>
           </cell>
-          <cell r="I73" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J73">
-            <v>-6</v>
-          </cell>
           <cell r="K73">
             <v>6</v>
           </cell>
-          <cell r="L73" t="str">
-            <v>2.2 out of 5</v>
-          </cell>
           <cell r="M73">
             <v>2.2000000000000002</v>
           </cell>
-          <cell r="N73" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="74">
-          <cell r="A74" t="str">
-            <v>Electric LED UV Mosquito Killer Lamp, Outdoor/Indoor Fly Killer Trap Light -USB</v>
-          </cell>
-          <cell r="B74" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C74" t="str">
-            <v>KSh 1,570</v>
-          </cell>
-          <cell r="D74">
-            <v>1570</v>
-          </cell>
-          <cell r="E74" t="str">
-            <v>KSh 2,988</v>
-          </cell>
-          <cell r="F74">
-            <v>2988</v>
-          </cell>
-          <cell r="G74">
-            <v>1418</v>
-          </cell>
           <cell r="H74">
             <v>0.47</v>
           </cell>
-          <cell r="I74" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J74">
-            <v>-7</v>
-          </cell>
           <cell r="K74">
             <v>7</v>
           </cell>
-          <cell r="L74" t="str">
-            <v>2.1 out of 5</v>
-          </cell>
           <cell r="M74">
             <v>2.1</v>
           </cell>
-          <cell r="N74" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="75">
-          <cell r="A75" t="str">
-            <v>2PCS/LOT Solar LED Outdoor Intelligent Light Controlled Wall Lamp</v>
-          </cell>
-          <cell r="B75" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C75" t="str">
-            <v>KSh 790</v>
-          </cell>
-          <cell r="D75">
-            <v>790</v>
-          </cell>
-          <cell r="E75" t="str">
-            <v>KSh 1,485</v>
-          </cell>
-          <cell r="F75">
-            <v>1485</v>
-          </cell>
-          <cell r="G75">
-            <v>695</v>
-          </cell>
           <cell r="H75">
             <v>0.47</v>
           </cell>
-          <cell r="I75" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K75" t="str">
             <v/>
           </cell>
           <cell r="M75" t="str">
             <v/>
           </cell>
-          <cell r="N75" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="76">
-          <cell r="A76" t="str">
-            <v>3PCS Rotary Scraper Thermomix For Kitchen</v>
-          </cell>
-          <cell r="B76" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C76" t="str">
-            <v>KSh 690</v>
-          </cell>
-          <cell r="D76">
-            <v>690</v>
-          </cell>
-          <cell r="E76" t="str">
-            <v>KSh 1,200</v>
-          </cell>
-          <cell r="F76">
-            <v>1200</v>
-          </cell>
-          <cell r="G76">
-            <v>510</v>
-          </cell>
           <cell r="H76">
             <v>0.43</v>
           </cell>
-          <cell r="I76" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K76" t="str">
             <v/>
           </cell>
           <cell r="M76" t="str">
             <v/>
           </cell>
-          <cell r="N76" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="77">
-          <cell r="A77" t="str">
-            <v>Cushion Silicone Butt Cushion Summer Ice Cushion Honeycomb Gel Cushion</v>
-          </cell>
-          <cell r="B77" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C77" t="str">
-            <v>KSh 1,732</v>
-          </cell>
-          <cell r="D77">
-            <v>1732</v>
-          </cell>
-          <cell r="E77" t="str">
-            <v>KSh 1,799</v>
-          </cell>
-          <cell r="F77">
-            <v>1799</v>
-          </cell>
-          <cell r="G77">
-            <v>67</v>
-          </cell>
           <cell r="H77">
             <v>0.04</v>
           </cell>
-          <cell r="I77" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K77" t="str">
             <v/>
           </cell>
           <cell r="M77" t="str">
             <v/>
           </cell>
-          <cell r="N77" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="78">
-          <cell r="A78" t="str">
-            <v>7PCS Silicone Thumb Knife Finger Protector Vegetable Harvesting Knife</v>
-          </cell>
-          <cell r="B78" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C78" t="str">
-            <v>KSh 230</v>
-          </cell>
-          <cell r="D78">
-            <v>230</v>
-          </cell>
-          <cell r="E78" t="str">
-            <v>KSh 450</v>
-          </cell>
-          <cell r="F78">
-            <v>450</v>
-          </cell>
-          <cell r="G78">
-            <v>220</v>
-          </cell>
           <cell r="H78">
             <v>0.49</v>
           </cell>
-          <cell r="I78" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K78" t="str">
             <v/>
           </cell>
           <cell r="M78" t="str">
             <v/>
           </cell>
-          <cell r="N78" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="79">
-          <cell r="A79" t="str">
-            <v>Memory Foam Neck Pillow Cover, With Pillow Core - 50*30cm</v>
-          </cell>
-          <cell r="B79" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C79" t="str">
-            <v>KSh 1,189</v>
-          </cell>
-          <cell r="D79">
-            <v>1189</v>
-          </cell>
-          <cell r="E79" t="str">
-            <v>KSh 2,199</v>
-          </cell>
-          <cell r="F79">
-            <v>2199</v>
-          </cell>
-          <cell r="G79">
-            <v>1010</v>
-          </cell>
           <cell r="H79">
             <v>0.46</v>
           </cell>
-          <cell r="I79" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J79">
-            <v>-1</v>
-          </cell>
           <cell r="K79">
             <v>1</v>
           </cell>
-          <cell r="L79" t="str">
-            <v>3 out of 5</v>
-          </cell>
           <cell r="M79">
             <v>3</v>
           </cell>
-          <cell r="N79" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="80">
-          <cell r="A80" t="str">
-            <v>Bedroom Simple Floor Hanging Clothes Rack Single Pole Hat Rack - White</v>
-          </cell>
-          <cell r="B80" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C80" t="str">
-            <v>KSh 979</v>
-          </cell>
-          <cell r="D80">
-            <v>979</v>
-          </cell>
-          <cell r="E80" t="str">
-            <v>KSh 1,920</v>
-          </cell>
-          <cell r="F80">
-            <v>1920</v>
-          </cell>
-          <cell r="G80">
-            <v>941</v>
-          </cell>
           <cell r="H80">
             <v>0.49</v>
           </cell>
-          <cell r="I80" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J80">
-            <v>-1</v>
-          </cell>
           <cell r="K80">
             <v>1</v>
           </cell>
-          <cell r="L80" t="str">
-            <v>5 out of 5</v>
-          </cell>
           <cell r="M80">
             <v>5</v>
           </cell>
-          <cell r="N80" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="81">
-          <cell r="A81" t="str">
-            <v>5m Waterproof Spherical LED String Lights Outdoor Ball Chain Lights Party Lighting Decoration Adjustable</v>
-          </cell>
-          <cell r="B81" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C81" t="str">
-            <v>KSh 1,460</v>
-          </cell>
-          <cell r="D81">
-            <v>1460</v>
-          </cell>
-          <cell r="E81" t="str">
-            <v>KSh 2,290</v>
-          </cell>
-          <cell r="F81">
-            <v>2290</v>
-          </cell>
-          <cell r="G81">
-            <v>830</v>
-          </cell>
           <cell r="H81">
             <v>0.36</v>
           </cell>
-          <cell r="I81" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K81" t="str">
             <v/>
           </cell>
           <cell r="M81" t="str">
             <v/>
           </cell>
-          <cell r="N81" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="82">
-          <cell r="A82" t="str">
-            <v>2 Pairs Cowhide Split Leather Work Gloves.32â„‰ Or Above Welding Gloves</v>
-          </cell>
-          <cell r="B82" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C82" t="str">
-            <v>KSh 1,666</v>
-          </cell>
-          <cell r="D82">
-            <v>1666</v>
-          </cell>
-          <cell r="E82" t="str">
-            <v>KSh 1,699</v>
-          </cell>
-          <cell r="F82">
-            <v>1699</v>
-          </cell>
-          <cell r="G82">
-            <v>33</v>
-          </cell>
           <cell r="H82">
             <v>0.02</v>
           </cell>
-          <cell r="I82" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K82" t="str">
             <v/>
           </cell>
           <cell r="M82" t="str">
             <v/>
           </cell>
-          <cell r="N82" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="83">
-          <cell r="A83" t="str">
-            <v>Household Pineapple Peeler Peeler</v>
-          </cell>
-          <cell r="B83" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C83" t="str">
-            <v>KSh 330</v>
-          </cell>
-          <cell r="D83">
-            <v>330</v>
-          </cell>
-          <cell r="E83" t="str">
-            <v>KSh 647</v>
-          </cell>
-          <cell r="F83">
-            <v>647</v>
-          </cell>
-          <cell r="G83">
-            <v>317</v>
-          </cell>
           <cell r="H83">
             <v>0.49</v>
           </cell>
-          <cell r="I83" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J83">
-            <v>-1</v>
-          </cell>
           <cell r="K83">
             <v>1</v>
           </cell>
-          <cell r="L83" t="str">
-            <v>4 out of 5</v>
-          </cell>
           <cell r="M83">
             <v>4</v>
           </cell>
-          <cell r="N83" t="str">
-            <v>Average</v>
-          </cell>
         </row>
         <row r="84">
-          <cell r="A84" t="str">
-            <v>Office Chair Lumbar Back Support Spine Posture Correction Pillow Car Cushion</v>
-          </cell>
-          <cell r="B84" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C84" t="str">
-            <v>KSh 1,466</v>
-          </cell>
-          <cell r="D84">
-            <v>1466</v>
-          </cell>
-          <cell r="E84" t="str">
-            <v>KSh 1,699</v>
-          </cell>
-          <cell r="F84">
-            <v>1699</v>
-          </cell>
-          <cell r="G84">
-            <v>233</v>
-          </cell>
           <cell r="H84">
             <v>0.14000000000000001</v>
           </cell>
-          <cell r="I84" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K84" t="str">
             <v/>
           </cell>
           <cell r="M84" t="str">
             <v/>
           </cell>
-          <cell r="N84" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="85">
-          <cell r="A85" t="str">
-            <v>Cartoon Car Decoration Cute Individuality For Car Home Desk</v>
-          </cell>
-          <cell r="B85" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C85" t="str">
-            <v>KSh 274</v>
-          </cell>
-          <cell r="D85">
-            <v>274</v>
-          </cell>
-          <cell r="E85" t="str">
-            <v>KSh 537</v>
-          </cell>
-          <cell r="F85">
-            <v>537</v>
-          </cell>
-          <cell r="G85">
-            <v>263</v>
-          </cell>
           <cell r="H85">
             <v>0.49</v>
           </cell>
-          <cell r="I85" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K85" t="str">
             <v/>
           </cell>
           <cell r="M85" t="str">
             <v/>
           </cell>
-          <cell r="N85" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="86">
-          <cell r="A86" t="str">
-            <v>Outdoor Portable Water Bottle With Medicine Box - 600ML - Black</v>
-          </cell>
-          <cell r="B86" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C86" t="str">
-            <v>KSh 799</v>
-          </cell>
-          <cell r="D86">
-            <v>799</v>
-          </cell>
-          <cell r="E86" t="str">
-            <v>KSh 900</v>
-          </cell>
-          <cell r="F86">
-            <v>900</v>
-          </cell>
-          <cell r="G86">
-            <v>101</v>
-          </cell>
           <cell r="H86">
             <v>0.11</v>
           </cell>
-          <cell r="I86" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K86" t="str">
             <v/>
           </cell>
           <cell r="M86" t="str">
             <v/>
           </cell>
-          <cell r="N86" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="87">
-          <cell r="A87" t="str">
-            <v>Wall-Mounted Toothbrush Toothpaste Holder With Multiple Slots</v>
-          </cell>
-          <cell r="B87" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C87" t="str">
-            <v>KSh 1,468</v>
-          </cell>
-          <cell r="D87">
-            <v>1468</v>
-          </cell>
-          <cell r="E87" t="str">
-            <v>KSh 1,699</v>
-          </cell>
-          <cell r="F87">
-            <v>1699</v>
-          </cell>
-          <cell r="G87">
-            <v>231</v>
-          </cell>
           <cell r="H87">
             <v>0.14000000000000001</v>
           </cell>
-          <cell r="I87" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K87" t="str">
             <v/>
           </cell>
           <cell r="M87" t="str">
             <v/>
           </cell>
-          <cell r="N87" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="88">
-          <cell r="A88" t="str">
-            <v>Multifunctional Hanging Storage Box Storage Bag (4 Layers)</v>
-          </cell>
-          <cell r="B88" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C88" t="str">
-            <v>KSh 630</v>
-          </cell>
-          <cell r="D88">
-            <v>630</v>
-          </cell>
-          <cell r="E88" t="str">
-            <v>KSh 1,100</v>
-          </cell>
-          <cell r="F88">
-            <v>1100</v>
-          </cell>
-          <cell r="G88">
-            <v>470</v>
-          </cell>
           <cell r="H88">
             <v>0.43</v>
           </cell>
-          <cell r="I88" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K88" t="str">
             <v/>
           </cell>
           <cell r="M88" t="str">
             <v/>
           </cell>
-          <cell r="N88" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="89">
-          <cell r="A89" t="str">
-            <v>Wall Clock With Hidden Safe Box</v>
-          </cell>
-          <cell r="B89" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C89" t="str">
-            <v>KSh 850</v>
-          </cell>
-          <cell r="D89">
-            <v>850</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>KSh 1,700</v>
-          </cell>
-          <cell r="F89">
-            <v>1700</v>
-          </cell>
-          <cell r="G89">
-            <v>850</v>
-          </cell>
           <cell r="H89">
             <v>0.5</v>
           </cell>
-          <cell r="I89" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K89" t="str">
             <v/>
           </cell>
           <cell r="M89" t="str">
             <v/>
           </cell>
-          <cell r="N89" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="90">
-          <cell r="A90" t="str">
-            <v>Portable Wine Table With Folding Round Table</v>
-          </cell>
-          <cell r="B90" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C90" t="str">
-            <v>KSh 1,300</v>
-          </cell>
-          <cell r="D90">
-            <v>1300</v>
-          </cell>
-          <cell r="E90" t="str">
-            <v>KSh 2,500</v>
-          </cell>
-          <cell r="F90">
-            <v>2500</v>
-          </cell>
-          <cell r="G90">
-            <v>1200</v>
-          </cell>
           <cell r="H90">
             <v>0.48</v>
           </cell>
-          <cell r="I90" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K90" t="str">
             <v/>
           </cell>
           <cell r="M90" t="str">
             <v/>
           </cell>
-          <cell r="N90" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="91">
-          <cell r="A91" t="str">
-            <v>Sewing Machine Needle Threader Stitch Insertion Tool Automatic Quick Sewing</v>
-          </cell>
-          <cell r="B91" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C91" t="str">
-            <v>KSh 105</v>
-          </cell>
-          <cell r="D91">
-            <v>105</v>
-          </cell>
-          <cell r="E91" t="str">
-            <v>KSh 200</v>
-          </cell>
-          <cell r="F91">
-            <v>200</v>
-          </cell>
-          <cell r="G91">
-            <v>95</v>
-          </cell>
           <cell r="H91">
             <v>0.48</v>
           </cell>
-          <cell r="I91" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K91" t="str">
             <v/>
           </cell>
           <cell r="M91" t="str">
             <v/>
           </cell>
-          <cell r="N91" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="92">
-          <cell r="A92" t="str">
-            <v>6 Layers Steel Pipe Assembling Dustproof Storage Shoe Cabinet</v>
-          </cell>
-          <cell r="B92" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C92" t="str">
-            <v>KSh 899</v>
-          </cell>
-          <cell r="D92">
-            <v>899</v>
-          </cell>
-          <cell r="E92" t="str">
-            <v>KSh 1,699</v>
-          </cell>
-          <cell r="F92">
-            <v>1699</v>
-          </cell>
-          <cell r="G92">
-            <v>800</v>
-          </cell>
           <cell r="H92">
             <v>0.47</v>
           </cell>
-          <cell r="I92" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K92" t="str">
             <v/>
           </cell>
           <cell r="M92" t="str">
             <v/>
           </cell>
-          <cell r="N92" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="93">
-          <cell r="A93" t="str">
-            <v>2PCS Ice Silk Square Cushion Cover Pillowcases - 65x65cm</v>
-          </cell>
-          <cell r="B93" t="str">
-            <v>Home Decor</v>
-          </cell>
-          <cell r="C93" t="str">
-            <v>KSh 1,200</v>
-          </cell>
-          <cell r="D93">
-            <v>1200</v>
-          </cell>
-          <cell r="E93" t="str">
-            <v>KSh 2,400</v>
-          </cell>
-          <cell r="F93">
-            <v>2400</v>
-          </cell>
-          <cell r="G93">
-            <v>1200</v>
-          </cell>
           <cell r="H93">
             <v>0.5</v>
           </cell>
-          <cell r="I93" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K93" t="str">
             <v/>
           </cell>
           <cell r="M93" t="str">
             <v/>
           </cell>
-          <cell r="N93" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="94">
-          <cell r="A94" t="str">
-            <v>Wall Mount Automatic Toothpaste Dispenser Toothbrush Holder Toothpaste Squeezer</v>
-          </cell>
-          <cell r="B94" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C94" t="str">
-            <v>KSh 1,526</v>
-          </cell>
-          <cell r="D94">
-            <v>1526</v>
-          </cell>
-          <cell r="E94" t="str">
-            <v>KSh 1,660</v>
-          </cell>
-          <cell r="F94">
-            <v>1660</v>
-          </cell>
-          <cell r="G94">
-            <v>134</v>
-          </cell>
           <cell r="H94">
             <v>0.08</v>
           </cell>
-          <cell r="I94" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K94" t="str">
             <v/>
           </cell>
           <cell r="M94" t="str">
             <v/>
           </cell>
-          <cell r="N94" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="95">
-          <cell r="A95" t="str">
-            <v>Portable Soap Dispenser Kitchen Detergent Press Box Kitchen Tools</v>
-          </cell>
-          <cell r="B95" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C95" t="str">
-            <v>KSh 1,462</v>
-          </cell>
-          <cell r="D95">
-            <v>1462</v>
-          </cell>
-          <cell r="E95" t="str">
-            <v>KSh 1,499</v>
-          </cell>
-          <cell r="F95">
-            <v>1499</v>
-          </cell>
-          <cell r="G95">
-            <v>37</v>
-          </cell>
           <cell r="H95">
             <v>0.02</v>
           </cell>
-          <cell r="I95" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K95" t="str">
             <v/>
           </cell>
           <cell r="M95" t="str">
             <v/>
           </cell>
-          <cell r="N95" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="96">
-          <cell r="A96" t="str">
-            <v>4 Piece Coloured Stainless Steel Kitchenware Set</v>
-          </cell>
-          <cell r="B96" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C96" t="str">
-            <v>KSh 248</v>
-          </cell>
-          <cell r="D96">
-            <v>248</v>
-          </cell>
-          <cell r="E96" t="str">
-            <v>KSh 486</v>
-          </cell>
-          <cell r="F96">
-            <v>486</v>
-          </cell>
-          <cell r="G96">
-            <v>238</v>
-          </cell>
           <cell r="H96">
             <v>0.49</v>
           </cell>
-          <cell r="I96" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K96" t="str">
             <v/>
           </cell>
           <cell r="M96" t="str">
             <v/>
           </cell>
-          <cell r="N96" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="97">
-          <cell r="A97" t="str">
-            <v>Metal Wall Clock Silver Dial Crystal Jewelry Round Home Decoration Wall Clock</v>
-          </cell>
-          <cell r="B97" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C97" t="str">
-            <v>KSh 3,546</v>
-          </cell>
-          <cell r="D97">
-            <v>3546</v>
-          </cell>
-          <cell r="E97" t="str">
-            <v>KSh 3,699</v>
-          </cell>
-          <cell r="F97">
-            <v>3699</v>
-          </cell>
-          <cell r="G97">
-            <v>153</v>
-          </cell>
           <cell r="H97">
             <v>0.04</v>
           </cell>
-          <cell r="I97" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K97" t="str">
             <v/>
           </cell>
           <cell r="M97" t="str">
             <v/>
           </cell>
-          <cell r="N97" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="98">
-          <cell r="A98" t="str">
-            <v>Baby Early Education Shape And Color Cognitive Training Toys</v>
-          </cell>
-          <cell r="B98" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C98" t="str">
-            <v>KSh 525</v>
-          </cell>
-          <cell r="D98">
-            <v>525</v>
-          </cell>
-          <cell r="E98" t="str">
-            <v>KSh 1,029</v>
-          </cell>
-          <cell r="F98">
-            <v>1029</v>
-          </cell>
-          <cell r="G98">
-            <v>504</v>
-          </cell>
           <cell r="H98">
             <v>0.49</v>
           </cell>
-          <cell r="I98" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K98" t="str">
             <v/>
           </cell>
           <cell r="M98" t="str">
             <v/>
           </cell>
-          <cell r="N98" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="99">
-          <cell r="A99" t="str">
-            <v>8in1 Screwdriver With LED Light</v>
-          </cell>
-          <cell r="B99" t="str">
-            <v>Tools &amp; Hardware</v>
-          </cell>
-          <cell r="C99" t="str">
-            <v>KSh 1,080</v>
-          </cell>
-          <cell r="D99">
-            <v>1080</v>
-          </cell>
-          <cell r="E99" t="str">
-            <v>KSh 1,874</v>
-          </cell>
-          <cell r="F99">
-            <v>1874</v>
-          </cell>
-          <cell r="G99">
-            <v>794</v>
-          </cell>
           <cell r="H99">
             <v>0.42</v>
           </cell>
-          <cell r="I99" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K99" t="str">
             <v/>
           </cell>
           <cell r="M99" t="str">
             <v/>
           </cell>
-          <cell r="N99" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="100">
-          <cell r="A100" t="str">
-            <v>Konka Healty Electric Kettle, 24-hour Heat Preservation,1.5L,800W, White</v>
-          </cell>
-          <cell r="B100" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C100" t="str">
-            <v>KSh 3,640</v>
-          </cell>
-          <cell r="D100">
-            <v>3640</v>
-          </cell>
-          <cell r="E100" t="str">
-            <v>KSh 4,588</v>
-          </cell>
-          <cell r="F100">
-            <v>4588</v>
-          </cell>
-          <cell r="G100">
-            <v>948</v>
-          </cell>
           <cell r="H100">
             <v>0.21</v>
           </cell>
-          <cell r="I100" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
-          <cell r="J100">
-            <v>-1</v>
-          </cell>
           <cell r="K100">
             <v>1</v>
           </cell>
-          <cell r="L100" t="str">
-            <v>5 out of 5</v>
-          </cell>
           <cell r="M100">
             <v>5</v>
           </cell>
-          <cell r="N100" t="str">
-            <v>Excellent</v>
-          </cell>
         </row>
         <row r="101">
-          <cell r="A101" t="str">
-            <v>9pcs Gas Mask, For Painting, Dust, Formaldehyde Grinding, Polishing</v>
-          </cell>
-          <cell r="B101" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C101" t="str">
-            <v>KSh 1,420</v>
-          </cell>
-          <cell r="D101">
-            <v>1420</v>
-          </cell>
-          <cell r="E101" t="str">
-            <v>KSh 2,420</v>
-          </cell>
-          <cell r="F101">
-            <v>2420</v>
-          </cell>
-          <cell r="G101">
-            <v>1000</v>
-          </cell>
           <cell r="H101">
             <v>0.41</v>
           </cell>
-          <cell r="I101" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K101" t="str">
             <v/>
           </cell>
           <cell r="M101" t="str">
             <v/>
           </cell>
-          <cell r="N101" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="102">
-          <cell r="A102" t="str">
-            <v>24 Grid Wall-mounted Sundries Organiser Fabric Closet Bag Storage Rack</v>
-          </cell>
-          <cell r="B102" t="str">
-            <v>Home &amp; Kitchen</v>
-          </cell>
-          <cell r="C102" t="str">
-            <v>KSh 1,875</v>
-          </cell>
-          <cell r="D102">
-            <v>1875</v>
-          </cell>
-          <cell r="E102" t="str">
-            <v>KSh 1,899</v>
-          </cell>
-          <cell r="F102">
-            <v>1899</v>
-          </cell>
-          <cell r="G102">
-            <v>24</v>
-          </cell>
           <cell r="H102">
             <v>0.01</v>
           </cell>
-          <cell r="I102" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K102" t="str">
             <v/>
           </cell>
           <cell r="M102" t="str">
             <v/>
           </cell>
-          <cell r="N102" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="103">
-          <cell r="A103" t="str">
-            <v>1PC Refrigerator Food Seal Pocket Fridge Bags</v>
-          </cell>
-          <cell r="B103" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C103" t="str">
-            <v>KSh 198</v>
-          </cell>
-          <cell r="D103">
-            <v>198</v>
-          </cell>
-          <cell r="E103" t="str">
-            <v>KSh 260</v>
-          </cell>
-          <cell r="F103">
-            <v>260</v>
-          </cell>
-          <cell r="G103">
-            <v>62</v>
-          </cell>
           <cell r="H103">
             <v>0.24</v>
           </cell>
-          <cell r="I103" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K103" t="str">
             <v/>
           </cell>
           <cell r="M103" t="str">
             <v/>
           </cell>
-          <cell r="N103" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="104">
-          <cell r="A104" t="str">
-            <v>LED Solar Street Light-fake Camera</v>
-          </cell>
-          <cell r="B104" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C104" t="str">
-            <v>KSh 1,150</v>
-          </cell>
-          <cell r="D104">
-            <v>1150</v>
-          </cell>
-          <cell r="E104" t="str">
-            <v>KSh 1,737</v>
-          </cell>
-          <cell r="F104">
-            <v>1737</v>
-          </cell>
-          <cell r="G104">
-            <v>587</v>
-          </cell>
           <cell r="H104">
             <v>0.34</v>
           </cell>
-          <cell r="I104" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K104" t="str">
             <v/>
           </cell>
           <cell r="M104" t="str">
             <v/>
           </cell>
-          <cell r="N104" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="105">
-          <cell r="A105" t="str">
-            <v>Cartoon Embroidered Mini Towel Bear Cotton Wash Cloth Hand 4pcs</v>
-          </cell>
-          <cell r="B105" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C105" t="str">
-            <v>KSh 1,190</v>
-          </cell>
-          <cell r="D105">
-            <v>1190</v>
-          </cell>
-          <cell r="E105" t="str">
-            <v>KSh 1,810</v>
-          </cell>
-          <cell r="F105">
-            <v>1810</v>
-          </cell>
-          <cell r="G105">
-            <v>620</v>
-          </cell>
           <cell r="H105">
             <v>0.34</v>
           </cell>
-          <cell r="I105" t="str">
-            <v xml:space="preserve">Medium </v>
-          </cell>
           <cell r="K105" t="str">
             <v/>
           </cell>
           <cell r="M105" t="str">
             <v/>
           </cell>
-          <cell r="N105" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="106">
-          <cell r="A106" t="str">
-            <v>Shower Nozzle Cleaning Unclogging Needle Mini Crevice Small Hole Cleaning Brush</v>
-          </cell>
-          <cell r="B106" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C106" t="str">
-            <v>KSh 1,658</v>
-          </cell>
-          <cell r="D106">
-            <v>1658</v>
-          </cell>
-          <cell r="E106" t="str">
-            <v>KSh 1,699</v>
-          </cell>
-          <cell r="F106">
-            <v>1699</v>
-          </cell>
-          <cell r="G106">
-            <v>41</v>
-          </cell>
           <cell r="H106">
             <v>0.02</v>
           </cell>
-          <cell r="I106" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K106" t="str">
             <v/>
           </cell>
           <cell r="M106" t="str">
             <v/>
           </cell>
-          <cell r="N106" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="107">
-          <cell r="A107" t="str">
-            <v>Thickening Multipurpose Non Stick Easy To Clean Heat Resistant Spoon Pad</v>
-          </cell>
-          <cell r="B107" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C107" t="str">
-            <v>KSh 1,768</v>
-          </cell>
-          <cell r="D107">
-            <v>1768</v>
-          </cell>
-          <cell r="E107" t="str">
-            <v>KSh 1,799</v>
-          </cell>
-          <cell r="F107">
-            <v>1799</v>
-          </cell>
-          <cell r="G107">
-            <v>31</v>
-          </cell>
           <cell r="H107">
             <v>0.02</v>
           </cell>
-          <cell r="I107" t="str">
-            <v>Low</v>
-          </cell>
           <cell r="K107" t="str">
             <v/>
           </cell>
           <cell r="M107" t="str">
             <v/>
           </cell>
-          <cell r="N107" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="108">
-          <cell r="A108" t="str">
-            <v>6 In 1 Bottle Can Opener Multifunctional Easy Opener</v>
-          </cell>
-          <cell r="B108" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C108" t="str">
-            <v>KSh 199</v>
-          </cell>
-          <cell r="D108">
-            <v>199</v>
-          </cell>
-          <cell r="E108" t="str">
-            <v>KSh 553</v>
-          </cell>
-          <cell r="F108">
-            <v>553</v>
-          </cell>
-          <cell r="G108">
-            <v>354</v>
-          </cell>
           <cell r="H108">
             <v>0.64</v>
           </cell>
-          <cell r="I108" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K108" t="str">
             <v/>
           </cell>
           <cell r="M108" t="str">
             <v/>
           </cell>
-          <cell r="N108" t="str">
-            <v/>
-          </cell>
         </row>
         <row r="109">
-          <cell r="A109" t="str">
-            <v>Wall-mounted Sticker Punch-free Plug Fixer</v>
-          </cell>
-          <cell r="B109" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C109" t="str">
-            <v>KSh 450</v>
-          </cell>
-          <cell r="D109">
-            <v>450</v>
-          </cell>
-          <cell r="E109" t="str">
-            <v>KSh 900</v>
-          </cell>
-          <cell r="F109">
-            <v>900</v>
-          </cell>
-          <cell r="G109">
-            <v>450</v>
-          </cell>
           <cell r="H109">
             <v>0.5</v>
           </cell>
-          <cell r="I109" t="str">
-            <v>High</v>
-          </cell>
-          <cell r="J109">
-            <v>-1</v>
-          </cell>
           <cell r="K109">
             <v>1</v>
           </cell>
-          <cell r="L109" t="str">
-            <v>2 out of 5</v>
-          </cell>
           <cell r="M109">
             <v>2</v>
           </cell>
-          <cell r="N109" t="str">
-            <v>Poor</v>
-          </cell>
         </row>
         <row r="110">
-          <cell r="A110" t="str">
-            <v>Black Simple Water Cup Wine Coaster Anti Slip Absorbent</v>
-          </cell>
-          <cell r="B110" t="str">
-            <v>Other</v>
-          </cell>
-          <cell r="C110" t="str">
-            <v>KSh 169</v>
-          </cell>
-          <cell r="D110">
-            <v>169</v>
-          </cell>
-          <cell r="E110" t="str">
-            <v>KSh 320</v>
-          </cell>
-          <cell r="F110">
-            <v>320</v>
-          </cell>
-          <cell r="G110">
-            <v>151</v>
-          </cell>
           <cell r="H110">
             <v>0.47</v>
           </cell>
-          <cell r="I110" t="str">
-            <v>High</v>
-          </cell>
           <cell r="K110" t="str">
             <v/>
           </cell>
           <cell r="M110" t="str">
-            <v/>
-          </cell>
-          <cell r="N110" t="str">
             <v/>
           </cell>
         </row>
@@ -12981,6 +9661,19 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Excel_jumia_dataset"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
